--- a/podcast-data/Punzadas_Sonoras_referencias.xlsx
+++ b/podcast-data/Punzadas_Sonoras_referencias.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Referencias" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Episodios" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Autores" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Leyenda" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Referencias" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Episodios" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Autores" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Leyenda" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -689,7 +689,7 @@
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>presentación, amor, amistad, Barthes</t>
+          <t>Formato especial y evento, Amor y vínculos afectivos, Monográfico de autor/a</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr"/>
@@ -780,7 +780,7 @@
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>ausencia, amor, memoria, familia</t>
+          <t>Muerte y duelo, Amor y vínculos afectivos, Memoria e historia, Familia y maternidad</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr"/>
@@ -867,7 +867,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>ausencia, amor, memoria, familia</t>
+          <t>Muerte y duelo, Amor y vínculos afectivos, Memoria e historia, Familia y maternidad</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr"/>
@@ -940,7 +940,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>ausencia, amor, memoria, familia</t>
+          <t>Muerte y duelo, Amor y vínculos afectivos, Memoria e historia, Familia y maternidad</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr"/>
@@ -1027,7 +1027,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>ausencia, amor, memoria, familia</t>
+          <t>Muerte y duelo, Amor y vínculos afectivos, Memoria e historia, Familia y maternidad</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr"/>
@@ -1096,7 +1096,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>ausencia, amor, memoria, familia</t>
+          <t>Muerte y duelo, Amor y vínculos afectivos, Memoria e historia, Familia y maternidad</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr"/>
@@ -1165,7 +1165,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>exuberancia, dinero, clase social, influencers, intimidad</t>
+          <t>Arte, Capitalismo, trabajo y economía, Identidad y clase social, Medios, redes e internet, Amor y vínculos afectivos</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr"/>
@@ -1238,7 +1238,7 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>exuberancia, dinero, clase social, influencers, intimidad</t>
+          <t>Arte, Capitalismo, trabajo y economía, Identidad y clase social, Medios, redes e internet, Amor y vínculos afectivos</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr"/>
@@ -1315,7 +1315,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>exuberancia, dinero, clase social, influencers, intimidad</t>
+          <t>Arte, Capitalismo, trabajo y economía, Identidad y clase social, Medios, redes e internet, Amor y vínculos afectivos</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr"/>
@@ -1392,7 +1392,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>exuberancia, dinero, clase social, influencers, intimidad</t>
+          <t>Arte, Capitalismo, trabajo y economía, Identidad y clase social, Medios, redes e internet, Amor y vínculos afectivos</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr"/>
@@ -1469,7 +1469,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>exuberancia, dinero, clase social, influencers, intimidad</t>
+          <t>Arte, Capitalismo, trabajo y economía, Identidad y clase social, Medios, redes e internet, Amor y vínculos afectivos</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr"/>
@@ -1542,7 +1542,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>exuberancia, dinero, clase social, influencers, intimidad</t>
+          <t>Arte, Capitalismo, trabajo y economía, Identidad y clase social, Medios, redes e internet, Amor y vínculos afectivos</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr"/>
@@ -1619,7 +1619,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>exuberancia, dinero, clase social, influencers, intimidad</t>
+          <t>Arte, Capitalismo, trabajo y economía, Identidad y clase social, Medios, redes e internet, Amor y vínculos afectivos</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr"/>
@@ -1692,7 +1692,7 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>desrealidad, espacio, arquitectura, jerarquías sociales, cine</t>
+          <t>Existencia y contingencia, Espacio, límite y frontera, Ciudad y urbanismo, Identidad y clase social, Cine y series</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr"/>
@@ -1779,7 +1779,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>desrealidad, espacio, arquitectura, jerarquías sociales, cine</t>
+          <t>Existencia y contingencia, Espacio, límite y frontera, Ciudad y urbanismo, Identidad y clase social, Cine y series</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr"/>
@@ -1848,7 +1848,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>desrealidad, espacio, arquitectura, jerarquías sociales, cine</t>
+          <t>Existencia y contingencia, Espacio, límite y frontera, Ciudad y urbanismo, Identidad y clase social, Cine y series</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr"/>
@@ -1917,7 +1917,7 @@
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>desrealidad, espacio, arquitectura, jerarquías sociales, cine</t>
+          <t>Existencia y contingencia, Espacio, límite y frontera, Ciudad y urbanismo, Identidad y clase social, Cine y series</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr"/>
@@ -1990,7 +1990,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>desrealidad, espacio, arquitectura, jerarquías sociales, cine</t>
+          <t>Existencia y contingencia, Espacio, límite y frontera, Ciudad y urbanismo, Identidad y clase social, Cine y series</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr"/>
@@ -2067,7 +2067,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>desrealidad, espacio, arquitectura, jerarquías sociales, cine</t>
+          <t>Existencia y contingencia, Espacio, límite y frontera, Ciudad y urbanismo, Identidad y clase social, Cine y series</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr"/>
@@ -2140,7 +2140,7 @@
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>desrealidad, espacio, arquitectura, jerarquías sociales, cine</t>
+          <t>Existencia y contingencia, Espacio, límite y frontera, Ciudad y urbanismo, Identidad y clase social, Cine y series</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr"/>
@@ -2213,7 +2213,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>desrealidad, espacio, arquitectura, jerarquías sociales, cine</t>
+          <t>Existencia y contingencia, Espacio, límite y frontera, Ciudad y urbanismo, Identidad y clase social, Cine y series</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr"/>
@@ -2290,7 +2290,7 @@
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>cartas, correspondencia, escritura, amor</t>
+          <t>Lenguaje y escritura, Amor y vínculos afectivos</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr"/>
@@ -2359,7 +2359,7 @@
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>cartas, correspondencia, escritura, amor</t>
+          <t>Lenguaje y escritura, Amor y vínculos afectivos</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr"/>
@@ -2428,7 +2428,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>cartas, correspondencia, escritura, amor</t>
+          <t>Lenguaje y escritura, Amor y vínculos afectivos</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr"/>
@@ -2497,7 +2497,7 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>cartas, correspondencia, escritura, amor</t>
+          <t>Lenguaje y escritura, Amor y vínculos afectivos</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr"/>
@@ -2570,7 +2570,7 @@
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>cartas, correspondencia, escritura, amor</t>
+          <t>Lenguaje y escritura, Amor y vínculos afectivos</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr"/>
@@ -2643,7 +2643,7 @@
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>salida, crisis amorosa, matrimonio, arte</t>
+          <t>Viaje y desplazamiento, Amor y vínculos afectivos, Arte</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr"/>
@@ -2734,7 +2734,7 @@
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>salida, crisis amorosa, matrimonio, arte</t>
+          <t>Viaje y desplazamiento, Amor y vínculos afectivos, Arte</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr"/>
@@ -2815,7 +2815,7 @@
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>salida, crisis amorosa, matrimonio, arte</t>
+          <t>Viaje y desplazamiento, Amor y vínculos afectivos, Arte</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr"/>
@@ -2898,7 +2898,7 @@
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>salida, crisis amorosa, matrimonio, arte</t>
+          <t>Viaje y desplazamiento, Amor y vínculos afectivos, Arte</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr"/>
@@ -2975,7 +2975,7 @@
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>salida, crisis amorosa, matrimonio, arte</t>
+          <t>Viaje y desplazamiento, Amor y vínculos afectivos, Arte</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr"/>
@@ -3048,7 +3048,7 @@
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>salida, crisis amorosa, matrimonio, arte</t>
+          <t>Viaje y desplazamiento, Amor y vínculos afectivos, Arte</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr"/>
@@ -3121,7 +3121,7 @@
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>jardín, naturaleza, fotografía, escritura, Barthes</t>
+          <t>Naturaleza y elementos, Fotografía e imagen, Lenguaje y escritura, Monográfico de autor/a</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr"/>
@@ -3208,7 +3208,7 @@
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>jardín, naturaleza, fotografía, escritura, Barthes</t>
+          <t>Naturaleza y elementos, Fotografía e imagen, Lenguaje y escritura, Monográfico de autor/a</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr"/>
@@ -3281,7 +3281,7 @@
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>jardín, naturaleza, fotografía, escritura, Barthes</t>
+          <t>Naturaleza y elementos, Fotografía e imagen, Lenguaje y escritura, Monográfico de autor/a</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr"/>
@@ -3354,7 +3354,7 @@
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>jardín, naturaleza, fotografía, escritura, Barthes</t>
+          <t>Naturaleza y elementos, Fotografía e imagen, Lenguaje y escritura, Monográfico de autor/a</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr"/>
@@ -3423,7 +3423,7 @@
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>jardín, naturaleza, fotografía, escritura, Barthes</t>
+          <t>Naturaleza y elementos, Fotografía e imagen, Lenguaje y escritura, Monográfico de autor/a</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr"/>
@@ -3492,7 +3492,7 @@
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>jardín, naturaleza, fotografía, escritura, Barthes</t>
+          <t>Naturaleza y elementos, Fotografía e imagen, Lenguaje y escritura, Monográfico de autor/a</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr"/>
@@ -3561,7 +3561,7 @@
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>cartas, arte, escritura asémica, correspondencia</t>
+          <t>Lenguaje y escritura, Arte</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr"/>
@@ -3634,7 +3634,7 @@
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>cartas, arte, escritura asémica, correspondencia</t>
+          <t>Lenguaje y escritura, Arte</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr"/>
@@ -3703,7 +3703,7 @@
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>cartas, arte, escritura asémica, correspondencia</t>
+          <t>Lenguaje y escritura, Arte</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr"/>
@@ -3776,7 +3776,7 @@
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>cartas, arte, escritura asémica, correspondencia</t>
+          <t>Lenguaje y escritura, Arte</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr"/>
@@ -3845,7 +3845,7 @@
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>cartas, arte, escritura asémica, correspondencia</t>
+          <t>Lenguaje y escritura, Arte</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr"/>
@@ -3914,7 +3914,7 @@
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t>cartas, arte, escritura asémica, correspondencia</t>
+          <t>Lenguaje y escritura, Arte</t>
         </is>
       </c>
       <c r="J45" s="2" t="inlineStr"/>
@@ -3987,7 +3987,7 @@
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>noche, oscuridad, abusos sexuales, urbanismo feminista, literatura japonesa</t>
+          <t>Tiempo, Miedo y vulnerabilidad, Violencia y daño, Ciudad y urbanismo, Literatura y lectura</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr"/>
@@ -4074,7 +4074,7 @@
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>noche, oscuridad, abusos sexuales, urbanismo feminista, literatura japonesa</t>
+          <t>Tiempo, Miedo y vulnerabilidad, Violencia y daño, Ciudad y urbanismo, Literatura y lectura</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr"/>
@@ -4143,7 +4143,7 @@
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>noche, oscuridad, abusos sexuales, urbanismo feminista, literatura japonesa</t>
+          <t>Tiempo, Miedo y vulnerabilidad, Violencia y daño, Ciudad y urbanismo, Literatura y lectura</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr"/>
@@ -4212,7 +4212,7 @@
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>noche, oscuridad, abusos sexuales, urbanismo feminista, literatura japonesa</t>
+          <t>Tiempo, Miedo y vulnerabilidad, Violencia y daño, Ciudad y urbanismo, Literatura y lectura</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr"/>
@@ -4289,7 +4289,7 @@
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>traducción, lenguaje, identidad</t>
+          <t>Lenguaje y escritura, Identidad y clase social</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr"/>
@@ -4376,7 +4376,7 @@
       </c>
       <c r="I51" s="2" t="inlineStr">
         <is>
-          <t>traducción, lenguaje, identidad</t>
+          <t>Lenguaje y escritura, Identidad y clase social</t>
         </is>
       </c>
       <c r="J51" s="2" t="inlineStr"/>
@@ -4449,7 +4449,7 @@
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>traducción, lenguaje, identidad</t>
+          <t>Lenguaje y escritura, Identidad y clase social</t>
         </is>
       </c>
       <c r="J52" s="2" t="inlineStr"/>
@@ -4518,7 +4518,7 @@
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>traducción, lenguaje, identidad</t>
+          <t>Lenguaje y escritura, Identidad y clase social</t>
         </is>
       </c>
       <c r="J53" s="2" t="inlineStr"/>
@@ -4587,7 +4587,7 @@
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>traducción, lenguaje, identidad</t>
+          <t>Lenguaje y escritura, Identidad y clase social</t>
         </is>
       </c>
       <c r="J54" s="2" t="inlineStr"/>
@@ -4656,7 +4656,7 @@
       </c>
       <c r="I55" s="2" t="inlineStr">
         <is>
-          <t>traducción, lenguaje, identidad</t>
+          <t>Lenguaje y escritura, Identidad y clase social</t>
         </is>
       </c>
       <c r="J55" s="2" t="inlineStr"/>
@@ -4725,7 +4725,7 @@
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t>declaración, cortejo, amor, cine</t>
+          <t>Amor y vínculos afectivos, Cine y series</t>
         </is>
       </c>
       <c r="J56" s="2" t="inlineStr"/>
@@ -4798,7 +4798,7 @@
       </c>
       <c r="I57" s="2" t="inlineStr">
         <is>
-          <t>declaración, cortejo, amor, cine</t>
+          <t>Amor y vínculos afectivos, Cine y series</t>
         </is>
       </c>
       <c r="J57" s="2" t="inlineStr"/>
@@ -4875,7 +4875,7 @@
       </c>
       <c r="I58" s="2" t="inlineStr">
         <is>
-          <t>declaración, cortejo, amor, cine</t>
+          <t>Amor y vínculos afectivos, Cine y series</t>
         </is>
       </c>
       <c r="J58" s="2" t="inlineStr"/>
@@ -4956,7 +4956,7 @@
       </c>
       <c r="I59" s="2" t="inlineStr">
         <is>
-          <t>declaración, cortejo, amor, cine</t>
+          <t>Amor y vínculos afectivos, Cine y series</t>
         </is>
       </c>
       <c r="J59" s="2" t="inlineStr"/>
@@ -5033,7 +5033,7 @@
       </c>
       <c r="I60" s="2" t="inlineStr">
         <is>
-          <t>noche, sueño, escepticismo, capitalismo, mitología</t>
+          <t>Tiempo, Existencia y contingencia, Filosofía y epistemología, Capitalismo, trabajo y economía, Mito y relato</t>
         </is>
       </c>
       <c r="J60" s="2" t="inlineStr"/>
@@ -5106,7 +5106,7 @@
       </c>
       <c r="I61" s="2" t="inlineStr">
         <is>
-          <t>noche, sueño, escepticismo, capitalismo, mitología</t>
+          <t>Tiempo, Existencia y contingencia, Filosofía y epistemología, Capitalismo, trabajo y economía, Mito y relato</t>
         </is>
       </c>
       <c r="J61" s="2" t="inlineStr"/>
@@ -5183,7 +5183,7 @@
       </c>
       <c r="I62" s="2" t="inlineStr">
         <is>
-          <t>recuerdo, olvido, lenguaje, series</t>
+          <t>Memoria e historia, Lenguaje y escritura, Cine y series</t>
         </is>
       </c>
       <c r="J62" s="2" t="inlineStr"/>
@@ -5252,7 +5252,7 @@
       </c>
       <c r="I63" s="2" t="inlineStr">
         <is>
-          <t>recuerdo, olvido, lenguaje, series</t>
+          <t>Memoria e historia, Lenguaje y escritura, Cine y series</t>
         </is>
       </c>
       <c r="J63" s="2" t="inlineStr"/>
@@ -5333,7 +5333,7 @@
       </c>
       <c r="I64" s="2" t="inlineStr">
         <is>
-          <t>recuerdo, olvido, lenguaje, series</t>
+          <t>Memoria e historia, Lenguaje y escritura, Cine y series</t>
         </is>
       </c>
       <c r="J64" s="2" t="inlineStr"/>
@@ -5406,7 +5406,7 @@
       </c>
       <c r="I65" s="2" t="inlineStr">
         <is>
-          <t>dolor, enfermedad, cáncer, vulnerabilidad</t>
+          <t>Emociones y afectos, Cuerpo y mirada, Miedo y vulnerabilidad</t>
         </is>
       </c>
       <c r="J65" s="2" t="inlineStr"/>
@@ -5475,7 +5475,7 @@
       </c>
       <c r="I66" s="2" t="inlineStr">
         <is>
-          <t>dolor, enfermedad, cáncer, vulnerabilidad</t>
+          <t>Emociones y afectos, Cuerpo y mirada, Miedo y vulnerabilidad</t>
         </is>
       </c>
       <c r="J66" s="2" t="inlineStr"/>
@@ -5544,7 +5544,7 @@
       </c>
       <c r="I67" s="2" t="inlineStr">
         <is>
-          <t>dolor, enfermedad, cáncer, vulnerabilidad</t>
+          <t>Emociones y afectos, Cuerpo y mirada, Miedo y vulnerabilidad</t>
         </is>
       </c>
       <c r="J67" s="2" t="inlineStr"/>
@@ -5613,7 +5613,7 @@
       </c>
       <c r="I68" s="2" t="inlineStr">
         <is>
-          <t>dolor, enfermedad, cáncer, vulnerabilidad</t>
+          <t>Emociones y afectos, Cuerpo y mirada, Miedo y vulnerabilidad</t>
         </is>
       </c>
       <c r="J68" s="2" t="inlineStr"/>
@@ -5682,7 +5682,7 @@
       </c>
       <c r="I69" s="2" t="inlineStr">
         <is>
-          <t>dolor, enfermedad, cáncer, vulnerabilidad</t>
+          <t>Emociones y afectos, Cuerpo y mirada, Miedo y vulnerabilidad</t>
         </is>
       </c>
       <c r="J69" s="2" t="inlineStr"/>
@@ -5755,7 +5755,7 @@
       </c>
       <c r="I70" s="2" t="inlineStr">
         <is>
-          <t>dolor, enfermedad, cáncer, vulnerabilidad</t>
+          <t>Emociones y afectos, Cuerpo y mirada, Miedo y vulnerabilidad</t>
         </is>
       </c>
       <c r="J70" s="2" t="inlineStr"/>
@@ -5824,7 +5824,7 @@
       </c>
       <c r="I71" s="2" t="inlineStr">
         <is>
-          <t>dolor ajeno, ética médica, vulnerabilidad</t>
+          <t>Emociones y afectos, Ética y moral, Miedo y vulnerabilidad</t>
         </is>
       </c>
       <c r="J71" s="2" t="inlineStr"/>
@@ -5893,7 +5893,7 @@
       </c>
       <c r="I72" s="2" t="inlineStr">
         <is>
-          <t>dolor ajeno, ética médica, vulnerabilidad</t>
+          <t>Emociones y afectos, Ética y moral, Miedo y vulnerabilidad</t>
         </is>
       </c>
       <c r="J72" s="2" t="inlineStr"/>
@@ -5962,7 +5962,7 @@
       </c>
       <c r="I73" s="2" t="inlineStr">
         <is>
-          <t>dolor ajeno, ética médica, vulnerabilidad</t>
+          <t>Emociones y afectos, Ética y moral, Miedo y vulnerabilidad</t>
         </is>
       </c>
       <c r="J73" s="2" t="inlineStr"/>
@@ -6035,7 +6035,7 @@
       </c>
       <c r="I74" s="2" t="inlineStr">
         <is>
-          <t>dolor ajeno, ética médica, vulnerabilidad</t>
+          <t>Emociones y afectos, Ética y moral, Miedo y vulnerabilidad</t>
         </is>
       </c>
       <c r="J74" s="2" t="inlineStr"/>
@@ -6122,7 +6122,7 @@
       </c>
       <c r="I75" s="2" t="inlineStr">
         <is>
-          <t>dolor ajeno, ética médica, vulnerabilidad</t>
+          <t>Emociones y afectos, Ética y moral, Miedo y vulnerabilidad</t>
         </is>
       </c>
       <c r="J75" s="2" t="inlineStr"/>
@@ -6199,7 +6199,7 @@
       </c>
       <c r="I76" s="2" t="inlineStr">
         <is>
-          <t>amistad, vínculos, toxicidad, Barthes</t>
+          <t>Amor y vínculos afectivos, Monográfico de autor/a</t>
         </is>
       </c>
       <c r="J76" s="2" t="inlineStr"/>
@@ -6286,7 +6286,7 @@
       </c>
       <c r="I77" s="2" t="inlineStr">
         <is>
-          <t>amistad, vínculos, toxicidad, Barthes</t>
+          <t>Amor y vínculos afectivos, Monográfico de autor/a</t>
         </is>
       </c>
       <c r="J77" s="2" t="inlineStr"/>
@@ -6355,7 +6355,7 @@
       </c>
       <c r="I78" s="2" t="inlineStr">
         <is>
-          <t>amistad, vínculos, toxicidad, Barthes</t>
+          <t>Amor y vínculos afectivos, Monográfico de autor/a</t>
         </is>
       </c>
       <c r="J78" s="2" t="inlineStr"/>
@@ -6424,7 +6424,7 @@
       </c>
       <c r="I79" s="2" t="inlineStr">
         <is>
-          <t>amistad, vínculos, toxicidad, Barthes</t>
+          <t>Amor y vínculos afectivos, Monográfico de autor/a</t>
         </is>
       </c>
       <c r="J79" s="2" t="inlineStr"/>
@@ -6493,7 +6493,7 @@
       </c>
       <c r="I80" s="2" t="inlineStr">
         <is>
-          <t>amistad, vínculos, toxicidad, Barthes</t>
+          <t>Amor y vínculos afectivos, Monográfico de autor/a</t>
         </is>
       </c>
       <c r="J80" s="2" t="inlineStr"/>
@@ -6566,7 +6566,7 @@
       </c>
       <c r="I81" s="2" t="inlineStr">
         <is>
-          <t>lectura, ficción, erotismo, arte y moral</t>
+          <t>Literatura y lectura, Narración, ficción y autoficción, Deseo y erotismo, Ética y moral</t>
         </is>
       </c>
       <c r="J81" s="2" t="inlineStr"/>
@@ -6653,7 +6653,7 @@
       </c>
       <c r="I82" s="2" t="inlineStr">
         <is>
-          <t>lectura, ficción, erotismo, arte y moral</t>
+          <t>Literatura y lectura, Narración, ficción y autoficción, Deseo y erotismo, Ética y moral</t>
         </is>
       </c>
       <c r="J82" s="2" t="inlineStr"/>
@@ -6736,7 +6736,7 @@
       </c>
       <c r="I83" s="2" t="inlineStr">
         <is>
-          <t>lectura, ficción, erotismo, arte y moral</t>
+          <t>Literatura y lectura, Narración, ficción y autoficción, Deseo y erotismo, Ética y moral</t>
         </is>
       </c>
       <c r="J83" s="2" t="inlineStr"/>
@@ -6805,7 +6805,7 @@
       </c>
       <c r="I84" s="2" t="inlineStr">
         <is>
-          <t>lectura, ficción, erotismo, arte y moral</t>
+          <t>Literatura y lectura, Narración, ficción y autoficción, Deseo y erotismo, Ética y moral</t>
         </is>
       </c>
       <c r="J84" s="2" t="inlineStr"/>
@@ -6874,7 +6874,7 @@
       </c>
       <c r="I85" s="2" t="inlineStr">
         <is>
-          <t>lectura, ficción, erotismo, arte y moral</t>
+          <t>Literatura y lectura, Narración, ficción y autoficción, Deseo y erotismo, Ética y moral</t>
         </is>
       </c>
       <c r="J85" s="2" t="inlineStr"/>
@@ -6943,7 +6943,7 @@
       </c>
       <c r="I86" s="2" t="inlineStr">
         <is>
-          <t>lectura, ficción, erotismo, arte y moral</t>
+          <t>Literatura y lectura, Narración, ficción y autoficción, Deseo y erotismo, Ética y moral</t>
         </is>
       </c>
       <c r="J86" s="2" t="inlineStr"/>
@@ -7012,7 +7012,7 @@
       </c>
       <c r="I87" s="2" t="inlineStr">
         <is>
-          <t>lectura, ficción, erotismo, arte y moral</t>
+          <t>Literatura y lectura, Narración, ficción y autoficción, Deseo y erotismo, Ética y moral</t>
         </is>
       </c>
       <c r="J87" s="2" t="inlineStr"/>
@@ -7081,7 +7081,7 @@
       </c>
       <c r="I88" s="2" t="inlineStr">
         <is>
-          <t>lectura, ficción, erotismo, arte y moral</t>
+          <t>Literatura y lectura, Narración, ficción y autoficción, Deseo y erotismo, Ética y moral</t>
         </is>
       </c>
       <c r="J88" s="2" t="inlineStr"/>
@@ -7150,7 +7150,7 @@
       </c>
       <c r="I89" s="2" t="inlineStr">
         <is>
-          <t>lectura, ficción, erotismo, arte y moral</t>
+          <t>Literatura y lectura, Narración, ficción y autoficción, Deseo y erotismo, Ética y moral</t>
         </is>
       </c>
       <c r="J89" s="2" t="inlineStr"/>
@@ -7223,7 +7223,7 @@
       </c>
       <c r="I90" s="2" t="inlineStr">
         <is>
-          <t>mito, ideología, publicidad, Barthes</t>
+          <t>Mito y relato, Política y actualidad, Medios, redes e internet, Monográfico de autor/a</t>
         </is>
       </c>
       <c r="J90" s="2" t="inlineStr"/>
@@ -7310,7 +7310,7 @@
       </c>
       <c r="I91" s="2" t="inlineStr">
         <is>
-          <t>mito, ideología, publicidad, Barthes</t>
+          <t>Mito y relato, Política y actualidad, Medios, redes e internet, Monográfico de autor/a</t>
         </is>
       </c>
       <c r="J91" s="2" t="inlineStr"/>
@@ -7397,7 +7397,7 @@
       </c>
       <c r="I92" s="2" t="inlineStr">
         <is>
-          <t>mito, ideología, publicidad, Barthes</t>
+          <t>Mito y relato, Política y actualidad, Medios, redes e internet, Monográfico de autor/a</t>
         </is>
       </c>
       <c r="J92" s="2" t="inlineStr"/>
@@ -7488,7 +7488,7 @@
       </c>
       <c r="I93" s="2" t="inlineStr">
         <is>
-          <t>fiesta, alegría, tiempo, trabajo</t>
+          <t>Emociones y afectos, Tiempo, Capitalismo, trabajo y economía</t>
         </is>
       </c>
       <c r="J93" s="2" t="inlineStr"/>
@@ -7579,7 +7579,7 @@
       </c>
       <c r="I94" s="2" t="inlineStr">
         <is>
-          <t>fiesta, alegría, tiempo, trabajo</t>
+          <t>Emociones y afectos, Tiempo, Capitalismo, trabajo y economía</t>
         </is>
       </c>
       <c r="J94" s="2" t="inlineStr"/>
@@ -7666,7 +7666,7 @@
       </c>
       <c r="I95" s="2" t="inlineStr">
         <is>
-          <t>fiesta, alegría, tiempo, trabajo</t>
+          <t>Emociones y afectos, Tiempo, Capitalismo, trabajo y economía</t>
         </is>
       </c>
       <c r="J95" s="2" t="inlineStr"/>
@@ -7753,7 +7753,7 @@
       </c>
       <c r="I96" s="2" t="inlineStr">
         <is>
-          <t>fiesta, alegría, tiempo, trabajo</t>
+          <t>Emociones y afectos, Tiempo, Capitalismo, trabajo y economía</t>
         </is>
       </c>
       <c r="J96" s="2" t="inlineStr"/>
@@ -7840,7 +7840,7 @@
       </c>
       <c r="I97" s="2" t="inlineStr">
         <is>
-          <t>fiesta, alegría, tiempo, trabajo</t>
+          <t>Emociones y afectos, Tiempo, Capitalismo, trabajo y economía</t>
         </is>
       </c>
       <c r="J97" s="2" t="inlineStr"/>
@@ -7917,7 +7917,7 @@
       </c>
       <c r="I98" s="2" t="inlineStr">
         <is>
-          <t>fiesta, alegría, tiempo, trabajo</t>
+          <t>Emociones y afectos, Tiempo, Capitalismo, trabajo y economía</t>
         </is>
       </c>
       <c r="J98" s="2" t="inlineStr"/>
@@ -7994,7 +7994,7 @@
       </c>
       <c r="I99" s="2" t="inlineStr">
         <is>
-          <t>Annie Ernaux, autoficción, orígenes, clase social</t>
+          <t>Monográfico de autor/a, Narración, ficción y autoficción, Memoria e historia, Identidad y clase social</t>
         </is>
       </c>
       <c r="J99" s="2" t="inlineStr"/>
@@ -8071,7 +8071,7 @@
       </c>
       <c r="I100" s="2" t="inlineStr">
         <is>
-          <t>exilio, lengua, imaginario amoroso, Historia</t>
+          <t>Viaje y desplazamiento, Lenguaje y escritura, Amor y vínculos afectivos, Memoria e historia</t>
         </is>
       </c>
       <c r="J100" s="2" t="inlineStr"/>
@@ -8162,7 +8162,7 @@
       </c>
       <c r="I101" s="2" t="inlineStr">
         <is>
-          <t>exilio, lengua, imaginario amoroso, Historia</t>
+          <t>Viaje y desplazamiento, Lenguaje y escritura, Amor y vínculos afectivos, Memoria e historia</t>
         </is>
       </c>
       <c r="J101" s="2" t="inlineStr"/>
@@ -8245,7 +8245,7 @@
       </c>
       <c r="I102" s="2" t="inlineStr">
         <is>
-          <t>exilio, lengua, imaginario amoroso, Historia</t>
+          <t>Viaje y desplazamiento, Lenguaje y escritura, Amor y vínculos afectivos, Memoria e historia</t>
         </is>
       </c>
       <c r="J102" s="2" t="inlineStr"/>
@@ -8318,7 +8318,7 @@
       </c>
       <c r="I103" s="2" t="inlineStr">
         <is>
-          <t>exilio, lengua, imaginario amoroso, Historia</t>
+          <t>Viaje y desplazamiento, Lenguaje y escritura, Amor y vínculos afectivos, Memoria e historia</t>
         </is>
       </c>
       <c r="J103" s="2" t="inlineStr"/>
@@ -8395,7 +8395,7 @@
       </c>
       <c r="I104" s="2" t="inlineStr">
         <is>
-          <t>exilio, lengua, imaginario amoroso, Historia</t>
+          <t>Viaje y desplazamiento, Lenguaje y escritura, Amor y vínculos afectivos, Memoria e historia</t>
         </is>
       </c>
       <c r="J104" s="2" t="inlineStr"/>
@@ -8468,7 +8468,7 @@
       </c>
       <c r="I105" s="2" t="inlineStr">
         <is>
-          <t>exilio, lengua, imaginario amoroso, Historia</t>
+          <t>Viaje y desplazamiento, Lenguaje y escritura, Amor y vínculos afectivos, Memoria e historia</t>
         </is>
       </c>
       <c r="J105" s="2" t="inlineStr"/>
@@ -8537,7 +8537,7 @@
       </c>
       <c r="I106" s="2" t="inlineStr">
         <is>
-          <t>exilio, lengua, imaginario amoroso, Historia</t>
+          <t>Viaje y desplazamiento, Lenguaje y escritura, Amor y vínculos afectivos, Memoria e historia</t>
         </is>
       </c>
       <c r="J106" s="2" t="inlineStr"/>
@@ -8610,7 +8610,7 @@
       </c>
       <c r="I107" s="2" t="inlineStr">
         <is>
-          <t>Annie Ernaux, clase social, tránsfuga de clase, universidad</t>
+          <t>Monográfico de autor/a, Identidad y clase social</t>
         </is>
       </c>
       <c r="J107" s="2" t="inlineStr"/>
@@ -8693,7 +8693,7 @@
       </c>
       <c r="I108" s="2" t="inlineStr">
         <is>
-          <t>Annie Ernaux, clase social, tránsfuga de clase, universidad</t>
+          <t>Monográfico de autor/a, Identidad y clase social</t>
         </is>
       </c>
       <c r="J108" s="2" t="inlineStr"/>
@@ -8762,7 +8762,7 @@
       </c>
       <c r="I109" s="2" t="inlineStr">
         <is>
-          <t>Annie Ernaux, clase social, tránsfuga de clase, universidad</t>
+          <t>Monográfico de autor/a, Identidad y clase social</t>
         </is>
       </c>
       <c r="J109" s="2" t="inlineStr"/>
@@ -8831,7 +8831,7 @@
       </c>
       <c r="I110" s="2" t="inlineStr">
         <is>
-          <t>Annie Ernaux, clase social, tránsfuga de clase, universidad</t>
+          <t>Monográfico de autor/a, Identidad y clase social</t>
         </is>
       </c>
       <c r="J110" s="2" t="inlineStr"/>
@@ -8900,7 +8900,7 @@
       </c>
       <c r="I111" s="2" t="inlineStr">
         <is>
-          <t>Annie Ernaux, clase social, tránsfuga de clase, universidad</t>
+          <t>Monográfico de autor/a, Identidad y clase social</t>
         </is>
       </c>
       <c r="J111" s="2" t="inlineStr"/>
@@ -8973,7 +8973,7 @@
       </c>
       <c r="I112" s="2" t="inlineStr">
         <is>
-          <t>Annie Ernaux, familia, aborto, escritura, duelo</t>
+          <t>Monográfico de autor/a, Familia y maternidad, Feminismo y género, Lenguaje y escritura, Muerte y duelo</t>
         </is>
       </c>
       <c r="J112" s="2" t="inlineStr"/>
@@ -9060,7 +9060,7 @@
       </c>
       <c r="I113" s="2" t="inlineStr">
         <is>
-          <t>Annie Ernaux, familia, aborto, escritura, duelo</t>
+          <t>Monográfico de autor/a, Familia y maternidad, Feminismo y género, Lenguaje y escritura, Muerte y duelo</t>
         </is>
       </c>
       <c r="J113" s="2" t="inlineStr"/>
@@ -9147,7 +9147,7 @@
       </c>
       <c r="I114" s="2" t="inlineStr">
         <is>
-          <t>Annie Ernaux, familia, aborto, escritura, duelo</t>
+          <t>Monográfico de autor/a, Familia y maternidad, Feminismo y género, Lenguaje y escritura, Muerte y duelo</t>
         </is>
       </c>
       <c r="J114" s="2" t="inlineStr"/>
@@ -9234,7 +9234,7 @@
       </c>
       <c r="I115" s="2" t="inlineStr">
         <is>
-          <t>Annie Ernaux, familia, aborto, escritura, duelo</t>
+          <t>Monográfico de autor/a, Familia y maternidad, Feminismo y género, Lenguaje y escritura, Muerte y duelo</t>
         </is>
       </c>
       <c r="J115" s="2" t="inlineStr"/>
@@ -9315,7 +9315,7 @@
       </c>
       <c r="I116" s="2" t="inlineStr">
         <is>
-          <t>Annie Ernaux, familia, aborto, escritura, duelo</t>
+          <t>Monográfico de autor/a, Familia y maternidad, Feminismo y género, Lenguaje y escritura, Muerte y duelo</t>
         </is>
       </c>
       <c r="J116" s="2" t="inlineStr"/>
@@ -9402,7 +9402,7 @@
       </c>
       <c r="I117" s="2" t="inlineStr">
         <is>
-          <t>encuentro, duelo amoroso, urbanismo, espacio público</t>
+          <t>Amor y vínculos afectivos, Ciudad y urbanismo</t>
         </is>
       </c>
       <c r="J117" s="2" t="inlineStr"/>
@@ -9493,7 +9493,7 @@
       </c>
       <c r="I118" s="2" t="inlineStr">
         <is>
-          <t>encuentro, duelo amoroso, urbanismo, espacio público</t>
+          <t>Amor y vínculos afectivos, Ciudad y urbanismo</t>
         </is>
       </c>
       <c r="J118" s="2" t="inlineStr"/>
@@ -9570,7 +9570,7 @@
       </c>
       <c r="I119" s="2" t="inlineStr">
         <is>
-          <t>encuentro, duelo amoroso, urbanismo, espacio público</t>
+          <t>Amor y vínculos afectivos, Ciudad y urbanismo</t>
         </is>
       </c>
       <c r="J119" s="2" t="inlineStr"/>
@@ -9643,7 +9643,7 @@
       </c>
       <c r="I120" s="2" t="inlineStr">
         <is>
-          <t>encuentro, duelo amoroso, urbanismo, espacio público</t>
+          <t>Amor y vínculos afectivos, Ciudad y urbanismo</t>
         </is>
       </c>
       <c r="J120" s="2" t="inlineStr"/>
@@ -9712,7 +9712,7 @@
       </c>
       <c r="I121" s="2" t="inlineStr">
         <is>
-          <t>encuentro, duelo amoroso, urbanismo, espacio público</t>
+          <t>Amor y vínculos afectivos, Ciudad y urbanismo</t>
         </is>
       </c>
       <c r="J121" s="2" t="inlineStr"/>
@@ -9781,7 +9781,7 @@
       </c>
       <c r="I122" s="2" t="inlineStr">
         <is>
-          <t>encuentro, duelo amoroso, urbanismo, espacio público</t>
+          <t>Amor y vínculos afectivos, Ciudad y urbanismo</t>
         </is>
       </c>
       <c r="J122" s="2" t="inlineStr"/>
@@ -9850,7 +9850,7 @@
       </c>
       <c r="I123" s="2" t="inlineStr">
         <is>
-          <t>encuentro, duelo amoroso, urbanismo, espacio público</t>
+          <t>Amor y vínculos afectivos, Ciudad y urbanismo</t>
         </is>
       </c>
       <c r="J123" s="2" t="inlineStr"/>
@@ -9919,7 +9919,7 @@
       </c>
       <c r="I124" s="2" t="inlineStr">
         <is>
-          <t>encuentro, duelo amoroso, urbanismo, espacio público</t>
+          <t>Amor y vínculos afectivos, Ciudad y urbanismo</t>
         </is>
       </c>
       <c r="J124" s="2" t="inlineStr"/>
@@ -9988,7 +9988,7 @@
       </c>
       <c r="I125" s="2" t="inlineStr">
         <is>
-          <t>encuentro, duelo amoroso, urbanismo, espacio público</t>
+          <t>Amor y vínculos afectivos, Ciudad y urbanismo</t>
         </is>
       </c>
       <c r="J125" s="2" t="inlineStr"/>
@@ -10065,7 +10065,7 @@
       </c>
       <c r="I126" s="2" t="inlineStr">
         <is>
-          <t>Annie Ernaux, pasión amorosa, deseo, celos, sexo</t>
+          <t>Monográfico de autor/a, Amor y vínculos afectivos, Deseo y erotismo, Sexualidad y disidencia sexual</t>
         </is>
       </c>
       <c r="J126" s="2" t="inlineStr"/>
@@ -10152,7 +10152,7 @@
       </c>
       <c r="I127" s="2" t="inlineStr">
         <is>
-          <t>Annie Ernaux, pasión amorosa, deseo, celos, sexo</t>
+          <t>Monográfico de autor/a, Amor y vínculos afectivos, Deseo y erotismo, Sexualidad y disidencia sexual</t>
         </is>
       </c>
       <c r="J127" s="2" t="inlineStr"/>
@@ -10243,7 +10243,7 @@
       </c>
       <c r="I128" s="2" t="inlineStr">
         <is>
-          <t>Annie Ernaux, pasión amorosa, deseo, celos, sexo</t>
+          <t>Monográfico de autor/a, Amor y vínculos afectivos, Deseo y erotismo, Sexualidad y disidencia sexual</t>
         </is>
       </c>
       <c r="J128" s="2" t="inlineStr"/>
@@ -10330,7 +10330,7 @@
       </c>
       <c r="I129" s="2" t="inlineStr">
         <is>
-          <t>Annie Ernaux, pasión amorosa, deseo, celos, sexo</t>
+          <t>Monográfico de autor/a, Amor y vínculos afectivos, Deseo y erotismo, Sexualidad y disidencia sexual</t>
         </is>
       </c>
       <c r="J129" s="2" t="inlineStr"/>
@@ -10417,7 +10417,7 @@
       </c>
       <c r="I130" s="2" t="inlineStr">
         <is>
-          <t>Annie Ernaux, pasión amorosa, deseo, celos, sexo</t>
+          <t>Monográfico de autor/a, Amor y vínculos afectivos, Deseo y erotismo, Sexualidad y disidencia sexual</t>
         </is>
       </c>
       <c r="J130" s="2" t="inlineStr"/>
@@ -10504,7 +10504,7 @@
       </c>
       <c r="I131" s="2" t="inlineStr">
         <is>
-          <t>Annie Ernaux, pasión amorosa, deseo, celos, sexo</t>
+          <t>Monográfico de autor/a, Amor y vínculos afectivos, Deseo y erotismo, Sexualidad y disidencia sexual</t>
         </is>
       </c>
       <c r="J131" s="2" t="inlineStr"/>
@@ -10585,7 +10585,7 @@
       </c>
       <c r="I132" s="2" t="inlineStr">
         <is>
-          <t>escucha, sonido, ruido, ética, radio</t>
+          <t>Sonido y escucha, Ética y moral</t>
         </is>
       </c>
       <c r="J132" s="2" t="inlineStr"/>
@@ -10676,7 +10676,7 @@
       </c>
       <c r="I133" s="2" t="inlineStr">
         <is>
-          <t>escucha, sonido, ruido, ética, radio</t>
+          <t>Sonido y escucha, Ética y moral</t>
         </is>
       </c>
       <c r="J133" s="2" t="inlineStr"/>
@@ -10763,7 +10763,7 @@
       </c>
       <c r="I134" s="2" t="inlineStr">
         <is>
-          <t>escucha, sonido, ruido, ética, radio</t>
+          <t>Sonido y escucha, Ética y moral</t>
         </is>
       </c>
       <c r="J134" s="2" t="inlineStr"/>
@@ -10836,7 +10836,7 @@
       </c>
       <c r="I135" s="2" t="inlineStr">
         <is>
-          <t>escucha, sonido, ruido, ética, radio</t>
+          <t>Sonido y escucha, Ética y moral</t>
         </is>
       </c>
       <c r="J135" s="2" t="inlineStr"/>
@@ -10905,7 +10905,7 @@
       </c>
       <c r="I136" s="2" t="inlineStr">
         <is>
-          <t>escucha, sonido, ruido, ética, radio</t>
+          <t>Sonido y escucha, Ética y moral</t>
         </is>
       </c>
       <c r="J136" s="2" t="inlineStr"/>
@@ -10974,7 +10974,7 @@
       </c>
       <c r="I137" s="2" t="inlineStr">
         <is>
-          <t>escucha, sonido, ruido, ética, radio</t>
+          <t>Sonido y escucha, Ética y moral</t>
         </is>
       </c>
       <c r="J137" s="2" t="inlineStr"/>
@@ -11043,7 +11043,7 @@
       </c>
       <c r="I138" s="2" t="inlineStr">
         <is>
-          <t>escucha, sonido, ruido, ética, radio</t>
+          <t>Sonido y escucha, Ética y moral</t>
         </is>
       </c>
       <c r="J138" s="2" t="inlineStr"/>
@@ -11116,7 +11116,7 @@
       </c>
       <c r="I139" s="2" t="inlineStr">
         <is>
-          <t>ruinas, memoria, ciudad, poesía, antropología</t>
+          <t>Ciudad y urbanismo, Memoria e historia, Literatura y lectura, Filosofía y epistemología</t>
         </is>
       </c>
       <c r="J139" s="2" t="inlineStr"/>
@@ -11193,7 +11193,7 @@
       </c>
       <c r="I140" s="2" t="inlineStr">
         <is>
-          <t>ruinas, memoria, ciudad, poesía, antropología</t>
+          <t>Ciudad y urbanismo, Memoria e historia, Literatura y lectura, Filosofía y epistemología</t>
         </is>
       </c>
       <c r="J140" s="2" t="inlineStr">
@@ -11284,7 +11284,7 @@
       </c>
       <c r="I141" s="2" t="inlineStr">
         <is>
-          <t>ruinas, memoria, ciudad, poesía, antropología</t>
+          <t>Ciudad y urbanismo, Memoria e historia, Literatura y lectura, Filosofía y epistemología</t>
         </is>
       </c>
       <c r="J141" s="2" t="inlineStr"/>
@@ -11365,7 +11365,7 @@
       </c>
       <c r="I142" s="2" t="inlineStr">
         <is>
-          <t>ruinas, memoria, ciudad, poesía, antropología</t>
+          <t>Ciudad y urbanismo, Memoria e historia, Literatura y lectura, Filosofía y epistemología</t>
         </is>
       </c>
       <c r="J142" s="2" t="inlineStr"/>
@@ -11442,7 +11442,7 @@
       </c>
       <c r="I143" s="2" t="inlineStr">
         <is>
-          <t>Katherine Mansfield, modernismo, cuento, biografía</t>
+          <t>Monográfico de autor/a, Arte, Literatura y lectura, Narración, ficción y autoficción</t>
         </is>
       </c>
       <c r="J143" s="2" t="inlineStr"/>
@@ -11515,7 +11515,7 @@
       </c>
       <c r="I144" s="2" t="inlineStr">
         <is>
-          <t>Katherine Mansfield, modernismo, cuento, biografía</t>
+          <t>Monográfico de autor/a, Arte, Literatura y lectura, Narración, ficción y autoficción</t>
         </is>
       </c>
       <c r="J144" s="2" t="inlineStr"/>
@@ -11584,7 +11584,7 @@
       </c>
       <c r="I145" s="2" t="inlineStr">
         <is>
-          <t>Katherine Mansfield, modernismo, cuento, biografía</t>
+          <t>Monográfico de autor/a, Arte, Literatura y lectura, Narración, ficción y autoficción</t>
         </is>
       </c>
       <c r="J145" s="2" t="inlineStr"/>
@@ -11657,7 +11657,7 @@
       </c>
       <c r="I146" s="2" t="inlineStr">
         <is>
-          <t>primavera, mito, crisis climática, mundo rural</t>
+          <t>Tiempo, Mito y relato, Ecología y crisis climática, Ruralidad y territorio</t>
         </is>
       </c>
       <c r="J146" s="2" t="inlineStr">
@@ -11744,7 +11744,7 @@
       </c>
       <c r="I147" s="2" t="inlineStr">
         <is>
-          <t>primavera, mito, crisis climática, mundo rural</t>
+          <t>Tiempo, Mito y relato, Ecología y crisis climática, Ruralidad y territorio</t>
         </is>
       </c>
       <c r="J147" s="2" t="inlineStr"/>
@@ -11813,7 +11813,7 @@
       </c>
       <c r="I148" s="2" t="inlineStr">
         <is>
-          <t>primavera, mito, crisis climática, mundo rural</t>
+          <t>Tiempo, Mito y relato, Ecología y crisis climática, Ruralidad y territorio</t>
         </is>
       </c>
       <c r="J148" s="2" t="inlineStr"/>
@@ -11882,7 +11882,7 @@
       </c>
       <c r="I149" s="2" t="inlineStr">
         <is>
-          <t>primavera, mito, crisis climática, mundo rural</t>
+          <t>Tiempo, Mito y relato, Ecología y crisis climática, Ruralidad y territorio</t>
         </is>
       </c>
       <c r="J149" s="2" t="inlineStr"/>
@@ -11955,7 +11955,7 @@
       </c>
       <c r="I150" s="2" t="inlineStr">
         <is>
-          <t>primavera, mito, crisis climática, mundo rural</t>
+          <t>Tiempo, Mito y relato, Ecología y crisis climática, Ruralidad y territorio</t>
         </is>
       </c>
       <c r="J150" s="2" t="inlineStr"/>
@@ -12032,7 +12032,7 @@
       </c>
       <c r="I151" s="2" t="inlineStr">
         <is>
-          <t>primavera, mito, crisis climática, mundo rural</t>
+          <t>Tiempo, Mito y relato, Ecología y crisis climática, Ruralidad y territorio</t>
         </is>
       </c>
       <c r="J151" s="2" t="inlineStr"/>
@@ -12109,7 +12109,7 @@
       </c>
       <c r="I152" s="2" t="inlineStr">
         <is>
-          <t>Janet Frame, salud mental, autobiografía, Nueva Zelanda</t>
+          <t>Monográfico de autor/a, Cuerpo y mirada, Narración, ficción y autoficción, Viaje y desplazamiento</t>
         </is>
       </c>
       <c r="J152" s="2" t="inlineStr">
@@ -12200,7 +12200,7 @@
       </c>
       <c r="I153" s="2" t="inlineStr">
         <is>
-          <t>Janet Frame, salud mental, autobiografía, Nueva Zelanda</t>
+          <t>Monográfico de autor/a, Cuerpo y mirada, Narración, ficción y autoficción, Viaje y desplazamiento</t>
         </is>
       </c>
       <c r="J153" s="2" t="inlineStr">
@@ -12291,7 +12291,7 @@
       </c>
       <c r="I154" s="2" t="inlineStr">
         <is>
-          <t>Janet Frame, salud mental, autobiografía, Nueva Zelanda</t>
+          <t>Monográfico de autor/a, Cuerpo y mirada, Narración, ficción y autoficción, Viaje y desplazamiento</t>
         </is>
       </c>
       <c r="J154" s="2" t="inlineStr"/>
@@ -12368,7 +12368,7 @@
       </c>
       <c r="I155" s="2" t="inlineStr">
         <is>
-          <t>ligar, deseo, vulnerabilidad, aislacionismo amoroso, ética</t>
+          <t>Amor y vínculos afectivos, Deseo y erotismo, Miedo y vulnerabilidad, Soledad y aislamiento, Ética y moral</t>
         </is>
       </c>
       <c r="J155" s="2" t="inlineStr"/>
@@ -12459,7 +12459,7 @@
       </c>
       <c r="I156" s="2" t="inlineStr">
         <is>
-          <t>ligar, deseo, vulnerabilidad, aislacionismo amoroso, ética</t>
+          <t>Amor y vínculos afectivos, Deseo y erotismo, Miedo y vulnerabilidad, Soledad y aislamiento, Ética y moral</t>
         </is>
       </c>
       <c r="J156" s="2" t="inlineStr"/>
@@ -12540,7 +12540,7 @@
       </c>
       <c r="I157" s="2" t="inlineStr">
         <is>
-          <t>ligar, deseo, vulnerabilidad, aislacionismo amoroso, ética</t>
+          <t>Amor y vínculos afectivos, Deseo y erotismo, Miedo y vulnerabilidad, Soledad y aislamiento, Ética y moral</t>
         </is>
       </c>
       <c r="J157" s="2" t="inlineStr"/>
@@ -12627,7 +12627,7 @@
       </c>
       <c r="I158" s="2" t="inlineStr">
         <is>
-          <t>ligar, deseo, vulnerabilidad, aislacionismo amoroso, ética</t>
+          <t>Amor y vínculos afectivos, Deseo y erotismo, Miedo y vulnerabilidad, Soledad y aislamiento, Ética y moral</t>
         </is>
       </c>
       <c r="J158" s="2" t="inlineStr"/>
@@ -12708,7 +12708,7 @@
       </c>
       <c r="I159" s="2" t="inlineStr">
         <is>
-          <t>ligar, deseo, vulnerabilidad, aislacionismo amoroso, ética</t>
+          <t>Amor y vínculos afectivos, Deseo y erotismo, Miedo y vulnerabilidad, Soledad y aislamiento, Ética y moral</t>
         </is>
       </c>
       <c r="J159" s="2" t="inlineStr"/>
@@ -12781,7 +12781,7 @@
       </c>
       <c r="I160" s="2" t="inlineStr">
         <is>
-          <t>ligar, deseo, vulnerabilidad, aislacionismo amoroso, ética</t>
+          <t>Amor y vínculos afectivos, Deseo y erotismo, Miedo y vulnerabilidad, Soledad y aislamiento, Ética y moral</t>
         </is>
       </c>
       <c r="J160" s="2" t="inlineStr"/>
@@ -12854,7 +12854,7 @@
       </c>
       <c r="I161" s="2" t="inlineStr">
         <is>
-          <t>lectura, lector, bibliotecas, clásicos</t>
+          <t>Literatura y lectura</t>
         </is>
       </c>
       <c r="J161" s="2" t="inlineStr"/>
@@ -12937,7 +12937,7 @@
       </c>
       <c r="I162" s="2" t="inlineStr">
         <is>
-          <t>lectura, lector, bibliotecas, clásicos</t>
+          <t>Literatura y lectura</t>
         </is>
       </c>
       <c r="J162" s="2" t="inlineStr"/>
@@ -13006,7 +13006,7 @@
       </c>
       <c r="I163" s="2" t="inlineStr">
         <is>
-          <t>lectura, lector, bibliotecas, clásicos</t>
+          <t>Literatura y lectura</t>
         </is>
       </c>
       <c r="J163" s="2" t="inlineStr"/>
@@ -13075,7 +13075,7 @@
       </c>
       <c r="I164" s="2" t="inlineStr">
         <is>
-          <t>lectura, lector, bibliotecas, clásicos</t>
+          <t>Literatura y lectura</t>
         </is>
       </c>
       <c r="J164" s="2" t="inlineStr"/>
@@ -13144,7 +13144,7 @@
       </c>
       <c r="I165" s="2" t="inlineStr">
         <is>
-          <t>lectura, lector, bibliotecas, clásicos</t>
+          <t>Literatura y lectura</t>
         </is>
       </c>
       <c r="J165" s="2" t="inlineStr"/>
@@ -13213,7 +13213,7 @@
       </c>
       <c r="I166" s="2" t="inlineStr">
         <is>
-          <t>lectura, lector, bibliotecas, clásicos</t>
+          <t>Literatura y lectura</t>
         </is>
       </c>
       <c r="J166" s="2" t="inlineStr"/>
@@ -13286,7 +13286,7 @@
       </c>
       <c r="I167" s="2" t="inlineStr">
         <is>
-          <t>lectura, lector, bibliotecas, clásicos</t>
+          <t>Literatura y lectura</t>
         </is>
       </c>
       <c r="J167" s="2" t="inlineStr"/>
@@ -13355,7 +13355,7 @@
       </c>
       <c r="I168" s="2" t="inlineStr">
         <is>
-          <t>agua, abismo, mito, filosofía griega, capitalismo</t>
+          <t>Naturaleza y elementos, Existencia y contingencia, Mito y relato, Filosofía y epistemología, Capitalismo, trabajo y economía</t>
         </is>
       </c>
       <c r="J168" s="2" t="inlineStr"/>
@@ -13424,7 +13424,7 @@
       </c>
       <c r="I169" s="2" t="inlineStr">
         <is>
-          <t>agua, abismo, mito, filosofía griega, capitalismo</t>
+          <t>Naturaleza y elementos, Existencia y contingencia, Mito y relato, Filosofía y epistemología, Capitalismo, trabajo y economía</t>
         </is>
       </c>
       <c r="J169" s="2" t="inlineStr"/>
@@ -13497,7 +13497,7 @@
       </c>
       <c r="I170" s="2" t="inlineStr">
         <is>
-          <t>juego, infancia, violencia, Feria del Libro de Madrid</t>
+          <t>Emociones y afectos, Familia y maternidad, Violencia y daño, Formato especial y evento</t>
         </is>
       </c>
       <c r="J170" s="2" t="inlineStr">
@@ -13582,7 +13582,7 @@
       </c>
       <c r="I171" s="2" t="inlineStr">
         <is>
-          <t>juego, infancia, violencia, Feria del Libro de Madrid</t>
+          <t>Emociones y afectos, Familia y maternidad, Violencia y daño, Formato especial y evento</t>
         </is>
       </c>
       <c r="J171" s="2" t="inlineStr">
@@ -13673,7 +13673,7 @@
       </c>
       <c r="I172" s="2" t="inlineStr">
         <is>
-          <t>juego, infancia, violencia, Feria del Libro de Madrid</t>
+          <t>Emociones y afectos, Familia y maternidad, Violencia y daño, Formato especial y evento</t>
         </is>
       </c>
       <c r="J172" s="2" t="inlineStr">
@@ -13758,7 +13758,7 @@
       </c>
       <c r="I173" s="2" t="inlineStr">
         <is>
-          <t>juego, infancia, violencia, Feria del Libro de Madrid</t>
+          <t>Emociones y afectos, Familia y maternidad, Violencia y daño, Formato especial y evento</t>
         </is>
       </c>
       <c r="J173" s="2" t="inlineStr">
@@ -13843,7 +13843,7 @@
       </c>
       <c r="I174" s="2" t="inlineStr">
         <is>
-          <t>juego, infancia, violencia, Feria del Libro de Madrid</t>
+          <t>Emociones y afectos, Familia y maternidad, Violencia y daño, Formato especial y evento</t>
         </is>
       </c>
       <c r="J174" s="2" t="inlineStr">
@@ -13934,7 +13934,7 @@
       </c>
       <c r="I175" s="2" t="inlineStr">
         <is>
-          <t>juego, infancia, violencia, Feria del Libro de Madrid</t>
+          <t>Emociones y afectos, Familia y maternidad, Violencia y daño, Formato especial y evento</t>
         </is>
       </c>
       <c r="J175" s="2" t="inlineStr">
@@ -14025,7 +14025,7 @@
       </c>
       <c r="I176" s="2" t="inlineStr">
         <is>
-          <t>juego, infancia, violencia, Feria del Libro de Madrid</t>
+          <t>Emociones y afectos, Familia y maternidad, Violencia y daño, Formato especial y evento</t>
         </is>
       </c>
       <c r="J176" s="2" t="inlineStr">
@@ -14106,7 +14106,7 @@
       </c>
       <c r="I177" s="2" t="inlineStr">
         <is>
-          <t>juego, infancia, violencia, Feria del Libro de Madrid</t>
+          <t>Emociones y afectos, Familia y maternidad, Violencia y daño, Formato especial y evento</t>
         </is>
       </c>
       <c r="J177" s="2" t="inlineStr"/>
@@ -14175,7 +14175,7 @@
       </c>
       <c r="I178" s="2" t="inlineStr">
         <is>
-          <t>juego, infancia, violencia, Feria del Libro de Madrid</t>
+          <t>Emociones y afectos, Familia y maternidad, Violencia y daño, Formato especial y evento</t>
         </is>
       </c>
       <c r="J178" s="2" t="inlineStr"/>
@@ -14244,7 +14244,7 @@
       </c>
       <c r="I179" s="2" t="inlineStr">
         <is>
-          <t>juego, infancia, violencia, Feria del Libro de Madrid</t>
+          <t>Emociones y afectos, Familia y maternidad, Violencia y daño, Formato especial y evento</t>
         </is>
       </c>
       <c r="J179" s="2" t="inlineStr"/>
@@ -14321,7 +14321,7 @@
       </c>
       <c r="I180" s="2" t="inlineStr">
         <is>
-          <t>daño, crueldad, tortura, obsesión, culpa</t>
+          <t>Violencia y daño, Emociones y afectos, Ética y moral</t>
         </is>
       </c>
       <c r="J180" s="2" t="inlineStr"/>
@@ -14412,7 +14412,7 @@
       </c>
       <c r="I181" s="2" t="inlineStr">
         <is>
-          <t>daño, crueldad, tortura, obsesión, culpa</t>
+          <t>Violencia y daño, Emociones y afectos, Ética y moral</t>
         </is>
       </c>
       <c r="J181" s="2" t="inlineStr"/>
@@ -14499,7 +14499,7 @@
       </c>
       <c r="I182" s="2" t="inlineStr">
         <is>
-          <t>daño, crueldad, tortura, obsesión, culpa</t>
+          <t>Violencia y daño, Emociones y afectos, Ética y moral</t>
         </is>
       </c>
       <c r="J182" s="2" t="inlineStr"/>
@@ -14586,7 +14586,7 @@
       </c>
       <c r="I183" s="2" t="inlineStr">
         <is>
-          <t>daño, crueldad, tortura, obsesión, culpa</t>
+          <t>Violencia y daño, Emociones y afectos, Ética y moral</t>
         </is>
       </c>
       <c r="J183" s="2" t="inlineStr"/>
@@ -14667,7 +14667,7 @@
       </c>
       <c r="I184" s="2" t="inlineStr">
         <is>
-          <t>daño, crueldad, tortura, obsesión, culpa</t>
+          <t>Violencia y daño, Emociones y afectos, Ética y moral</t>
         </is>
       </c>
       <c r="J184" s="2" t="inlineStr"/>
@@ -14744,7 +14744,7 @@
       </c>
       <c r="I185" s="2" t="inlineStr">
         <is>
-          <t>daño, crueldad, tortura, obsesión, culpa</t>
+          <t>Violencia y daño, Emociones y afectos, Ética y moral</t>
         </is>
       </c>
       <c r="J185" s="2" t="inlineStr"/>
@@ -14835,7 +14835,7 @@
       </c>
       <c r="I186" s="2" t="inlineStr">
         <is>
-          <t>daño, crueldad, tortura, obsesión, culpa</t>
+          <t>Violencia y daño, Emociones y afectos, Ética y moral</t>
         </is>
       </c>
       <c r="J186" s="2" t="inlineStr"/>
@@ -14912,7 +14912,7 @@
       </c>
       <c r="I187" s="2" t="inlineStr">
         <is>
-          <t>daño, crueldad, tortura, obsesión, culpa</t>
+          <t>Violencia y daño, Emociones y afectos, Ética y moral</t>
         </is>
       </c>
       <c r="J187" s="2" t="inlineStr"/>
@@ -14989,7 +14989,7 @@
       </c>
       <c r="I188" s="2" t="inlineStr">
         <is>
-          <t>verano, memoria, turismo, identidad, Barthes</t>
+          <t>Tiempo, Memoria e historia, Viaje y desplazamiento, Identidad y clase social, Monográfico de autor/a</t>
         </is>
       </c>
       <c r="J188" s="2" t="inlineStr"/>
@@ -15076,7 +15076,7 @@
       </c>
       <c r="I189" s="2" t="inlineStr">
         <is>
-          <t>verano, memoria, turismo, identidad, Barthes</t>
+          <t>Tiempo, Memoria e historia, Viaje y desplazamiento, Identidad y clase social, Monográfico de autor/a</t>
         </is>
       </c>
       <c r="J189" s="2" t="inlineStr"/>
@@ -15157,7 +15157,7 @@
       </c>
       <c r="I190" s="2" t="inlineStr">
         <is>
-          <t>verano, memoria, turismo, identidad, Barthes</t>
+          <t>Tiempo, Memoria e historia, Viaje y desplazamiento, Identidad y clase social, Monográfico de autor/a</t>
         </is>
       </c>
       <c r="J190" s="2" t="inlineStr"/>
@@ -15244,7 +15244,7 @@
       </c>
       <c r="I191" s="2" t="inlineStr">
         <is>
-          <t>verano, memoria, turismo, identidad, Barthes</t>
+          <t>Tiempo, Memoria e historia, Viaje y desplazamiento, Identidad y clase social, Monográfico de autor/a</t>
         </is>
       </c>
       <c r="J191" s="2" t="inlineStr"/>
@@ -15331,7 +15331,7 @@
       </c>
       <c r="I192" s="2" t="inlineStr">
         <is>
-          <t>verano, memoria, turismo, identidad, Barthes</t>
+          <t>Tiempo, Memoria e historia, Viaje y desplazamiento, Identidad y clase social, Monográfico de autor/a</t>
         </is>
       </c>
       <c r="J192" s="2" t="inlineStr"/>
@@ -15418,7 +15418,7 @@
       </c>
       <c r="I193" s="2" t="inlineStr">
         <is>
-          <t>verano, memoria, turismo, identidad, Barthes</t>
+          <t>Tiempo, Memoria e historia, Viaje y desplazamiento, Identidad y clase social, Monográfico de autor/a</t>
         </is>
       </c>
       <c r="J193" s="2" t="inlineStr"/>
@@ -15505,7 +15505,7 @@
       </c>
       <c r="I194" s="2" t="inlineStr">
         <is>
-          <t>verano, memoria, turismo, identidad, Barthes</t>
+          <t>Tiempo, Memoria e historia, Viaje y desplazamiento, Identidad y clase social, Monográfico de autor/a</t>
         </is>
       </c>
       <c r="J194" s="2" t="inlineStr"/>
@@ -15586,7 +15586,7 @@
       </c>
       <c r="I195" s="2" t="inlineStr">
         <is>
-          <t>verano, memoria, turismo, identidad, Barthes</t>
+          <t>Tiempo, Memoria e historia, Viaje y desplazamiento, Identidad y clase social, Monográfico de autor/a</t>
         </is>
       </c>
       <c r="J195" s="2" t="inlineStr"/>
@@ -15677,7 +15677,7 @@
       </c>
       <c r="I196" s="2" t="inlineStr">
         <is>
-          <t>amor, ficción, deseo autotélico, emociones</t>
+          <t>Amor y vínculos afectivos, Narración, ficción y autoficción, Deseo y erotismo, Emociones y afectos</t>
         </is>
       </c>
       <c r="J196" s="2" t="inlineStr"/>
@@ -15768,7 +15768,7 @@
       </c>
       <c r="I197" s="2" t="inlineStr">
         <is>
-          <t>amor, ficción, deseo autotélico, emociones</t>
+          <t>Amor y vínculos afectivos, Narración, ficción y autoficción, Deseo y erotismo, Emociones y afectos</t>
         </is>
       </c>
       <c r="J197" s="2" t="inlineStr"/>
@@ -15845,7 +15845,7 @@
       </c>
       <c r="I198" s="2" t="inlineStr">
         <is>
-          <t>amor, ficción, deseo autotélico, emociones</t>
+          <t>Amor y vínculos afectivos, Narración, ficción y autoficción, Deseo y erotismo, Emociones y afectos</t>
         </is>
       </c>
       <c r="J198" s="2" t="inlineStr"/>
@@ -15918,7 +15918,7 @@
       </c>
       <c r="I199" s="2" t="inlineStr">
         <is>
-          <t>sexo, educación sexual, pornografía, intimidad, cine</t>
+          <t>Sexualidad y disidencia sexual, Amor y vínculos afectivos, Cine y series</t>
         </is>
       </c>
       <c r="J199" s="2" t="inlineStr"/>
@@ -15991,7 +15991,7 @@
       </c>
       <c r="I200" s="2" t="inlineStr">
         <is>
-          <t>sexo, educación sexual, pornografía, intimidad, cine</t>
+          <t>Sexualidad y disidencia sexual, Amor y vínculos afectivos, Cine y series</t>
         </is>
       </c>
       <c r="J200" s="2" t="inlineStr"/>
@@ -16064,7 +16064,7 @@
       </c>
       <c r="I201" s="2" t="inlineStr">
         <is>
-          <t>sexo, educación sexual, pornografía, intimidad, cine</t>
+          <t>Sexualidad y disidencia sexual, Amor y vínculos afectivos, Cine y series</t>
         </is>
       </c>
       <c r="J201" s="2" t="inlineStr"/>
@@ -16141,7 +16141,7 @@
       </c>
       <c r="I202" s="2" t="inlineStr">
         <is>
-          <t>rapto, caída, mito, inclinación, amor</t>
+          <t>Violencia y daño, Existencia y contingencia, Mito y relato, Filosofía y epistemología, Amor y vínculos afectivos</t>
         </is>
       </c>
       <c r="J202" s="2" t="inlineStr"/>
@@ -16232,7 +16232,7 @@
       </c>
       <c r="I203" s="2" t="inlineStr">
         <is>
-          <t>rapto, caída, mito, inclinación, amor</t>
+          <t>Violencia y daño, Existencia y contingencia, Mito y relato, Filosofía y epistemología, Amor y vínculos afectivos</t>
         </is>
       </c>
       <c r="J203" s="2" t="inlineStr"/>
@@ -16323,7 +16323,7 @@
       </c>
       <c r="I204" s="2" t="inlineStr">
         <is>
-          <t>rapto, caída, mito, inclinación, amor</t>
+          <t>Violencia y daño, Existencia y contingencia, Mito y relato, Filosofía y epistemología, Amor y vínculos afectivos</t>
         </is>
       </c>
       <c r="J204" s="2" t="inlineStr"/>
@@ -16410,7 +16410,7 @@
       </c>
       <c r="I205" s="2" t="inlineStr">
         <is>
-          <t>rapto, caída, mito, inclinación, amor</t>
+          <t>Violencia y daño, Existencia y contingencia, Mito y relato, Filosofía y epistemología, Amor y vínculos afectivos</t>
         </is>
       </c>
       <c r="J205" s="2" t="inlineStr"/>
@@ -16497,7 +16497,7 @@
       </c>
       <c r="I206" s="2" t="inlineStr">
         <is>
-          <t>imagen, violencia, muerte, Gaza, fotografía</t>
+          <t>Fotografía e imagen, Violencia y daño, Muerte y duelo, Política y actualidad</t>
         </is>
       </c>
       <c r="J206" s="2" t="inlineStr"/>
@@ -16570,7 +16570,7 @@
       </c>
       <c r="I207" s="2" t="inlineStr">
         <is>
-          <t>imagen, violencia, muerte, Gaza, fotografía</t>
+          <t>Fotografía e imagen, Violencia y daño, Muerte y duelo, Política y actualidad</t>
         </is>
       </c>
       <c r="J207" s="2" t="inlineStr"/>
@@ -16643,7 +16643,7 @@
       </c>
       <c r="I208" s="2" t="inlineStr">
         <is>
-          <t>imagen, violencia, muerte, Gaza, fotografía</t>
+          <t>Fotografía e imagen, Violencia y daño, Muerte y duelo, Política y actualidad</t>
         </is>
       </c>
       <c r="J208" s="2" t="inlineStr"/>
@@ -16712,7 +16712,7 @@
       </c>
       <c r="I209" s="2" t="inlineStr">
         <is>
-          <t>imagen, violencia, muerte, Gaza, fotografía</t>
+          <t>Fotografía e imagen, Violencia y daño, Muerte y duelo, Política y actualidad</t>
         </is>
       </c>
       <c r="J209" s="2" t="inlineStr"/>
@@ -16785,7 +16785,7 @@
       </c>
       <c r="I210" s="2" t="inlineStr">
         <is>
-          <t>deseo, consumo, publicidad, sexo, epistemología</t>
+          <t>Deseo y erotismo, Capitalismo, trabajo y economía, Medios, redes e internet, Sexualidad y disidencia sexual, Filosofía y epistemología</t>
         </is>
       </c>
       <c r="J210" s="2" t="inlineStr"/>
@@ -16872,7 +16872,7 @@
       </c>
       <c r="I211" s="2" t="inlineStr">
         <is>
-          <t>deseo, consumo, publicidad, sexo, epistemología</t>
+          <t>Deseo y erotismo, Capitalismo, trabajo y economía, Medios, redes e internet, Sexualidad y disidencia sexual, Filosofía y epistemología</t>
         </is>
       </c>
       <c r="J211" s="2" t="inlineStr"/>
@@ -16945,7 +16945,7 @@
       </c>
       <c r="I212" s="2" t="inlineStr">
         <is>
-          <t>deseo, consumo, publicidad, sexo, epistemología</t>
+          <t>Deseo y erotismo, Capitalismo, trabajo y economía, Medios, redes e internet, Sexualidad y disidencia sexual, Filosofía y epistemología</t>
         </is>
       </c>
       <c r="J212" s="2" t="inlineStr"/>
@@ -17018,7 +17018,7 @@
       </c>
       <c r="I213" s="2" t="inlineStr">
         <is>
-          <t>deseo, consumo, publicidad, sexo, epistemología</t>
+          <t>Deseo y erotismo, Capitalismo, trabajo y economía, Medios, redes e internet, Sexualidad y disidencia sexual, Filosofía y epistemología</t>
         </is>
       </c>
       <c r="J213" s="2" t="inlineStr"/>
@@ -17091,7 +17091,7 @@
       </c>
       <c r="I214" s="2" t="inlineStr">
         <is>
-          <t>deseo, consumo, publicidad, sexo, epistemología</t>
+          <t>Deseo y erotismo, Capitalismo, trabajo y economía, Medios, redes e internet, Sexualidad y disidencia sexual, Filosofía y epistemología</t>
         </is>
       </c>
       <c r="J214" s="2" t="inlineStr"/>
@@ -17160,7 +17160,7 @@
       </c>
       <c r="I215" s="2" t="inlineStr">
         <is>
-          <t>deseo, consumo, publicidad, sexo, epistemología</t>
+          <t>Deseo y erotismo, Capitalismo, trabajo y economía, Medios, redes e internet, Sexualidad y disidencia sexual, Filosofía y epistemología</t>
         </is>
       </c>
       <c r="J215" s="2" t="inlineStr"/>
@@ -17233,7 +17233,7 @@
       </c>
       <c r="I216" s="2" t="inlineStr">
         <is>
-          <t>deseo, consumo, publicidad, sexo, epistemología</t>
+          <t>Deseo y erotismo, Capitalismo, trabajo y economía, Medios, redes e internet, Sexualidad y disidencia sexual, Filosofía y epistemología</t>
         </is>
       </c>
       <c r="J216" s="2" t="inlineStr"/>
@@ -17314,7 +17314,7 @@
       </c>
       <c r="I217" s="2" t="inlineStr">
         <is>
-          <t>narración, memoria, identidad, tiempo, autoengaño</t>
+          <t>Narración, ficción y autoficción, Memoria e historia, Identidad y clase social, Tiempo, Ética y moral</t>
         </is>
       </c>
       <c r="J217" s="2" t="inlineStr"/>
@@ -17401,7 +17401,7 @@
       </c>
       <c r="I218" s="2" t="inlineStr">
         <is>
-          <t>narración, memoria, identidad, tiempo, autoengaño</t>
+          <t>Narración, ficción y autoficción, Memoria e historia, Identidad y clase social, Tiempo, Ética y moral</t>
         </is>
       </c>
       <c r="J218" s="2" t="inlineStr"/>
@@ -17484,7 +17484,7 @@
       </c>
       <c r="I219" s="2" t="inlineStr">
         <is>
-          <t>narración, memoria, identidad, tiempo, autoengaño</t>
+          <t>Narración, ficción y autoficción, Memoria e historia, Identidad y clase social, Tiempo, Ética y moral</t>
         </is>
       </c>
       <c r="J219" s="2" t="inlineStr"/>
@@ -17553,7 +17553,7 @@
       </c>
       <c r="I220" s="2" t="inlineStr">
         <is>
-          <t>narración, memoria, identidad, tiempo, autoengaño</t>
+          <t>Narración, ficción y autoficción, Memoria e historia, Identidad y clase social, Tiempo, Ética y moral</t>
         </is>
       </c>
       <c r="J220" s="2" t="inlineStr"/>
@@ -17622,7 +17622,7 @@
       </c>
       <c r="I221" s="2" t="inlineStr">
         <is>
-          <t>narración, memoria, identidad, tiempo, autoengaño</t>
+          <t>Narración, ficción y autoficción, Memoria e historia, Identidad y clase social, Tiempo, Ética y moral</t>
         </is>
       </c>
       <c r="J221" s="2" t="inlineStr"/>
@@ -17695,7 +17695,7 @@
       </c>
       <c r="I222" s="2" t="inlineStr">
         <is>
-          <t>narración, memoria, identidad, tiempo, autoengaño</t>
+          <t>Narración, ficción y autoficción, Memoria e historia, Identidad y clase social, Tiempo, Ética y moral</t>
         </is>
       </c>
       <c r="J222" s="2" t="inlineStr"/>
@@ -17772,7 +17772,7 @@
       </c>
       <c r="I223" s="2" t="inlineStr">
         <is>
-          <t>nombre propio, identidad, memoria, dictadura, comunidad trans</t>
+          <t>Lenguaje y escritura, Identidad y clase social, Memoria e historia, Sexualidad y disidencia sexual</t>
         </is>
       </c>
       <c r="J223" s="2" t="inlineStr"/>
@@ -17859,7 +17859,7 @@
       </c>
       <c r="I224" s="2" t="inlineStr">
         <is>
-          <t>nombre propio, identidad, memoria, dictadura, comunidad trans</t>
+          <t>Lenguaje y escritura, Identidad y clase social, Memoria e historia, Sexualidad y disidencia sexual</t>
         </is>
       </c>
       <c r="J224" s="2" t="inlineStr"/>
@@ -17936,7 +17936,7 @@
       </c>
       <c r="I225" s="2" t="inlineStr">
         <is>
-          <t>nombre propio, identidad, memoria, dictadura, comunidad trans</t>
+          <t>Lenguaje y escritura, Identidad y clase social, Memoria e historia, Sexualidad y disidencia sexual</t>
         </is>
       </c>
       <c r="J225" s="2" t="inlineStr">
@@ -18021,7 +18021,7 @@
       </c>
       <c r="I226" s="2" t="inlineStr">
         <is>
-          <t>nombre propio, identidad, memoria, dictadura, comunidad trans</t>
+          <t>Lenguaje y escritura, Identidad y clase social, Memoria e historia, Sexualidad y disidencia sexual</t>
         </is>
       </c>
       <c r="J226" s="2" t="inlineStr">
@@ -18112,7 +18112,7 @@
       </c>
       <c r="I227" s="2" t="inlineStr">
         <is>
-          <t>nombre propio, identidad, memoria, dictadura, comunidad trans</t>
+          <t>Lenguaje y escritura, Identidad y clase social, Memoria e historia, Sexualidad y disidencia sexual</t>
         </is>
       </c>
       <c r="J227" s="2" t="inlineStr"/>
@@ -18199,7 +18199,7 @@
       </c>
       <c r="I228" s="2" t="inlineStr">
         <is>
-          <t>finales, angustia, muerte, fin de la historia, éxito</t>
+          <t>Tiempo, Miedo y vulnerabilidad, Muerte y duelo, Política y actualidad, Emociones y afectos</t>
         </is>
       </c>
       <c r="J228" s="2" t="inlineStr"/>
@@ -18286,7 +18286,7 @@
       </c>
       <c r="I229" s="2" t="inlineStr">
         <is>
-          <t>finales, angustia, muerte, fin de la historia, éxito</t>
+          <t>Tiempo, Miedo y vulnerabilidad, Muerte y duelo, Política y actualidad, Emociones y afectos</t>
         </is>
       </c>
       <c r="J229" s="2" t="inlineStr"/>
@@ -18373,7 +18373,7 @@
       </c>
       <c r="I230" s="2" t="inlineStr">
         <is>
-          <t>finales, angustia, muerte, fin de la historia, éxito</t>
+          <t>Tiempo, Miedo y vulnerabilidad, Muerte y duelo, Política y actualidad, Emociones y afectos</t>
         </is>
       </c>
       <c r="J230" s="2" t="inlineStr"/>
@@ -18446,7 +18446,7 @@
       </c>
       <c r="I231" s="2" t="inlineStr">
         <is>
-          <t>finales, angustia, muerte, fin de la historia, éxito</t>
+          <t>Tiempo, Miedo y vulnerabilidad, Muerte y duelo, Política y actualidad, Emociones y afectos</t>
         </is>
       </c>
       <c r="J231" s="2" t="inlineStr"/>
@@ -18515,7 +18515,7 @@
       </c>
       <c r="I232" s="2" t="inlineStr">
         <is>
-          <t>finales, angustia, muerte, fin de la historia, éxito</t>
+          <t>Tiempo, Miedo y vulnerabilidad, Muerte y duelo, Política y actualidad, Emociones y afectos</t>
         </is>
       </c>
       <c r="J232" s="2" t="inlineStr"/>
@@ -18588,7 +18588,7 @@
       </c>
       <c r="I233" s="2" t="inlineStr">
         <is>
-          <t>finales, angustia, muerte, fin de la historia, éxito</t>
+          <t>Tiempo, Miedo y vulnerabilidad, Muerte y duelo, Política y actualidad, Emociones y afectos</t>
         </is>
       </c>
       <c r="J233" s="2" t="inlineStr"/>
@@ -18661,7 +18661,7 @@
       </c>
       <c r="I234" s="2" t="inlineStr">
         <is>
-          <t>finales, angustia, muerte, fin de la historia, éxito</t>
+          <t>Tiempo, Miedo y vulnerabilidad, Muerte y duelo, Política y actualidad, Emociones y afectos</t>
         </is>
       </c>
       <c r="J234" s="2" t="inlineStr"/>
@@ -18730,7 +18730,7 @@
       </c>
       <c r="I235" s="2" t="inlineStr">
         <is>
-          <t>finales, angustia, muerte, fin de la historia, éxito</t>
+          <t>Tiempo, Miedo y vulnerabilidad, Muerte y duelo, Política y actualidad, Emociones y afectos</t>
         </is>
       </c>
       <c r="J235" s="2" t="inlineStr"/>
@@ -18803,7 +18803,7 @@
       </c>
       <c r="I236" s="2" t="inlineStr">
         <is>
-          <t>fatiga, pereza, trabajo, agotamiento emocional, Barthes</t>
+          <t>Emociones y afectos, Capitalismo, trabajo y economía, Monográfico de autor/a</t>
         </is>
       </c>
       <c r="J236" s="2" t="inlineStr"/>
@@ -18890,7 +18890,7 @@
       </c>
       <c r="I237" s="2" t="inlineStr">
         <is>
-          <t>fatiga, pereza, trabajo, agotamiento emocional, Barthes</t>
+          <t>Emociones y afectos, Capitalismo, trabajo y economía, Monográfico de autor/a</t>
         </is>
       </c>
       <c r="J237" s="2" t="inlineStr"/>
@@ -18977,7 +18977,7 @@
       </c>
       <c r="I238" s="2" t="inlineStr">
         <is>
-          <t>fatiga, pereza, trabajo, agotamiento emocional, Barthes</t>
+          <t>Emociones y afectos, Capitalismo, trabajo y economía, Monográfico de autor/a</t>
         </is>
       </c>
       <c r="J238" s="2" t="inlineStr"/>
@@ -19050,7 +19050,7 @@
       </c>
       <c r="I239" s="2" t="inlineStr">
         <is>
-          <t>fatiga, pereza, trabajo, agotamiento emocional, Barthes</t>
+          <t>Emociones y afectos, Capitalismo, trabajo y economía, Monográfico de autor/a</t>
         </is>
       </c>
       <c r="J239" s="2" t="inlineStr"/>
@@ -19137,7 +19137,7 @@
       </c>
       <c r="I240" s="2" t="inlineStr">
         <is>
-          <t>fatiga, pereza, trabajo, agotamiento emocional, Barthes</t>
+          <t>Emociones y afectos, Capitalismo, trabajo y economía, Monográfico de autor/a</t>
         </is>
       </c>
       <c r="J240" s="2" t="inlineStr"/>
@@ -19206,7 +19206,7 @@
       </c>
       <c r="I241" s="2" t="inlineStr">
         <is>
-          <t>fatiga, pereza, trabajo, agotamiento emocional, Barthes</t>
+          <t>Emociones y afectos, Capitalismo, trabajo y economía, Monográfico de autor/a</t>
         </is>
       </c>
       <c r="J241" s="2" t="inlineStr"/>
@@ -19275,7 +19275,7 @@
       </c>
       <c r="I242" s="2" t="inlineStr">
         <is>
-          <t>fatiga, pereza, trabajo, agotamiento emocional, Barthes</t>
+          <t>Emociones y afectos, Capitalismo, trabajo y economía, Monográfico de autor/a</t>
         </is>
       </c>
       <c r="J242" s="2" t="inlineStr"/>
@@ -19348,7 +19348,7 @@
       </c>
       <c r="I243" s="2" t="inlineStr">
         <is>
-          <t>imagen, intimidad, redes sociales, influencers, ética de la mirada</t>
+          <t>Fotografía e imagen, Amor y vínculos afectivos, Medios, redes e internet, Ética y moral</t>
         </is>
       </c>
       <c r="J243" s="2" t="inlineStr"/>
@@ -19431,7 +19431,7 @@
       </c>
       <c r="I244" s="2" t="inlineStr">
         <is>
-          <t>imagen, intimidad, redes sociales, influencers, ética de la mirada</t>
+          <t>Fotografía e imagen, Amor y vínculos afectivos, Medios, redes e internet, Ética y moral</t>
         </is>
       </c>
       <c r="J244" s="2" t="inlineStr"/>
@@ -19504,7 +19504,7 @@
       </c>
       <c r="I245" s="2" t="inlineStr">
         <is>
-          <t>imagen, intimidad, redes sociales, influencers, ética de la mirada</t>
+          <t>Fotografía e imagen, Amor y vínculos afectivos, Medios, redes e internet, Ética y moral</t>
         </is>
       </c>
       <c r="J245" s="2" t="inlineStr"/>
@@ -19577,7 +19577,7 @@
       </c>
       <c r="I246" s="2" t="inlineStr">
         <is>
-          <t>imagen, intimidad, redes sociales, influencers, ética de la mirada</t>
+          <t>Fotografía e imagen, Amor y vínculos afectivos, Medios, redes e internet, Ética y moral</t>
         </is>
       </c>
       <c r="J246" s="2" t="inlineStr"/>
@@ -19664,7 +19664,7 @@
       </c>
       <c r="I247" s="2" t="inlineStr">
         <is>
-          <t>herencia, duelo, clase social, posteridad</t>
+          <t>Memoria e historia, Muerte y duelo, Identidad y clase social</t>
         </is>
       </c>
       <c r="J247" s="2" t="inlineStr"/>
@@ -19751,7 +19751,7 @@
       </c>
       <c r="I248" s="2" t="inlineStr">
         <is>
-          <t>herencia, duelo, clase social, posteridad</t>
+          <t>Memoria e historia, Muerte y duelo, Identidad y clase social</t>
         </is>
       </c>
       <c r="J248" s="2" t="inlineStr"/>
@@ -19838,7 +19838,7 @@
       </c>
       <c r="I249" s="2" t="inlineStr">
         <is>
-          <t>herencia, duelo, clase social, posteridad</t>
+          <t>Memoria e historia, Muerte y duelo, Identidad y clase social</t>
         </is>
       </c>
       <c r="J249" s="2" t="inlineStr"/>
@@ -19921,7 +19921,7 @@
       </c>
       <c r="I250" s="2" t="inlineStr">
         <is>
-          <t>herencia, duelo, clase social, posteridad</t>
+          <t>Memoria e historia, Muerte y duelo, Identidad y clase social</t>
         </is>
       </c>
       <c r="J250" s="2" t="inlineStr"/>
@@ -19990,7 +19990,7 @@
       </c>
       <c r="I251" s="2" t="inlineStr">
         <is>
-          <t>herencia, duelo, clase social, posteridad</t>
+          <t>Memoria e historia, Muerte y duelo, Identidad y clase social</t>
         </is>
       </c>
       <c r="J251" s="2" t="inlineStr"/>
@@ -20059,7 +20059,7 @@
       </c>
       <c r="I252" s="2" t="inlineStr">
         <is>
-          <t>herencia, duelo, clase social, posteridad</t>
+          <t>Memoria e historia, Muerte y duelo, Identidad y clase social</t>
         </is>
       </c>
       <c r="J252" s="2" t="inlineStr"/>
@@ -20128,7 +20128,7 @@
       </c>
       <c r="I253" s="2" t="inlineStr">
         <is>
-          <t>herencia, duelo, clase social, posteridad</t>
+          <t>Memoria e historia, Muerte y duelo, Identidad y clase social</t>
         </is>
       </c>
       <c r="J253" s="2" t="inlineStr"/>
@@ -20197,7 +20197,7 @@
       </c>
       <c r="I254" s="2" t="inlineStr">
         <is>
-          <t>herencia, duelo, clase social, posteridad</t>
+          <t>Memoria e historia, Muerte y duelo, Identidad y clase social</t>
         </is>
       </c>
       <c r="J254" s="2" t="inlineStr"/>
@@ -20266,7 +20266,7 @@
       </c>
       <c r="I255" s="2" t="inlineStr">
         <is>
-          <t>herencia, duelo, clase social, posteridad</t>
+          <t>Memoria e historia, Muerte y duelo, Identidad y clase social</t>
         </is>
       </c>
       <c r="J255" s="2" t="inlineStr"/>
@@ -20339,7 +20339,7 @@
       </c>
       <c r="I256" s="2" t="inlineStr">
         <is>
-          <t>maternidad, aborto, abandono, arrepentimiento, mito</t>
+          <t>Familia y maternidad, Feminismo y género, Amor y vínculos afectivos, Emociones y afectos, Mito y relato</t>
         </is>
       </c>
       <c r="J256" s="2" t="inlineStr"/>
@@ -20422,7 +20422,7 @@
       </c>
       <c r="I257" s="2" t="inlineStr">
         <is>
-          <t>maternidad, aborto, abandono, arrepentimiento, mito</t>
+          <t>Familia y maternidad, Feminismo y género, Amor y vínculos afectivos, Emociones y afectos, Mito y relato</t>
         </is>
       </c>
       <c r="J257" s="2" t="inlineStr"/>
@@ -20495,7 +20495,7 @@
       </c>
       <c r="I258" s="2" t="inlineStr">
         <is>
-          <t>maternidad, aborto, abandono, arrepentimiento, mito</t>
+          <t>Familia y maternidad, Feminismo y género, Amor y vínculos afectivos, Emociones y afectos, Mito y relato</t>
         </is>
       </c>
       <c r="J258" s="2" t="inlineStr"/>
@@ -20572,7 +20572,7 @@
       </c>
       <c r="I259" s="2" t="inlineStr">
         <is>
-          <t>maternidad, aborto, abandono, arrepentimiento, mito</t>
+          <t>Familia y maternidad, Feminismo y género, Amor y vínculos afectivos, Emociones y afectos, Mito y relato</t>
         </is>
       </c>
       <c r="J259" s="2" t="inlineStr"/>
@@ -20659,7 +20659,7 @@
       </c>
       <c r="I260" s="2" t="inlineStr">
         <is>
-          <t>maternidad, aborto, abandono, arrepentimiento, mito</t>
+          <t>Familia y maternidad, Feminismo y género, Amor y vínculos afectivos, Emociones y afectos, Mito y relato</t>
         </is>
       </c>
       <c r="J260" s="2" t="inlineStr"/>
@@ -20750,7 +20750,7 @@
       </c>
       <c r="I261" s="2" t="inlineStr">
         <is>
-          <t>maternidad, aborto, abandono, arrepentimiento, mito</t>
+          <t>Familia y maternidad, Feminismo y género, Amor y vínculos afectivos, Emociones y afectos, Mito y relato</t>
         </is>
       </c>
       <c r="J261" s="2" t="inlineStr"/>
@@ -20837,7 +20837,7 @@
       </c>
       <c r="I262" s="2" t="inlineStr">
         <is>
-          <t>mirar atrás, memoria, tiempo, arrepentimiento, mito</t>
+          <t>Memoria e historia, Tiempo, Emociones y afectos, Mito y relato</t>
         </is>
       </c>
       <c r="J262" s="2" t="inlineStr"/>
@@ -20906,7 +20906,7 @@
       </c>
       <c r="I263" s="2" t="inlineStr">
         <is>
-          <t>mirar atrás, memoria, tiempo, arrepentimiento, mito</t>
+          <t>Memoria e historia, Tiempo, Emociones y afectos, Mito y relato</t>
         </is>
       </c>
       <c r="J263" s="2" t="inlineStr"/>
@@ -20979,7 +20979,7 @@
       </c>
       <c r="I264" s="2" t="inlineStr">
         <is>
-          <t>mirar atrás, memoria, tiempo, arrepentimiento, mito</t>
+          <t>Memoria e historia, Tiempo, Emociones y afectos, Mito y relato</t>
         </is>
       </c>
       <c r="J264" s="2" t="inlineStr"/>
@@ -21048,7 +21048,7 @@
       </c>
       <c r="I265" s="2" t="inlineStr">
         <is>
-          <t>mirar atrás, memoria, tiempo, arrepentimiento, mito</t>
+          <t>Memoria e historia, Tiempo, Emociones y afectos, Mito y relato</t>
         </is>
       </c>
       <c r="J265" s="2" t="inlineStr"/>
@@ -21117,7 +21117,7 @@
       </c>
       <c r="I266" s="2" t="inlineStr">
         <is>
-          <t>mirar atrás, memoria, tiempo, arrepentimiento, mito</t>
+          <t>Memoria e historia, Tiempo, Emociones y afectos, Mito y relato</t>
         </is>
       </c>
       <c r="J266" s="2" t="inlineStr"/>
@@ -21186,7 +21186,7 @@
       </c>
       <c r="I267" s="2" t="inlineStr">
         <is>
-          <t>mirar atrás, memoria, tiempo, arrepentimiento, mito</t>
+          <t>Memoria e historia, Tiempo, Emociones y afectos, Mito y relato</t>
         </is>
       </c>
       <c r="J267" s="2" t="inlineStr"/>
@@ -21263,7 +21263,7 @@
       </c>
       <c r="I268" s="2" t="inlineStr">
         <is>
-          <t>memoria histórica, olvido, franquismo, memoria colectiva</t>
+          <t>Memoria e historia</t>
         </is>
       </c>
       <c r="J268" s="2" t="inlineStr"/>
@@ -21346,7 +21346,7 @@
       </c>
       <c r="I269" s="2" t="inlineStr">
         <is>
-          <t>memoria histórica, olvido, franquismo, memoria colectiva</t>
+          <t>Memoria e historia</t>
         </is>
       </c>
       <c r="J269" s="2" t="inlineStr"/>
@@ -21427,7 +21427,7 @@
       </c>
       <c r="I270" s="2" t="inlineStr">
         <is>
-          <t>memoria histórica, olvido, franquismo, memoria colectiva</t>
+          <t>Memoria e historia</t>
         </is>
       </c>
       <c r="J270" s="2" t="inlineStr"/>
@@ -21504,7 +21504,7 @@
       </c>
       <c r="I271" s="2" t="inlineStr">
         <is>
-          <t>memoria histórica, olvido, franquismo, memoria colectiva</t>
+          <t>Memoria e historia</t>
         </is>
       </c>
       <c r="J271" s="2" t="inlineStr"/>
@@ -21581,7 +21581,7 @@
       </c>
       <c r="I272" s="2" t="inlineStr">
         <is>
-          <t>tabú, transgresión, canibalismo, virginidad, ruralidad queer</t>
+          <t>Ética y moral, Violencia y daño, Sexualidad y disidencia sexual, Ruralidad y territorio</t>
         </is>
       </c>
       <c r="J272" s="2" t="inlineStr"/>
@@ -21668,7 +21668,7 @@
       </c>
       <c r="I273" s="2" t="inlineStr">
         <is>
-          <t>tabú, transgresión, canibalismo, virginidad, ruralidad queer</t>
+          <t>Ética y moral, Violencia y daño, Sexualidad y disidencia sexual, Ruralidad y territorio</t>
         </is>
       </c>
       <c r="J273" s="2" t="inlineStr"/>
@@ -21737,7 +21737,7 @@
       </c>
       <c r="I274" s="2" t="inlineStr">
         <is>
-          <t>tabú, transgresión, canibalismo, virginidad, ruralidad queer</t>
+          <t>Ética y moral, Violencia y daño, Sexualidad y disidencia sexual, Ruralidad y territorio</t>
         </is>
       </c>
       <c r="J274" s="2" t="inlineStr"/>
@@ -21806,7 +21806,7 @@
       </c>
       <c r="I275" s="2" t="inlineStr">
         <is>
-          <t>tabú, transgresión, canibalismo, virginidad, ruralidad queer</t>
+          <t>Ética y moral, Violencia y daño, Sexualidad y disidencia sexual, Ruralidad y territorio</t>
         </is>
       </c>
       <c r="J275" s="2" t="inlineStr"/>
@@ -21875,7 +21875,7 @@
       </c>
       <c r="I276" s="2" t="inlineStr">
         <is>
-          <t>tabú, transgresión, canibalismo, virginidad, ruralidad queer</t>
+          <t>Ética y moral, Violencia y daño, Sexualidad y disidencia sexual, Ruralidad y territorio</t>
         </is>
       </c>
       <c r="J276" s="2" t="inlineStr"/>
@@ -21944,7 +21944,7 @@
       </c>
       <c r="I277" s="2" t="inlineStr">
         <is>
-          <t>tabú, transgresión, canibalismo, virginidad, ruralidad queer</t>
+          <t>Ética y moral, Violencia y daño, Sexualidad y disidencia sexual, Ruralidad y territorio</t>
         </is>
       </c>
       <c r="J277" s="2" t="inlineStr"/>
@@ -22021,7 +22021,7 @@
       </c>
       <c r="I278" s="2" t="inlineStr">
         <is>
-          <t>orientación, fenomenología queer, norte, orientalismo</t>
+          <t>Sexualidad y disidencia sexual, Espacio, límite y frontera, Colonialismo y poscolonialismo</t>
         </is>
       </c>
       <c r="J278" s="2" t="inlineStr"/>
@@ -22112,7 +22112,7 @@
       </c>
       <c r="I279" s="2" t="inlineStr">
         <is>
-          <t>orientación, fenomenología queer, norte, orientalismo</t>
+          <t>Sexualidad y disidencia sexual, Espacio, límite y frontera, Colonialismo y poscolonialismo</t>
         </is>
       </c>
       <c r="J279" s="2" t="inlineStr"/>
@@ -22193,7 +22193,7 @@
       </c>
       <c r="I280" s="2" t="inlineStr">
         <is>
-          <t>orientación, fenomenología queer, norte, orientalismo</t>
+          <t>Sexualidad y disidencia sexual, Espacio, límite y frontera, Colonialismo y poscolonialismo</t>
         </is>
       </c>
       <c r="J280" s="2" t="inlineStr"/>
@@ -22276,7 +22276,7 @@
       </c>
       <c r="I281" s="2" t="inlineStr">
         <is>
-          <t>orientación, fenomenología queer, norte, orientalismo</t>
+          <t>Sexualidad y disidencia sexual, Espacio, límite y frontera, Colonialismo y poscolonialismo</t>
         </is>
       </c>
       <c r="J281" s="2" t="inlineStr"/>
@@ -22349,7 +22349,7 @@
       </c>
       <c r="I282" s="2" t="inlineStr">
         <is>
-          <t>orientación, fenomenología queer, norte, orientalismo</t>
+          <t>Sexualidad y disidencia sexual, Espacio, límite y frontera, Colonialismo y poscolonialismo</t>
         </is>
       </c>
       <c r="J282" s="2" t="inlineStr"/>
@@ -22418,7 +22418,7 @@
       </c>
       <c r="I283" s="2" t="inlineStr">
         <is>
-          <t>orientación, fenomenología queer, norte, orientalismo</t>
+          <t>Sexualidad y disidencia sexual, Espacio, límite y frontera, Colonialismo y poscolonialismo</t>
         </is>
       </c>
       <c r="J283" s="2" t="inlineStr"/>
@@ -22491,7 +22491,7 @@
       </c>
       <c r="I284" s="2" t="inlineStr">
         <is>
-          <t>inercia, amor, razones, existencia</t>
+          <t>Existencia y contingencia, Amor y vínculos afectivos, Filosofía y epistemología</t>
         </is>
       </c>
       <c r="J284" s="2" t="inlineStr"/>
@@ -22578,7 +22578,7 @@
       </c>
       <c r="I285" s="2" t="inlineStr">
         <is>
-          <t>inercia, amor, razones, existencia</t>
+          <t>Existencia y contingencia, Amor y vínculos afectivos, Filosofía y epistemología</t>
         </is>
       </c>
       <c r="J285" s="2" t="inlineStr"/>
@@ -22669,7 +22669,7 @@
       </c>
       <c r="I286" s="2" t="inlineStr">
         <is>
-          <t>inercia, amor, razones, existencia</t>
+          <t>Existencia y contingencia, Amor y vínculos afectivos, Filosofía y epistemología</t>
         </is>
       </c>
       <c r="J286" s="2" t="inlineStr"/>
@@ -22756,7 +22756,7 @@
       </c>
       <c r="I287" s="2" t="inlineStr">
         <is>
-          <t>inercia, amor, razones, existencia</t>
+          <t>Existencia y contingencia, Amor y vínculos afectivos, Filosofía y epistemología</t>
         </is>
       </c>
       <c r="J287" s="2" t="inlineStr"/>
@@ -22833,7 +22833,7 @@
       </c>
       <c r="I288" s="2" t="inlineStr">
         <is>
-          <t>inercia, amor, razones, existencia</t>
+          <t>Existencia y contingencia, Amor y vínculos afectivos, Filosofía y epistemología</t>
         </is>
       </c>
       <c r="J288" s="2" t="inlineStr"/>
@@ -22914,7 +22914,7 @@
       </c>
       <c r="I289" s="2" t="inlineStr">
         <is>
-          <t>dependencia, competición, ser segundo, jerarquía afectiva</t>
+          <t>Amor y vínculos afectivos, Emociones y afectos, Feminismo y género</t>
         </is>
       </c>
       <c r="J289" s="2" t="inlineStr"/>
@@ -23001,7 +23001,7 @@
       </c>
       <c r="I290" s="2" t="inlineStr">
         <is>
-          <t>dependencia, competición, ser segundo, jerarquía afectiva</t>
+          <t>Amor y vínculos afectivos, Emociones y afectos, Feminismo y género</t>
         </is>
       </c>
       <c r="J290" s="2" t="inlineStr"/>
@@ -23088,7 +23088,7 @@
       </c>
       <c r="I291" s="2" t="inlineStr">
         <is>
-          <t>dependencia, competición, ser segundo, jerarquía afectiva</t>
+          <t>Amor y vínculos afectivos, Emociones y afectos, Feminismo y género</t>
         </is>
       </c>
       <c r="J291" s="2" t="inlineStr"/>
@@ -23175,7 +23175,7 @@
       </c>
       <c r="I292" s="2" t="inlineStr">
         <is>
-          <t>dependencia, competición, ser segundo, jerarquía afectiva</t>
+          <t>Amor y vínculos afectivos, Emociones y afectos, Feminismo y género</t>
         </is>
       </c>
       <c r="J292" s="2" t="inlineStr"/>
@@ -23256,7 +23256,7 @@
       </c>
       <c r="I293" s="2" t="inlineStr">
         <is>
-          <t>dependencia, competición, ser segundo, jerarquía afectiva</t>
+          <t>Amor y vínculos afectivos, Emociones y afectos, Feminismo y género</t>
         </is>
       </c>
       <c r="J293" s="2" t="inlineStr"/>
@@ -23347,7 +23347,7 @@
       </c>
       <c r="I294" s="2" t="inlineStr">
         <is>
-          <t>amor, lenguaje, Barthes, afasia</t>
+          <t>Amor y vínculos afectivos, Lenguaje y escritura, Monográfico de autor/a</t>
         </is>
       </c>
       <c r="J294" s="2" t="inlineStr"/>
@@ -23428,7 +23428,7 @@
       </c>
       <c r="I295" s="2" t="inlineStr">
         <is>
-          <t>amor, lenguaje, Barthes, afasia</t>
+          <t>Amor y vínculos afectivos, Lenguaje y escritura, Monográfico de autor/a</t>
         </is>
       </c>
       <c r="J295" s="2" t="inlineStr"/>
@@ -23515,7 +23515,7 @@
       </c>
       <c r="I296" s="2" t="inlineStr">
         <is>
-          <t>amor, lenguaje, Barthes, afasia</t>
+          <t>Amor y vínculos afectivos, Lenguaje y escritura, Monográfico de autor/a</t>
         </is>
       </c>
       <c r="J296" s="2" t="inlineStr"/>
@@ -23602,7 +23602,7 @@
       </c>
       <c r="I297" s="2" t="inlineStr">
         <is>
-          <t>amor, lenguaje, Barthes, afasia</t>
+          <t>Amor y vínculos afectivos, Lenguaje y escritura, Monográfico de autor/a</t>
         </is>
       </c>
       <c r="J297" s="2" t="inlineStr"/>
@@ -23689,7 +23689,7 @@
       </c>
       <c r="I298" s="2" t="inlineStr">
         <is>
-          <t>amor, lenguaje, Barthes, afasia</t>
+          <t>Amor y vínculos afectivos, Lenguaje y escritura, Monográfico de autor/a</t>
         </is>
       </c>
       <c r="J298" s="2" t="inlineStr"/>
@@ -23776,7 +23776,7 @@
       </c>
       <c r="I299" s="2" t="inlineStr">
         <is>
-          <t>Gaza, violencia, mal, decolonial, ética</t>
+          <t>Política y actualidad, Violencia y daño, Ética y moral, Colonialismo y poscolonialismo</t>
         </is>
       </c>
       <c r="J299" s="2" t="inlineStr"/>
@@ -23853,7 +23853,7 @@
       </c>
       <c r="I300" s="2" t="inlineStr">
         <is>
-          <t>Gaza, violencia, mal, decolonial, ética</t>
+          <t>Política y actualidad, Violencia y daño, Ética y moral, Colonialismo y poscolonialismo</t>
         </is>
       </c>
       <c r="J300" s="2" t="inlineStr"/>
@@ -23922,7 +23922,7 @@
       </c>
       <c r="I301" s="2" t="inlineStr">
         <is>
-          <t>Gaza, violencia, mal, decolonial, ética</t>
+          <t>Política y actualidad, Violencia y daño, Ética y moral, Colonialismo y poscolonialismo</t>
         </is>
       </c>
       <c r="J301" s="2" t="inlineStr"/>
@@ -23991,7 +23991,7 @@
       </c>
       <c r="I302" s="2" t="inlineStr">
         <is>
-          <t>Gaza, violencia, mal, decolonial, ética</t>
+          <t>Política y actualidad, Violencia y daño, Ética y moral, Colonialismo y poscolonialismo</t>
         </is>
       </c>
       <c r="J302" s="2" t="inlineStr"/>
@@ -24060,7 +24060,7 @@
       </c>
       <c r="I303" s="2" t="inlineStr">
         <is>
-          <t>Gaza, violencia, mal, decolonial, ética</t>
+          <t>Política y actualidad, Violencia y daño, Ética y moral, Colonialismo y poscolonialismo</t>
         </is>
       </c>
       <c r="J303" s="2" t="inlineStr"/>
@@ -24129,7 +24129,7 @@
       </c>
       <c r="I304" s="2" t="inlineStr">
         <is>
-          <t>Gaza, violencia, mal, decolonial, ética</t>
+          <t>Política y actualidad, Violencia y daño, Ética y moral, Colonialismo y poscolonialismo</t>
         </is>
       </c>
       <c r="J304" s="2" t="inlineStr"/>
@@ -24202,7 +24202,7 @@
       </c>
       <c r="I305" s="2" t="inlineStr">
         <is>
-          <t>matrimonio, mito, violencia sexual, herencia, miedo, episodio con invitada</t>
+          <t>Amor y vínculos afectivos, Mito y relato, Violencia y daño, Memoria e historia, Miedo y vulnerabilidad, Formato especial y evento</t>
         </is>
       </c>
       <c r="J305" s="2" t="inlineStr"/>
@@ -24283,7 +24283,7 @@
       </c>
       <c r="I306" s="2" t="inlineStr">
         <is>
-          <t>matrimonio, mito, violencia sexual, herencia, miedo, episodio con invitada</t>
+          <t>Amor y vínculos afectivos, Mito y relato, Violencia y daño, Memoria e historia, Miedo y vulnerabilidad, Formato especial y evento</t>
         </is>
       </c>
       <c r="J306" s="2" t="inlineStr"/>
@@ -24370,7 +24370,7 @@
       </c>
       <c r="I307" s="2" t="inlineStr">
         <is>
-          <t>matrimonio, mito, violencia sexual, herencia, miedo, episodio con invitada</t>
+          <t>Amor y vínculos afectivos, Mito y relato, Violencia y daño, Memoria e historia, Miedo y vulnerabilidad, Formato especial y evento</t>
         </is>
       </c>
       <c r="J307" s="2" t="inlineStr"/>
@@ -24451,7 +24451,7 @@
       </c>
       <c r="I308" s="2" t="inlineStr">
         <is>
-          <t>matrimonio, mito, violencia sexual, herencia, miedo, episodio con invitada</t>
+          <t>Amor y vínculos afectivos, Mito y relato, Violencia y daño, Memoria e historia, Miedo y vulnerabilidad, Formato especial y evento</t>
         </is>
       </c>
       <c r="J308" s="2" t="inlineStr"/>
@@ -24532,7 +24532,7 @@
       </c>
       <c r="I309" s="2" t="inlineStr">
         <is>
-          <t>matrimonio, mito, violencia sexual, herencia, miedo, episodio con invitada</t>
+          <t>Amor y vínculos afectivos, Mito y relato, Violencia y daño, Memoria e historia, Miedo y vulnerabilidad, Formato especial y evento</t>
         </is>
       </c>
       <c r="J309" s="2" t="inlineStr"/>
@@ -24619,7 +24619,7 @@
       </c>
       <c r="I310" s="2" t="inlineStr">
         <is>
-          <t>matrimonio, mito, violencia sexual, herencia, miedo, episodio con invitada</t>
+          <t>Amor y vínculos afectivos, Mito y relato, Violencia y daño, Memoria e historia, Miedo y vulnerabilidad, Formato especial y evento</t>
         </is>
       </c>
       <c r="J310" s="2" t="inlineStr"/>
@@ -24696,7 +24696,7 @@
       </c>
       <c r="I311" s="2" t="inlineStr">
         <is>
-          <t>soledad, lenguaje, despoblación, política</t>
+          <t>Soledad y aislamiento, Lenguaje y escritura, Ruralidad y territorio, Política y actualidad</t>
         </is>
       </c>
       <c r="J311" s="2" t="inlineStr"/>
@@ -24783,7 +24783,7 @@
       </c>
       <c r="I312" s="2" t="inlineStr">
         <is>
-          <t>soledad, lenguaje, despoblación, política</t>
+          <t>Soledad y aislamiento, Lenguaje y escritura, Ruralidad y territorio, Política y actualidad</t>
         </is>
       </c>
       <c r="J312" s="2" t="inlineStr"/>
@@ -24864,7 +24864,7 @@
       </c>
       <c r="I313" s="2" t="inlineStr">
         <is>
-          <t>soledad, lenguaje, despoblación, política</t>
+          <t>Soledad y aislamiento, Lenguaje y escritura, Ruralidad y territorio, Política y actualidad</t>
         </is>
       </c>
       <c r="J313" s="2" t="inlineStr"/>
@@ -24945,7 +24945,7 @@
       </c>
       <c r="I314" s="2" t="inlineStr">
         <is>
-          <t>soledad, lenguaje, despoblación, política</t>
+          <t>Soledad y aislamiento, Lenguaje y escritura, Ruralidad y territorio, Política y actualidad</t>
         </is>
       </c>
       <c r="J314" s="2" t="inlineStr"/>
@@ -25026,7 +25026,7 @@
       </c>
       <c r="I315" s="2" t="inlineStr">
         <is>
-          <t>pérdida, olvido, memoria, Barthes</t>
+          <t>Muerte y duelo, Memoria e historia, Monográfico de autor/a</t>
         </is>
       </c>
       <c r="J315" s="2" t="inlineStr"/>
@@ -25107,7 +25107,7 @@
       </c>
       <c r="I316" s="2" t="inlineStr">
         <is>
-          <t>pérdida, olvido, memoria, Barthes</t>
+          <t>Muerte y duelo, Memoria e historia, Monográfico de autor/a</t>
         </is>
       </c>
       <c r="J316" s="2" t="inlineStr"/>
@@ -25190,7 +25190,7 @@
       </c>
       <c r="I317" s="2" t="inlineStr">
         <is>
-          <t>pérdida, olvido, memoria, Barthes</t>
+          <t>Muerte y duelo, Memoria e historia, Monográfico de autor/a</t>
         </is>
       </c>
       <c r="J317" s="2" t="inlineStr"/>
@@ -25263,7 +25263,7 @@
       </c>
       <c r="I318" s="2" t="inlineStr">
         <is>
-          <t>pérdida, olvido, memoria, Barthes</t>
+          <t>Muerte y duelo, Memoria e historia, Monográfico de autor/a</t>
         </is>
       </c>
       <c r="J318" s="2" t="inlineStr"/>
@@ -25336,7 +25336,7 @@
       </c>
       <c r="I319" s="2" t="inlineStr">
         <is>
-          <t>pérdida, olvido, memoria, Barthes</t>
+          <t>Muerte y duelo, Memoria e historia, Monográfico de autor/a</t>
         </is>
       </c>
       <c r="J319" s="2" t="inlineStr"/>
@@ -25405,7 +25405,7 @@
       </c>
       <c r="I320" s="2" t="inlineStr">
         <is>
-          <t>pérdida, olvido, memoria, Barthes</t>
+          <t>Muerte y duelo, Memoria e historia, Monográfico de autor/a</t>
         </is>
       </c>
       <c r="J320" s="2" t="inlineStr"/>
@@ -25474,7 +25474,7 @@
       </c>
       <c r="I321" s="2" t="inlineStr">
         <is>
-          <t>pérdida, olvido, memoria, Barthes</t>
+          <t>Muerte y duelo, Memoria e historia, Monográfico de autor/a</t>
         </is>
       </c>
       <c r="J321" s="2" t="inlineStr"/>
@@ -25543,7 +25543,7 @@
       </c>
       <c r="I322" s="2" t="inlineStr">
         <is>
-          <t>pérdida, olvido, memoria, Barthes</t>
+          <t>Muerte y duelo, Memoria e historia, Monográfico de autor/a</t>
         </is>
       </c>
       <c r="J322" s="2" t="inlineStr"/>
@@ -25620,7 +25620,7 @@
       </c>
       <c r="I323" s="2" t="inlineStr">
         <is>
-          <t>caminar, exilio, filosofía, viaje, FIL Guadalajara</t>
+          <t>Viaje y desplazamiento, Filosofía y epistemología, Formato especial y evento</t>
         </is>
       </c>
       <c r="J323" s="2" t="inlineStr"/>
@@ -25707,7 +25707,7 @@
       </c>
       <c r="I324" s="2" t="inlineStr">
         <is>
-          <t>caminar, exilio, filosofía, viaje, FIL Guadalajara</t>
+          <t>Viaje y desplazamiento, Filosofía y epistemología, Formato especial y evento</t>
         </is>
       </c>
       <c r="J324" s="2" t="inlineStr"/>
@@ -25788,7 +25788,7 @@
       </c>
       <c r="I325" s="2" t="inlineStr">
         <is>
-          <t>caminar, exilio, filosofía, viaje, FIL Guadalajara</t>
+          <t>Viaje y desplazamiento, Filosofía y epistemología, Formato especial y evento</t>
         </is>
       </c>
       <c r="J325" s="2" t="inlineStr"/>
@@ -25871,7 +25871,7 @@
       </c>
       <c r="I326" s="2" t="inlineStr">
         <is>
-          <t>caminar, exilio, filosofía, viaje, FIL Guadalajara</t>
+          <t>Viaje y desplazamiento, Filosofía y epistemología, Formato especial y evento</t>
         </is>
       </c>
       <c r="J326" s="2" t="inlineStr"/>
@@ -25940,7 +25940,7 @@
       </c>
       <c r="I327" s="2" t="inlineStr">
         <is>
-          <t>caminar, exilio, filosofía, viaje, FIL Guadalajara</t>
+          <t>Viaje y desplazamiento, Filosofía y epistemología, Formato especial y evento</t>
         </is>
       </c>
       <c r="J327" s="2" t="inlineStr"/>
@@ -26013,7 +26013,7 @@
       </c>
       <c r="I328" s="2" t="inlineStr">
         <is>
-          <t>caminar, exilio, filosofía, viaje, FIL Guadalajara</t>
+          <t>Viaje y desplazamiento, Filosofía y epistemología, Formato especial y evento</t>
         </is>
       </c>
       <c r="J328" s="2" t="inlineStr"/>
@@ -26090,7 +26090,7 @@
       </c>
       <c r="I329" s="2" t="inlineStr">
         <is>
-          <t>caminar, exilio, filosofía, viaje, FIL Guadalajara</t>
+          <t>Viaje y desplazamiento, Filosofía y epistemología, Formato especial y evento</t>
         </is>
       </c>
       <c r="J329" s="2" t="inlineStr"/>
@@ -26167,7 +26167,7 @@
       </c>
       <c r="I330" s="2" t="inlineStr">
         <is>
-          <t>caminar, exilio, filosofía, viaje, FIL Guadalajara</t>
+          <t>Viaje y desplazamiento, Filosofía y epistemología, Formato especial y evento</t>
         </is>
       </c>
       <c r="J330" s="2" t="inlineStr"/>
@@ -26244,7 +26244,7 @@
       </c>
       <c r="I331" s="2" t="inlineStr">
         <is>
-          <t>caminar, exilio, filosofía, viaje, FIL Guadalajara</t>
+          <t>Viaje y desplazamiento, Filosofía y epistemología, Formato especial y evento</t>
         </is>
       </c>
       <c r="J331" s="2" t="inlineStr"/>
@@ -26321,7 +26321,7 @@
       </c>
       <c r="I332" s="2" t="inlineStr">
         <is>
-          <t>amor contemporáneo, deseo, pareja, FIL Guadalajara, episodio con invitada</t>
+          <t>Amor y vínculos afectivos, Deseo y erotismo, Formato especial y evento</t>
         </is>
       </c>
       <c r="J332" s="2" t="inlineStr"/>
@@ -26408,7 +26408,7 @@
       </c>
       <c r="I333" s="2" t="inlineStr">
         <is>
-          <t>amor contemporáneo, deseo, pareja, FIL Guadalajara, episodio con invitada</t>
+          <t>Amor y vínculos afectivos, Deseo y erotismo, Formato especial y evento</t>
         </is>
       </c>
       <c r="J333" s="2" t="inlineStr"/>
@@ -26477,7 +26477,7 @@
       </c>
       <c r="I334" s="2" t="inlineStr">
         <is>
-          <t>amor contemporáneo, deseo, pareja, FIL Guadalajara, episodio con invitada</t>
+          <t>Amor y vínculos afectivos, Deseo y erotismo, Formato especial y evento</t>
         </is>
       </c>
       <c r="J334" s="2" t="inlineStr"/>
@@ -26546,7 +26546,7 @@
       </c>
       <c r="I335" s="2" t="inlineStr">
         <is>
-          <t>amor contemporáneo, deseo, pareja, FIL Guadalajara, episodio con invitada</t>
+          <t>Amor y vínculos afectivos, Deseo y erotismo, Formato especial y evento</t>
         </is>
       </c>
       <c r="J335" s="2" t="inlineStr"/>
@@ -26615,7 +26615,7 @@
       </c>
       <c r="I336" s="2" t="inlineStr">
         <is>
-          <t>amor contemporáneo, deseo, pareja, FIL Guadalajara, episodio con invitada</t>
+          <t>Amor y vínculos afectivos, Deseo y erotismo, Formato especial y evento</t>
         </is>
       </c>
       <c r="J336" s="2" t="inlineStr"/>
@@ -26688,7 +26688,7 @@
       </c>
       <c r="I337" s="2" t="inlineStr">
         <is>
-          <t>comienzos, tiempo, mito, prehistoria, narración</t>
+          <t>Tiempo, Mito y relato, Narración, ficción y autoficción</t>
         </is>
       </c>
       <c r="J337" s="2" t="inlineStr"/>
@@ -26779,7 +26779,7 @@
       </c>
       <c r="I338" s="2" t="inlineStr">
         <is>
-          <t>comienzos, tiempo, mito, prehistoria, narración</t>
+          <t>Tiempo, Mito y relato, Narración, ficción y autoficción</t>
         </is>
       </c>
       <c r="J338" s="2" t="inlineStr"/>
@@ -26866,7 +26866,7 @@
       </c>
       <c r="I339" s="2" t="inlineStr">
         <is>
-          <t>comienzos, tiempo, mito, prehistoria, narración</t>
+          <t>Tiempo, Mito y relato, Narración, ficción y autoficción</t>
         </is>
       </c>
       <c r="J339" s="2" t="inlineStr"/>
@@ -26947,7 +26947,7 @@
       </c>
       <c r="I340" s="2" t="inlineStr">
         <is>
-          <t>comienzos, tiempo, mito, prehistoria, narración</t>
+          <t>Tiempo, Mito y relato, Narración, ficción y autoficción</t>
         </is>
       </c>
       <c r="J340" s="2" t="inlineStr"/>
@@ -27028,7 +27028,7 @@
       </c>
       <c r="I341" s="2" t="inlineStr">
         <is>
-          <t>comienzos, tiempo, mito, prehistoria, narración</t>
+          <t>Tiempo, Mito y relato, Narración, ficción y autoficción</t>
         </is>
       </c>
       <c r="J341" s="2" t="inlineStr"/>
@@ -27109,7 +27109,7 @@
       </c>
       <c r="I342" s="2" t="inlineStr">
         <is>
-          <t>afuera, lugar social, escritura, ruralidad, adentro/afuera</t>
+          <t>Espacio, límite y frontera, Identidad y clase social, Lenguaje y escritura, Ruralidad y territorio</t>
         </is>
       </c>
       <c r="J342" s="2" t="inlineStr"/>
@@ -27190,7 +27190,7 @@
       </c>
       <c r="I343" s="2" t="inlineStr">
         <is>
-          <t>afuera, lugar social, escritura, ruralidad, adentro/afuera</t>
+          <t>Espacio, límite y frontera, Identidad y clase social, Lenguaje y escritura, Ruralidad y territorio</t>
         </is>
       </c>
       <c r="J343" s="2" t="inlineStr"/>
@@ -27271,7 +27271,7 @@
       </c>
       <c r="I344" s="2" t="inlineStr">
         <is>
-          <t>afuera, lugar social, escritura, ruralidad, adentro/afuera</t>
+          <t>Espacio, límite y frontera, Identidad y clase social, Lenguaje y escritura, Ruralidad y territorio</t>
         </is>
       </c>
       <c r="J344" s="2" t="inlineStr"/>
@@ -27358,7 +27358,7 @@
       </c>
       <c r="I345" s="2" t="inlineStr">
         <is>
-          <t>afuera, lugar social, escritura, ruralidad, adentro/afuera</t>
+          <t>Espacio, límite y frontera, Identidad y clase social, Lenguaje y escritura, Ruralidad y territorio</t>
         </is>
       </c>
       <c r="J345" s="2" t="inlineStr"/>
@@ -27439,7 +27439,7 @@
       </c>
       <c r="I346" s="2" t="inlineStr">
         <is>
-          <t>afuera, lugar social, escritura, ruralidad, adentro/afuera</t>
+          <t>Espacio, límite y frontera, Identidad y clase social, Lenguaje y escritura, Ruralidad y territorio</t>
         </is>
       </c>
       <c r="J346" s="2" t="inlineStr"/>
@@ -27516,7 +27516,7 @@
       </c>
       <c r="I347" s="2" t="inlineStr">
         <is>
-          <t>afuera, lugar social, escritura, ruralidad, adentro/afuera</t>
+          <t>Espacio, límite y frontera, Identidad y clase social, Lenguaje y escritura, Ruralidad y territorio</t>
         </is>
       </c>
       <c r="J347" s="2" t="inlineStr"/>
@@ -27603,7 +27603,7 @@
       </c>
       <c r="I348" s="2" t="inlineStr">
         <is>
-          <t>espera, amor, Barthes, Penélope, tiempo</t>
+          <t>Tiempo, Amor y vínculos afectivos, Monográfico de autor/a, Mito y relato</t>
         </is>
       </c>
       <c r="J348" s="2" t="inlineStr"/>
@@ -27694,7 +27694,7 @@
       </c>
       <c r="I349" s="2" t="inlineStr">
         <is>
-          <t>espera, amor, Barthes, Penélope, tiempo</t>
+          <t>Tiempo, Amor y vínculos afectivos, Monográfico de autor/a, Mito y relato</t>
         </is>
       </c>
       <c r="J349" s="2" t="inlineStr"/>
@@ -27775,7 +27775,7 @@
       </c>
       <c r="I350" s="2" t="inlineStr">
         <is>
-          <t>espera, amor, Barthes, Penélope, tiempo</t>
+          <t>Tiempo, Amor y vínculos afectivos, Monográfico de autor/a, Mito y relato</t>
         </is>
       </c>
       <c r="J350" s="2" t="inlineStr"/>
@@ -27852,7 +27852,7 @@
       </c>
       <c r="I351" s="2" t="inlineStr">
         <is>
-          <t>espera, amor, Barthes, Penélope, tiempo</t>
+          <t>Tiempo, Amor y vínculos afectivos, Monográfico de autor/a, Mito y relato</t>
         </is>
       </c>
       <c r="J351" s="2" t="inlineStr"/>
@@ -27939,7 +27939,7 @@
       </c>
       <c r="I352" s="2" t="inlineStr">
         <is>
-          <t>espera, amor, Barthes, Penélope, tiempo</t>
+          <t>Tiempo, Amor y vínculos afectivos, Monográfico de autor/a, Mito y relato</t>
         </is>
       </c>
       <c r="J352" s="2" t="inlineStr"/>
@@ -28020,7 +28020,7 @@
       </c>
       <c r="I353" s="2" t="inlineStr">
         <is>
-          <t>espera, amor, Barthes, Penélope, tiempo</t>
+          <t>Tiempo, Amor y vínculos afectivos, Monográfico de autor/a, Mito y relato</t>
         </is>
       </c>
       <c r="J353" s="2" t="inlineStr"/>
@@ -28107,7 +28107,7 @@
       </c>
       <c r="I354" s="2" t="inlineStr">
         <is>
-          <t>espera, amor, Barthes, Penélope, tiempo</t>
+          <t>Tiempo, Amor y vínculos afectivos, Monográfico de autor/a, Mito y relato</t>
         </is>
       </c>
       <c r="J354" s="2" t="inlineStr"/>
@@ -28194,7 +28194,7 @@
       </c>
       <c r="I355" s="2" t="inlineStr">
         <is>
-          <t>espera, amor, Barthes, Penélope, tiempo</t>
+          <t>Tiempo, Amor y vínculos afectivos, Monográfico de autor/a, Mito y relato</t>
         </is>
       </c>
       <c r="J355" s="2" t="inlineStr"/>
@@ -28267,7 +28267,7 @@
       </c>
       <c r="I356" s="2" t="inlineStr">
         <is>
-          <t>espera, amor, Barthes, Penélope, tiempo</t>
+          <t>Tiempo, Amor y vínculos afectivos, Monográfico de autor/a, Mito y relato</t>
         </is>
       </c>
       <c r="J356" s="2" t="inlineStr"/>
@@ -28348,7 +28348,7 @@
       </c>
       <c r="I357" s="2" t="inlineStr">
         <is>
-          <t>espera, amor, Barthes, Penélope, tiempo</t>
+          <t>Tiempo, Amor y vínculos afectivos, Monográfico de autor/a, Mito y relato</t>
         </is>
       </c>
       <c r="J357" s="2" t="inlineStr"/>
@@ -28439,7 +28439,7 @@
       </c>
       <c r="I358" s="2" t="inlineStr">
         <is>
-          <t>vacío, España vaciada, espacio, horror vacui, Barthes</t>
+          <t>Existencia y contingencia, Ruralidad y territorio, Espacio, límite y frontera, Arte, Monográfico de autor/a</t>
         </is>
       </c>
       <c r="J358" s="2" t="inlineStr"/>
@@ -28516,7 +28516,7 @@
       </c>
       <c r="I359" s="2" t="inlineStr">
         <is>
-          <t>vacío, España vaciada, espacio, horror vacui, Barthes</t>
+          <t>Existencia y contingencia, Ruralidad y territorio, Espacio, límite y frontera, Arte, Monográfico de autor/a</t>
         </is>
       </c>
       <c r="J359" s="2" t="inlineStr"/>
@@ -28603,7 +28603,7 @@
       </c>
       <c r="I360" s="2" t="inlineStr">
         <is>
-          <t>vacío, España vaciada, espacio, horror vacui, Barthes</t>
+          <t>Existencia y contingencia, Ruralidad y territorio, Espacio, límite y frontera, Arte, Monográfico de autor/a</t>
         </is>
       </c>
       <c r="J360" s="2" t="inlineStr"/>
@@ -28686,7 +28686,7 @@
       </c>
       <c r="I361" s="2" t="inlineStr">
         <is>
-          <t>vacío, España vaciada, espacio, horror vacui, Barthes</t>
+          <t>Existencia y contingencia, Ruralidad y territorio, Espacio, límite y frontera, Arte, Monográfico de autor/a</t>
         </is>
       </c>
       <c r="J361" s="2" t="inlineStr"/>
@@ -28763,7 +28763,7 @@
       </c>
       <c r="I362" s="2" t="inlineStr">
         <is>
-          <t>vacío, España vaciada, espacio, horror vacui, Barthes</t>
+          <t>Existencia y contingencia, Ruralidad y territorio, Espacio, límite y frontera, Arte, Monográfico de autor/a</t>
         </is>
       </c>
       <c r="J362" s="2" t="inlineStr"/>
@@ -28840,7 +28840,7 @@
       </c>
       <c r="I363" s="2" t="inlineStr">
         <is>
-          <t>vacío, España vaciada, espacio, horror vacui, Barthes</t>
+          <t>Existencia y contingencia, Ruralidad y territorio, Espacio, límite y frontera, Arte, Monográfico de autor/a</t>
         </is>
       </c>
       <c r="J363" s="2" t="inlineStr"/>
@@ -28927,7 +28927,7 @@
       </c>
       <c r="I364" s="2" t="inlineStr">
         <is>
-          <t>vacío, España vaciada, espacio, horror vacui, Barthes</t>
+          <t>Existencia y contingencia, Ruralidad y territorio, Espacio, límite y frontera, Arte, Monográfico de autor/a</t>
         </is>
       </c>
       <c r="J364" s="2" t="inlineStr"/>
@@ -29018,7 +29018,7 @@
       </c>
       <c r="I365" s="2" t="inlineStr">
         <is>
-          <t>vacío, España vaciada, espacio, horror vacui, Barthes</t>
+          <t>Existencia y contingencia, Ruralidad y territorio, Espacio, límite y frontera, Arte, Monográfico de autor/a</t>
         </is>
       </c>
       <c r="J365" s="2" t="inlineStr"/>
@@ -29095,7 +29095,7 @@
       </c>
       <c r="I366" s="2" t="inlineStr">
         <is>
-          <t>mirada aérea, paisaje, costa, poesía, fotografía</t>
+          <t>Cuerpo y mirada, Naturaleza y elementos, Espacio, límite y frontera, Literatura y lectura, Fotografía e imagen</t>
         </is>
       </c>
       <c r="J366" s="2" t="inlineStr"/>
@@ -29172,7 +29172,7 @@
       </c>
       <c r="I367" s="2" t="inlineStr">
         <is>
-          <t>mirada aérea, paisaje, costa, poesía, fotografía</t>
+          <t>Cuerpo y mirada, Naturaleza y elementos, Espacio, límite y frontera, Literatura y lectura, Fotografía e imagen</t>
         </is>
       </c>
       <c r="J367" s="2" t="inlineStr"/>
@@ -29245,7 +29245,7 @@
       </c>
       <c r="I368" s="2" t="inlineStr">
         <is>
-          <t>mirada aérea, paisaje, costa, poesía, fotografía</t>
+          <t>Cuerpo y mirada, Naturaleza y elementos, Espacio, límite y frontera, Literatura y lectura, Fotografía e imagen</t>
         </is>
       </c>
       <c r="J368" s="2" t="inlineStr"/>
@@ -29318,7 +29318,7 @@
       </c>
       <c r="I369" s="2" t="inlineStr">
         <is>
-          <t>mirada aérea, paisaje, costa, poesía, fotografía</t>
+          <t>Cuerpo y mirada, Naturaleza y elementos, Espacio, límite y frontera, Literatura y lectura, Fotografía e imagen</t>
         </is>
       </c>
       <c r="J369" s="2" t="inlineStr"/>
@@ -29395,7 +29395,7 @@
       </c>
       <c r="I370" s="2" t="inlineStr">
         <is>
-          <t>mirada aérea, paisaje, costa, poesía, fotografía</t>
+          <t>Cuerpo y mirada, Naturaleza y elementos, Espacio, límite y frontera, Literatura y lectura, Fotografía e imagen</t>
         </is>
       </c>
       <c r="J370" s="2" t="inlineStr"/>
@@ -29476,7 +29476,7 @@
       </c>
       <c r="I371" s="2" t="inlineStr">
         <is>
-          <t>mirada aérea, paisaje, costa, poesía, fotografía</t>
+          <t>Cuerpo y mirada, Naturaleza y elementos, Espacio, límite y frontera, Literatura y lectura, Fotografía e imagen</t>
         </is>
       </c>
       <c r="J371" s="2" t="inlineStr"/>
@@ -29557,7 +29557,7 @@
       </c>
       <c r="I372" s="2" t="inlineStr">
         <is>
-          <t>mirada aérea, paisaje, costa, poesía, fotografía</t>
+          <t>Cuerpo y mirada, Naturaleza y elementos, Espacio, límite y frontera, Literatura y lectura, Fotografía e imagen</t>
         </is>
       </c>
       <c r="J372" s="2" t="inlineStr"/>
@@ -29634,7 +29634,7 @@
       </c>
       <c r="I373" s="2" t="inlineStr">
         <is>
-          <t>mirada aérea, paisaje, costa, poesía, fotografía</t>
+          <t>Cuerpo y mirada, Naturaleza y elementos, Espacio, límite y frontera, Literatura y lectura, Fotografía e imagen</t>
         </is>
       </c>
       <c r="J373" s="2" t="inlineStr"/>
@@ -29707,7 +29707,7 @@
       </c>
       <c r="I374" s="2" t="inlineStr">
         <is>
-          <t>realidad, ficción, desinformación, series, internet</t>
+          <t>Existencia y contingencia, Narración, ficción y autoficción, Medios, redes e internet, Cine y series</t>
         </is>
       </c>
       <c r="J374" s="2" t="inlineStr"/>
@@ -29776,7 +29776,7 @@
       </c>
       <c r="I375" s="2" t="inlineStr">
         <is>
-          <t>realidad, ficción, desinformación, series, internet</t>
+          <t>Existencia y contingencia, Narración, ficción y autoficción, Medios, redes e internet, Cine y series</t>
         </is>
       </c>
       <c r="J375" s="2" t="inlineStr"/>
@@ -29849,7 +29849,7 @@
       </c>
       <c r="I376" s="2" t="inlineStr">
         <is>
-          <t>realidad, ficción, desinformación, series, internet</t>
+          <t>Existencia y contingencia, Narración, ficción y autoficción, Medios, redes e internet, Cine y series</t>
         </is>
       </c>
       <c r="J376" s="2" t="inlineStr"/>
@@ -29930,7 +29930,7 @@
       </c>
       <c r="I377" s="2" t="inlineStr">
         <is>
-          <t>realidad, ficción, desinformación, series, internet</t>
+          <t>Existencia y contingencia, Narración, ficción y autoficción, Medios, redes e internet, Cine y series</t>
         </is>
       </c>
       <c r="J377" s="2" t="inlineStr"/>
@@ -30015,7 +30015,7 @@
       </c>
       <c r="I378" s="2" t="inlineStr">
         <is>
-          <t>realidad, ficción, desinformación, series, internet</t>
+          <t>Existencia y contingencia, Narración, ficción y autoficción, Medios, redes e internet, Cine y series</t>
         </is>
       </c>
       <c r="J378" s="2" t="inlineStr"/>
@@ -30096,7 +30096,7 @@
       </c>
       <c r="I379" s="2" t="inlineStr">
         <is>
-          <t>realidad, ficción, desinformación, series, internet</t>
+          <t>Existencia y contingencia, Narración, ficción y autoficción, Medios, redes e internet, Cine y series</t>
         </is>
       </c>
       <c r="J379" s="2" t="inlineStr"/>
@@ -30183,7 +30183,7 @@
       </c>
       <c r="I380" s="2" t="inlineStr">
         <is>
-          <t>realidad, ficción, desinformación, series, internet</t>
+          <t>Existencia y contingencia, Narración, ficción y autoficción, Medios, redes e internet, Cine y series</t>
         </is>
       </c>
       <c r="J380" s="2" t="inlineStr"/>
@@ -30260,7 +30260,7 @@
       </c>
       <c r="I381" s="2" t="inlineStr">
         <is>
-          <t>realidad, ficción, desinformación, series, internet</t>
+          <t>Existencia y contingencia, Narración, ficción y autoficción, Medios, redes e internet, Cine y series</t>
         </is>
       </c>
       <c r="J381" s="2" t="inlineStr"/>
@@ -30337,7 +30337,7 @@
       </c>
       <c r="I382" s="2" t="inlineStr">
         <is>
-          <t>realidad, ficción, desinformación, series, internet</t>
+          <t>Existencia y contingencia, Narración, ficción y autoficción, Medios, redes e internet, Cine y series</t>
         </is>
       </c>
       <c r="J382" s="2" t="inlineStr"/>
@@ -30410,7 +30410,7 @@
       </c>
       <c r="I383" s="2" t="inlineStr">
         <is>
-          <t>amor no correspondido, rechazo, Barthes, psicología</t>
+          <t>Amor y vínculos afectivos, Monográfico de autor/a, Filosofía y epistemología</t>
         </is>
       </c>
       <c r="J383" s="2" t="inlineStr"/>
@@ -30497,7 +30497,7 @@
       </c>
       <c r="I384" s="2" t="inlineStr">
         <is>
-          <t>amor no correspondido, rechazo, Barthes, psicología</t>
+          <t>Amor y vínculos afectivos, Monográfico de autor/a, Filosofía y epistemología</t>
         </is>
       </c>
       <c r="J384" s="2" t="inlineStr"/>
@@ -30578,7 +30578,7 @@
       </c>
       <c r="I385" s="2" t="inlineStr">
         <is>
-          <t>amor no correspondido, rechazo, Barthes, psicología</t>
+          <t>Amor y vínculos afectivos, Monográfico de autor/a, Filosofía y epistemología</t>
         </is>
       </c>
       <c r="J385" s="2" t="inlineStr"/>
@@ -30665,7 +30665,7 @@
       </c>
       <c r="I386" s="2" t="inlineStr">
         <is>
-          <t>amor no correspondido, rechazo, Barthes, psicología</t>
+          <t>Amor y vínculos afectivos, Monográfico de autor/a, Filosofía y epistemología</t>
         </is>
       </c>
       <c r="J386" s="2" t="inlineStr"/>
@@ -30742,7 +30742,7 @@
       </c>
       <c r="I387" s="2" t="inlineStr">
         <is>
-          <t>amor no correspondido, rechazo, Barthes, psicología</t>
+          <t>Amor y vínculos afectivos, Monográfico de autor/a, Filosofía y epistemología</t>
         </is>
       </c>
       <c r="J387" s="2" t="inlineStr"/>
@@ -30819,7 +30819,7 @@
       </c>
       <c r="I388" s="2" t="inlineStr">
         <is>
-          <t>amor no correspondido, rechazo, Barthes, psicología</t>
+          <t>Amor y vínculos afectivos, Monográfico de autor/a, Filosofía y epistemología</t>
         </is>
       </c>
       <c r="J388" s="2" t="inlineStr"/>
@@ -30896,7 +30896,7 @@
       </c>
       <c r="I389" s="2" t="inlineStr">
         <is>
-          <t>límite, transgresión, liminalidad, frontera, lenguaje</t>
+          <t>Espacio, límite y frontera, Violencia y daño, Lenguaje y escritura</t>
         </is>
       </c>
       <c r="J389" s="2" t="inlineStr"/>
@@ -30981,7 +30981,7 @@
       </c>
       <c r="I390" s="2" t="inlineStr">
         <is>
-          <t>límite, transgresión, liminalidad, frontera, lenguaje</t>
+          <t>Espacio, límite y frontera, Violencia y daño, Lenguaje y escritura</t>
         </is>
       </c>
       <c r="J390" s="2" t="inlineStr"/>
@@ -31068,7 +31068,7 @@
       </c>
       <c r="I391" s="2" t="inlineStr">
         <is>
-          <t>límite, transgresión, liminalidad, frontera, lenguaje</t>
+          <t>Espacio, límite y frontera, Violencia y daño, Lenguaje y escritura</t>
         </is>
       </c>
       <c r="J391" s="2" t="inlineStr"/>
@@ -31155,7 +31155,7 @@
       </c>
       <c r="I392" s="2" t="inlineStr">
         <is>
-          <t>límite, transgresión, liminalidad, frontera, lenguaje</t>
+          <t>Espacio, límite y frontera, Violencia y daño, Lenguaje y escritura</t>
         </is>
       </c>
       <c r="J392" s="2" t="inlineStr"/>
@@ -31238,7 +31238,7 @@
       </c>
       <c r="I393" s="2" t="inlineStr">
         <is>
-          <t>límite, transgresión, liminalidad, frontera, lenguaje</t>
+          <t>Espacio, límite y frontera, Violencia y daño, Lenguaje y escritura</t>
         </is>
       </c>
       <c r="J393" s="2" t="inlineStr"/>
@@ -31315,7 +31315,7 @@
       </c>
       <c r="I394" s="2" t="inlineStr">
         <is>
-          <t>límite, transgresión, liminalidad, frontera, lenguaje</t>
+          <t>Espacio, límite y frontera, Violencia y daño, Lenguaje y escritura</t>
         </is>
       </c>
       <c r="J394" s="2" t="inlineStr"/>
@@ -31402,7 +31402,7 @@
       </c>
       <c r="I395" s="2" t="inlineStr">
         <is>
-          <t>límite, transgresión, liminalidad, frontera, lenguaje</t>
+          <t>Espacio, límite y frontera, Violencia y daño, Lenguaje y escritura</t>
         </is>
       </c>
       <c r="J395" s="2" t="inlineStr"/>
@@ -31479,7 +31479,7 @@
       </c>
       <c r="I396" s="2" t="inlineStr">
         <is>
-          <t>límite, transgresión, liminalidad, frontera, lenguaje</t>
+          <t>Espacio, límite y frontera, Violencia y daño, Lenguaje y escritura</t>
         </is>
       </c>
       <c r="J396" s="2" t="inlineStr"/>
@@ -31556,7 +31556,7 @@
       </c>
       <c r="I397" s="2" t="inlineStr">
         <is>
-          <t>límite, transgresión, liminalidad, frontera, lenguaje</t>
+          <t>Espacio, límite y frontera, Violencia y daño, Lenguaje y escritura</t>
         </is>
       </c>
       <c r="J397" s="2" t="inlineStr"/>
@@ -31633,7 +31633,7 @@
       </c>
       <c r="I398" s="2" t="inlineStr">
         <is>
-          <t>límite, transgresión, liminalidad, frontera, lenguaje</t>
+          <t>Espacio, límite y frontera, Violencia y daño, Lenguaje y escritura</t>
         </is>
       </c>
       <c r="J398" s="2" t="inlineStr"/>
@@ -31710,7 +31710,7 @@
       </c>
       <c r="I399" s="2" t="inlineStr">
         <is>
-          <t>límite, transgresión, liminalidad, frontera, lenguaje</t>
+          <t>Espacio, límite y frontera, Violencia y daño, Lenguaje y escritura</t>
         </is>
       </c>
       <c r="J399" s="2" t="inlineStr"/>
@@ -31783,7 +31783,7 @@
       </c>
       <c r="I400" s="2" t="inlineStr">
         <is>
-          <t>límite, transgresión, liminalidad, frontera, lenguaje</t>
+          <t>Espacio, límite y frontera, Violencia y daño, Lenguaje y escritura</t>
         </is>
       </c>
       <c r="J400" s="2" t="inlineStr"/>
@@ -31860,7 +31860,7 @@
       </c>
       <c r="I401" s="2" t="inlineStr">
         <is>
-          <t>trabajo, artesanía, arte, marxismo, división sexual del trabajo, epistemología</t>
+          <t>Capitalismo, trabajo y economía, Arte, Feminismo y género, Filosofía y epistemología</t>
         </is>
       </c>
       <c r="J401" s="2" t="inlineStr"/>
@@ -31941,7 +31941,7 @@
       </c>
       <c r="I402" s="2" t="inlineStr">
         <is>
-          <t>trabajo, artesanía, arte, marxismo, división sexual del trabajo, epistemología</t>
+          <t>Capitalismo, trabajo y economía, Arte, Feminismo y género, Filosofía y epistemología</t>
         </is>
       </c>
       <c r="J402" s="2" t="inlineStr"/>
@@ -32018,7 +32018,7 @@
       </c>
       <c r="I403" s="2" t="inlineStr">
         <is>
-          <t>trabajo, artesanía, arte, marxismo, división sexual del trabajo, epistemología</t>
+          <t>Capitalismo, trabajo y economía, Arte, Feminismo y género, Filosofía y epistemología</t>
         </is>
       </c>
       <c r="J403" s="2" t="inlineStr"/>
@@ -32099,7 +32099,7 @@
       </c>
       <c r="I404" s="2" t="inlineStr">
         <is>
-          <t>trabajo, artesanía, arte, marxismo, división sexual del trabajo, epistemología</t>
+          <t>Capitalismo, trabajo y economía, Arte, Feminismo y género, Filosofía y epistemología</t>
         </is>
       </c>
       <c r="J404" s="2" t="inlineStr"/>
@@ -32180,7 +32180,7 @@
       </c>
       <c r="I405" s="2" t="inlineStr">
         <is>
-          <t>trabajo, artesanía, arte, marxismo, división sexual del trabajo, epistemología</t>
+          <t>Capitalismo, trabajo y economía, Arte, Feminismo y género, Filosofía y epistemología</t>
         </is>
       </c>
       <c r="J405" s="2" t="inlineStr"/>
@@ -32257,7 +32257,7 @@
       </c>
       <c r="I406" s="2" t="inlineStr">
         <is>
-          <t>trabajo, artesanía, arte, marxismo, división sexual del trabajo, epistemología</t>
+          <t>Capitalismo, trabajo y economía, Arte, Feminismo y género, Filosofía y epistemología</t>
         </is>
       </c>
       <c r="J406" s="2" t="inlineStr"/>
@@ -32334,7 +32334,7 @@
       </c>
       <c r="I407" s="2" t="inlineStr">
         <is>
-          <t>trabajo, artesanía, arte, marxismo, división sexual del trabajo, epistemología</t>
+          <t>Capitalismo, trabajo y economía, Arte, Feminismo y género, Filosofía y epistemología</t>
         </is>
       </c>
       <c r="J407" s="2" t="inlineStr"/>
@@ -32415,7 +32415,7 @@
       </c>
       <c r="I408" s="2" t="inlineStr">
         <is>
-          <t>trabajo, artesanía, arte, marxismo, división sexual del trabajo, epistemología</t>
+          <t>Capitalismo, trabajo y economía, Arte, Feminismo y género, Filosofía y epistemología</t>
         </is>
       </c>
       <c r="J408" s="2" t="inlineStr"/>
@@ -32492,7 +32492,7 @@
       </c>
       <c r="I409" s="2" t="inlineStr">
         <is>
-          <t>trabajo, artesanía, arte, marxismo, división sexual del trabajo, epistemología</t>
+          <t>Capitalismo, trabajo y economía, Arte, Feminismo y género, Filosofía y epistemología</t>
         </is>
       </c>
       <c r="J409" s="2" t="inlineStr"/>
@@ -32569,7 +32569,7 @@
       </c>
       <c r="I410" s="2" t="inlineStr">
         <is>
-          <t>plan, planificación, bricoleur, Estado, urbanismo</t>
+          <t>Existencia y contingencia, Arte, Política y actualidad, Ciudad y urbanismo</t>
         </is>
       </c>
       <c r="J410" s="2" t="inlineStr"/>
@@ -32650,7 +32650,7 @@
       </c>
       <c r="I411" s="2" t="inlineStr">
         <is>
-          <t>plan, planificación, bricoleur, Estado, urbanismo</t>
+          <t>Existencia y contingencia, Arte, Política y actualidad, Ciudad y urbanismo</t>
         </is>
       </c>
       <c r="J411" s="2" t="inlineStr"/>
@@ -32727,7 +32727,7 @@
       </c>
       <c r="I412" s="2" t="inlineStr">
         <is>
-          <t>plan, planificación, bricoleur, Estado, urbanismo</t>
+          <t>Existencia y contingencia, Arte, Política y actualidad, Ciudad y urbanismo</t>
         </is>
       </c>
       <c r="J412" s="2" t="inlineStr"/>
@@ -32804,7 +32804,7 @@
       </c>
       <c r="I413" s="2" t="inlineStr">
         <is>
-          <t>delirio amoroso, erotomanía, locura femenina, Barthes, literatura</t>
+          <t>Amor y vínculos afectivos, Feminismo y género, Monográfico de autor/a, Literatura y lectura</t>
         </is>
       </c>
       <c r="J413" s="2" t="inlineStr"/>
@@ -32881,7 +32881,7 @@
       </c>
       <c r="I414" s="2" t="inlineStr">
         <is>
-          <t>delirio amoroso, erotomanía, locura femenina, Barthes, literatura</t>
+          <t>Amor y vínculos afectivos, Feminismo y género, Monográfico de autor/a, Literatura y lectura</t>
         </is>
       </c>
       <c r="J414" s="2" t="inlineStr"/>
@@ -32962,7 +32962,7 @@
       </c>
       <c r="I415" s="2" t="inlineStr">
         <is>
-          <t>delirio amoroso, erotomanía, locura femenina, Barthes, literatura</t>
+          <t>Amor y vínculos afectivos, Feminismo y género, Monográfico de autor/a, Literatura y lectura</t>
         </is>
       </c>
       <c r="J415" s="2" t="inlineStr"/>
@@ -33049,7 +33049,7 @@
       </c>
       <c r="I416" s="2" t="inlineStr">
         <is>
-          <t>delirio amoroso, erotomanía, locura femenina, Barthes, literatura</t>
+          <t>Amor y vínculos afectivos, Feminismo y género, Monográfico de autor/a, Literatura y lectura</t>
         </is>
       </c>
       <c r="J416" s="2" t="inlineStr"/>
@@ -33136,7 +33136,7 @@
       </c>
       <c r="I417" s="2" t="inlineStr">
         <is>
-          <t>delirio amoroso, erotomanía, locura femenina, Barthes, literatura</t>
+          <t>Amor y vínculos afectivos, Feminismo y género, Monográfico de autor/a, Literatura y lectura</t>
         </is>
       </c>
       <c r="J417" s="2" t="inlineStr"/>
@@ -33213,7 +33213,7 @@
       </c>
       <c r="I418" s="2" t="inlineStr">
         <is>
-          <t>delirio amoroso, erotomanía, locura femenina, Barthes, literatura</t>
+          <t>Amor y vínculos afectivos, Feminismo y género, Monográfico de autor/a, Literatura y lectura</t>
         </is>
       </c>
       <c r="J418" s="2" t="inlineStr"/>
@@ -33290,7 +33290,7 @@
       </c>
       <c r="I419" s="2" t="inlineStr">
         <is>
-          <t>delirio amoroso, erotomanía, locura femenina, Barthes, literatura</t>
+          <t>Amor y vínculos afectivos, Feminismo y género, Monográfico de autor/a, Literatura y lectura</t>
         </is>
       </c>
       <c r="J419" s="2" t="inlineStr"/>
@@ -33377,7 +33377,7 @@
       </c>
       <c r="I420" s="2" t="inlineStr">
         <is>
-          <t>delirio amoroso, erotomanía, locura femenina, Barthes, literatura</t>
+          <t>Amor y vínculos afectivos, Feminismo y género, Monográfico de autor/a, Literatura y lectura</t>
         </is>
       </c>
       <c r="J420" s="2" t="inlineStr"/>
@@ -33454,7 +33454,7 @@
       </c>
       <c r="I421" s="2" t="inlineStr">
         <is>
-          <t>delirio amoroso, erotomanía, locura femenina, Barthes, literatura</t>
+          <t>Amor y vínculos afectivos, Feminismo y género, Monográfico de autor/a, Literatura y lectura</t>
         </is>
       </c>
       <c r="J421" s="2" t="inlineStr"/>
@@ -33531,7 +33531,7 @@
       </c>
       <c r="I422" s="2" t="inlineStr">
         <is>
-          <t>delirio amoroso, erotomanía, locura femenina, Barthes, literatura</t>
+          <t>Amor y vínculos afectivos, Feminismo y género, Monográfico de autor/a, Literatura y lectura</t>
         </is>
       </c>
       <c r="J422" s="2" t="inlineStr"/>
@@ -33618,7 +33618,7 @@
       </c>
       <c r="I423" s="2" t="inlineStr">
         <is>
-          <t>verano, ruralidad, huida, tiempo, ocio</t>
+          <t>Tiempo, Ruralidad y territorio, Viaje y desplazamiento, Emociones y afectos</t>
         </is>
       </c>
       <c r="J423" s="2" t="inlineStr"/>
@@ -33699,7 +33699,7 @@
       </c>
       <c r="I424" s="2" t="inlineStr">
         <is>
-          <t>verano, ruralidad, huida, tiempo, ocio</t>
+          <t>Tiempo, Ruralidad y territorio, Viaje y desplazamiento, Emociones y afectos</t>
         </is>
       </c>
       <c r="J424" s="2" t="inlineStr"/>
@@ -33776,7 +33776,7 @@
       </c>
       <c r="I425" s="2" t="inlineStr">
         <is>
-          <t>verano, ruralidad, huida, tiempo, ocio</t>
+          <t>Tiempo, Ruralidad y territorio, Viaje y desplazamiento, Emociones y afectos</t>
         </is>
       </c>
       <c r="J425" s="2" t="inlineStr"/>
@@ -33853,7 +33853,7 @@
       </c>
       <c r="I426" s="2" t="inlineStr">
         <is>
-          <t>verano, ruralidad, huida, tiempo, ocio</t>
+          <t>Tiempo, Ruralidad y territorio, Viaje y desplazamiento, Emociones y afectos</t>
         </is>
       </c>
       <c r="J426" s="2" t="inlineStr"/>
@@ -33930,7 +33930,7 @@
       </c>
       <c r="I427" s="2" t="inlineStr">
         <is>
-          <t>verano, ruralidad, huida, tiempo, ocio</t>
+          <t>Tiempo, Ruralidad y territorio, Viaje y desplazamiento, Emociones y afectos</t>
         </is>
       </c>
       <c r="J427" s="2" t="inlineStr"/>
@@ -34007,7 +34007,7 @@
       </c>
       <c r="I428" s="2" t="inlineStr">
         <is>
-          <t>verano, ruralidad, huida, tiempo, ocio</t>
+          <t>Tiempo, Ruralidad y territorio, Viaje y desplazamiento, Emociones y afectos</t>
         </is>
       </c>
       <c r="J428" s="2" t="inlineStr"/>
@@ -34088,7 +34088,7 @@
       </c>
       <c r="I429" s="2" t="inlineStr">
         <is>
-          <t>verano, ruralidad, huida, tiempo, ocio</t>
+          <t>Tiempo, Ruralidad y territorio, Viaje y desplazamiento, Emociones y afectos</t>
         </is>
       </c>
       <c r="J429" s="2" t="inlineStr"/>
@@ -34169,7 +34169,7 @@
       </c>
       <c r="I430" s="2" t="inlineStr">
         <is>
-          <t>verano, ruralidad, huida, tiempo, ocio</t>
+          <t>Tiempo, Ruralidad y territorio, Viaje y desplazamiento, Emociones y afectos</t>
         </is>
       </c>
       <c r="J430" s="2" t="inlineStr"/>
@@ -34250,7 +34250,7 @@
       </c>
       <c r="I431" s="2" t="inlineStr">
         <is>
-          <t>responsabilidad moral, violencia, víctima, Gaza, ética, acción y omisión</t>
+          <t>Ética y moral, Violencia y daño, Política y actualidad</t>
         </is>
       </c>
       <c r="J431" s="2" t="inlineStr"/>
@@ -34331,7 +34331,7 @@
       </c>
       <c r="I432" s="2" t="inlineStr">
         <is>
-          <t>responsabilidad moral, violencia, víctima, Gaza, ética, acción y omisión</t>
+          <t>Ética y moral, Violencia y daño, Política y actualidad</t>
         </is>
       </c>
       <c r="J432" s="2" t="inlineStr"/>
@@ -34408,7 +34408,7 @@
       </c>
       <c r="I433" s="2" t="inlineStr">
         <is>
-          <t>responsabilidad moral, violencia, víctima, Gaza, ética, acción y omisión</t>
+          <t>Ética y moral, Violencia y daño, Política y actualidad</t>
         </is>
       </c>
       <c r="J433" s="2" t="inlineStr"/>
@@ -34489,7 +34489,7 @@
       </c>
       <c r="I434" s="2" t="inlineStr">
         <is>
-          <t>responsabilidad moral, violencia, víctima, Gaza, ética, acción y omisión</t>
+          <t>Ética y moral, Violencia y daño, Política y actualidad</t>
         </is>
       </c>
       <c r="J434" s="2" t="inlineStr"/>
@@ -34570,7 +34570,7 @@
       </c>
       <c r="I435" s="2" t="inlineStr">
         <is>
-          <t>responsabilidad moral, violencia, víctima, Gaza, ética, acción y omisión</t>
+          <t>Ética y moral, Violencia y daño, Política y actualidad</t>
         </is>
       </c>
       <c r="J435" s="2" t="inlineStr"/>
@@ -34647,7 +34647,7 @@
       </c>
       <c r="I436" s="2" t="inlineStr">
         <is>
-          <t>responsabilidad moral, violencia, víctima, Gaza, ética, acción y omisión</t>
+          <t>Ética y moral, Violencia y daño, Política y actualidad</t>
         </is>
       </c>
       <c r="J436" s="2" t="inlineStr"/>
@@ -34720,7 +34720,7 @@
       </c>
       <c r="I437" s="2" t="inlineStr">
         <is>
-          <t>responsabilidad moral, violencia, víctima, Gaza, ética, acción y omisión</t>
+          <t>Ética y moral, Violencia y daño, Política y actualidad</t>
         </is>
       </c>
       <c r="J437" s="2" t="inlineStr"/>
@@ -34797,7 +34797,7 @@
       </c>
       <c r="I438" s="2" t="inlineStr">
         <is>
-          <t>fragmento, brevedad, glosa, escritura, Barthes</t>
+          <t>Lenguaje y escritura, Formato especial y evento, Monográfico de autor/a</t>
         </is>
       </c>
       <c r="J438" s="2" t="inlineStr"/>
@@ -34878,7 +34878,7 @@
       </c>
       <c r="I439" s="2" t="inlineStr">
         <is>
-          <t>fragmento, brevedad, glosa, escritura, Barthes</t>
+          <t>Lenguaje y escritura, Formato especial y evento, Monográfico de autor/a</t>
         </is>
       </c>
       <c r="J439" s="2" t="inlineStr"/>
@@ -34959,7 +34959,7 @@
       </c>
       <c r="I440" s="2" t="inlineStr">
         <is>
-          <t>fragmento, brevedad, glosa, escritura, Barthes</t>
+          <t>Lenguaje y escritura, Formato especial y evento, Monográfico de autor/a</t>
         </is>
       </c>
       <c r="J440" s="2" t="inlineStr"/>
@@ -35032,7 +35032,7 @@
       </c>
       <c r="I441" s="2" t="inlineStr">
         <is>
-          <t>fragmento, brevedad, glosa, escritura, Barthes</t>
+          <t>Lenguaje y escritura, Formato especial y evento, Monográfico de autor/a</t>
         </is>
       </c>
       <c r="J441" s="2" t="inlineStr"/>
@@ -35109,7 +35109,7 @@
       </c>
       <c r="I442" s="2" t="inlineStr">
         <is>
-          <t>mirada, voyeurismo, fotografía, arte, deseo, performance</t>
+          <t>Cuerpo y mirada, Fotografía e imagen, Arte, Deseo y erotismo</t>
         </is>
       </c>
       <c r="J442" s="2" t="inlineStr">
@@ -35194,7 +35194,7 @@
       </c>
       <c r="I443" s="2" t="inlineStr">
         <is>
-          <t>mirada, voyeurismo, fotografía, arte, deseo, performance</t>
+          <t>Cuerpo y mirada, Fotografía e imagen, Arte, Deseo y erotismo</t>
         </is>
       </c>
       <c r="J443" s="2" t="inlineStr"/>
@@ -35281,7 +35281,7 @@
       </c>
       <c r="I444" s="2" t="inlineStr">
         <is>
-          <t>mirada, voyeurismo, fotografía, arte, deseo, performance</t>
+          <t>Cuerpo y mirada, Fotografía e imagen, Arte, Deseo y erotismo</t>
         </is>
       </c>
       <c r="J444" s="2" t="inlineStr"/>
@@ -35358,7 +35358,7 @@
       </c>
       <c r="I445" s="2" t="inlineStr">
         <is>
-          <t>mirada, voyeurismo, fotografía, arte, deseo, performance</t>
+          <t>Cuerpo y mirada, Fotografía e imagen, Arte, Deseo y erotismo</t>
         </is>
       </c>
       <c r="J445" s="2" t="inlineStr"/>
@@ -35445,7 +35445,7 @@
       </c>
       <c r="I446" s="2" t="inlineStr">
         <is>
-          <t>mirada, voyeurismo, fotografía, arte, deseo, performance</t>
+          <t>Cuerpo y mirada, Fotografía e imagen, Arte, Deseo y erotismo</t>
         </is>
       </c>
       <c r="J446" s="2" t="inlineStr"/>
@@ -35522,7 +35522,7 @@
       </c>
       <c r="I447" s="2" t="inlineStr">
         <is>
-          <t>mirada, voyeurismo, fotografía, arte, deseo, performance</t>
+          <t>Cuerpo y mirada, Fotografía e imagen, Arte, Deseo y erotismo</t>
         </is>
       </c>
       <c r="J447" s="2" t="inlineStr"/>
@@ -35599,7 +35599,7 @@
       </c>
       <c r="I448" s="2" t="inlineStr">
         <is>
-          <t>mirada, voyeurismo, fotografía, arte, deseo, performance</t>
+          <t>Cuerpo y mirada, Fotografía e imagen, Arte, Deseo y erotismo</t>
         </is>
       </c>
       <c r="J448" s="2" t="inlineStr"/>
@@ -35676,7 +35676,7 @@
       </c>
       <c r="I449" s="2" t="inlineStr">
         <is>
-          <t>mirada, voyeurismo, fotografía, arte, deseo, performance</t>
+          <t>Cuerpo y mirada, Fotografía e imagen, Arte, Deseo y erotismo</t>
         </is>
       </c>
       <c r="J449" s="2" t="inlineStr"/>
@@ -35753,7 +35753,7 @@
       </c>
       <c r="I450" s="2" t="inlineStr">
         <is>
-          <t>mirada, voyeurismo, fotografía, arte, deseo, performance</t>
+          <t>Cuerpo y mirada, Fotografía e imagen, Arte, Deseo y erotismo</t>
         </is>
       </c>
       <c r="J450" s="2" t="inlineStr"/>
@@ -35830,7 +35830,7 @@
       </c>
       <c r="I451" s="2" t="inlineStr">
         <is>
-          <t>mirada, voyeurismo, fotografía, arte, deseo, performance</t>
+          <t>Cuerpo y mirada, Fotografía e imagen, Arte, Deseo y erotismo</t>
         </is>
       </c>
       <c r="J451" s="2" t="inlineStr"/>
@@ -35907,7 +35907,7 @@
       </c>
       <c r="I452" s="2" t="inlineStr">
         <is>
-          <t>familia, abolición de la familia, extrema derecha, políticas públicas, feminismo</t>
+          <t>Familia y maternidad, Política y actualidad, Feminismo y género</t>
         </is>
       </c>
       <c r="J452" s="2" t="inlineStr"/>
@@ -35988,7 +35988,7 @@
       </c>
       <c r="I453" s="2" t="inlineStr">
         <is>
-          <t>familia, abolición de la familia, extrema derecha, políticas públicas, feminismo</t>
+          <t>Familia y maternidad, Política y actualidad, Feminismo y género</t>
         </is>
       </c>
       <c r="J453" s="2" t="inlineStr"/>
@@ -36065,7 +36065,7 @@
       </c>
       <c r="I454" s="2" t="inlineStr">
         <is>
-          <t>familia, abolición de la familia, extrema derecha, políticas públicas, feminismo</t>
+          <t>Familia y maternidad, Política y actualidad, Feminismo y género</t>
         </is>
       </c>
       <c r="J454" s="2" t="inlineStr"/>
@@ -36146,7 +36146,7 @@
       </c>
       <c r="I455" s="2" t="inlineStr">
         <is>
-          <t>familia, abolición de la familia, extrema derecha, políticas públicas, feminismo</t>
+          <t>Familia y maternidad, Política y actualidad, Feminismo y género</t>
         </is>
       </c>
       <c r="J455" s="2" t="inlineStr"/>
@@ -36227,7 +36227,7 @@
       </c>
       <c r="I456" s="2" t="inlineStr">
         <is>
-          <t>familia, abolición de la familia, extrema derecha, políticas públicas, feminismo</t>
+          <t>Familia y maternidad, Política y actualidad, Feminismo y género</t>
         </is>
       </c>
       <c r="J456" s="2" t="inlineStr"/>
@@ -36308,7 +36308,7 @@
       </c>
       <c r="I457" s="2" t="inlineStr">
         <is>
-          <t>familia, abolición de la familia, extrema derecha, políticas públicas, feminismo</t>
+          <t>Familia y maternidad, Política y actualidad, Feminismo y género</t>
         </is>
       </c>
       <c r="J457" s="2" t="inlineStr"/>
@@ -36385,7 +36385,7 @@
       </c>
       <c r="I458" s="2" t="inlineStr">
         <is>
-          <t>familia, abolición de la familia, extrema derecha, políticas públicas, feminismo</t>
+          <t>Familia y maternidad, Política y actualidad, Feminismo y género</t>
         </is>
       </c>
       <c r="J458" s="2" t="inlineStr"/>
@@ -36466,7 +36466,7 @@
       </c>
       <c r="I459" s="2" t="inlineStr">
         <is>
-          <t>familia, abolición de la familia, extrema derecha, políticas públicas, feminismo</t>
+          <t>Familia y maternidad, Política y actualidad, Feminismo y género</t>
         </is>
       </c>
       <c r="J459" s="2" t="inlineStr"/>
@@ -36543,7 +36543,7 @@
       </c>
       <c r="I460" s="2" t="inlineStr">
         <is>
-          <t>sacrificio, religión, violencia, ética, política</t>
+          <t>Ética y moral, Filosofía y epistemología, Violencia y daño, Política y actualidad</t>
         </is>
       </c>
       <c r="J460" s="2" t="inlineStr"/>
@@ -36620,7 +36620,7 @@
       </c>
       <c r="I461" s="2" t="inlineStr">
         <is>
-          <t>sacrificio, religión, violencia, ética, política</t>
+          <t>Ética y moral, Filosofía y epistemología, Violencia y daño, Política y actualidad</t>
         </is>
       </c>
       <c r="J461" s="2" t="inlineStr"/>
@@ -36707,7 +36707,7 @@
       </c>
       <c r="I462" s="2" t="inlineStr">
         <is>
-          <t>sacrificio, religión, violencia, ética, política</t>
+          <t>Ética y moral, Filosofía y epistemología, Violencia y daño, Política y actualidad</t>
         </is>
       </c>
       <c r="J462" s="2" t="inlineStr"/>
@@ -36784,7 +36784,7 @@
       </c>
       <c r="I463" s="2" t="inlineStr">
         <is>
-          <t>sacrificio, religión, violencia, ética, política</t>
+          <t>Ética y moral, Filosofía y epistemología, Violencia y daño, Política y actualidad</t>
         </is>
       </c>
       <c r="J463" s="2" t="inlineStr"/>
@@ -36871,7 +36871,7 @@
       </c>
       <c r="I464" s="2" t="inlineStr">
         <is>
-          <t>sacrificio, religión, violencia, ética, política</t>
+          <t>Ética y moral, Filosofía y epistemología, Violencia y daño, Política y actualidad</t>
         </is>
       </c>
       <c r="J464" s="2" t="inlineStr"/>
@@ -36954,7 +36954,7 @@
       </c>
       <c r="I465" s="2" t="inlineStr">
         <is>
-          <t>sacrificio, religión, violencia, ética, política</t>
+          <t>Ética y moral, Filosofía y epistemología, Violencia y daño, Política y actualidad</t>
         </is>
       </c>
       <c r="J465" s="2" t="inlineStr"/>
@@ -37031,7 +37031,7 @@
       </c>
       <c r="I466" s="2" t="inlineStr">
         <is>
-          <t>sacrificio, religión, violencia, ética, política</t>
+          <t>Ética y moral, Filosofía y epistemología, Violencia y daño, Política y actualidad</t>
         </is>
       </c>
       <c r="J466" s="2" t="inlineStr"/>
@@ -37118,7 +37118,7 @@
       </c>
       <c r="I467" s="2" t="inlineStr">
         <is>
-          <t>sacrificio, religión, violencia, ética, política</t>
+          <t>Ética y moral, Filosofía y epistemología, Violencia y daño, Política y actualidad</t>
         </is>
       </c>
       <c r="J467" s="2" t="inlineStr"/>
@@ -37191,7 +37191,7 @@
       </c>
       <c r="I468" s="2" t="inlineStr">
         <is>
-          <t>sacrificio, religión, violencia, ética, política</t>
+          <t>Ética y moral, Filosofía y epistemología, Violencia y daño, Política y actualidad</t>
         </is>
       </c>
       <c r="J468" s="2" t="inlineStr"/>
@@ -37268,7 +37268,7 @@
       </c>
       <c r="I469" s="2" t="inlineStr">
         <is>
-          <t>conocimiento del otro, amor, misterio, secreto</t>
+          <t>Filosofía y epistemología, Amor y vínculos afectivos, Existencia y contingencia, Miedo y vulnerabilidad</t>
         </is>
       </c>
       <c r="J469" s="2" t="inlineStr"/>
@@ -37355,7 +37355,7 @@
       </c>
       <c r="I470" s="2" t="inlineStr">
         <is>
-          <t>conocimiento del otro, amor, misterio, secreto</t>
+          <t>Filosofía y epistemología, Amor y vínculos afectivos, Existencia y contingencia, Miedo y vulnerabilidad</t>
         </is>
       </c>
       <c r="J470" s="2" t="inlineStr"/>
@@ -37436,7 +37436,7 @@
       </c>
       <c r="I471" s="2" t="inlineStr">
         <is>
-          <t>conocimiento del otro, amor, misterio, secreto</t>
+          <t>Filosofía y epistemología, Amor y vínculos afectivos, Existencia y contingencia, Miedo y vulnerabilidad</t>
         </is>
       </c>
       <c r="J471" s="2" t="inlineStr"/>
@@ -37513,7 +37513,7 @@
       </c>
       <c r="I472" s="2" t="inlineStr">
         <is>
-          <t>conocimiento del otro, amor, misterio, secreto</t>
+          <t>Filosofía y epistemología, Amor y vínculos afectivos, Existencia y contingencia, Miedo y vulnerabilidad</t>
         </is>
       </c>
       <c r="J472" s="2" t="inlineStr"/>
@@ -37600,7 +37600,7 @@
       </c>
       <c r="I473" s="2" t="inlineStr">
         <is>
-          <t>conocimiento del otro, amor, misterio, secreto</t>
+          <t>Filosofía y epistemología, Amor y vínculos afectivos, Existencia y contingencia, Miedo y vulnerabilidad</t>
         </is>
       </c>
       <c r="J473" s="2" t="inlineStr"/>
@@ -37687,7 +37687,7 @@
       </c>
       <c r="I474" s="2" t="inlineStr">
         <is>
-          <t>conocimiento del otro, amor, misterio, secreto</t>
+          <t>Filosofía y epistemología, Amor y vínculos afectivos, Existencia y contingencia, Miedo y vulnerabilidad</t>
         </is>
       </c>
       <c r="J474" s="2" t="inlineStr"/>
@@ -37778,7 +37778,7 @@
       </c>
       <c r="I475" s="2" t="inlineStr">
         <is>
-          <t>Barthes, homosexualidad, colonialismo, turismo sexual, biografía</t>
+          <t>Monográfico de autor/a, Sexualidad y disidencia sexual, Colonialismo y poscolonialismo, Narración, ficción y autoficción</t>
         </is>
       </c>
       <c r="J475" s="2" t="inlineStr">
@@ -37863,7 +37863,7 @@
       </c>
       <c r="I476" s="2" t="inlineStr">
         <is>
-          <t>Barthes, homosexualidad, colonialismo, turismo sexual, biografía</t>
+          <t>Monográfico de autor/a, Sexualidad y disidencia sexual, Colonialismo y poscolonialismo, Narración, ficción y autoficción</t>
         </is>
       </c>
       <c r="J476" s="2" t="inlineStr"/>
@@ -37950,7 +37950,7 @@
       </c>
       <c r="I477" s="2" t="inlineStr">
         <is>
-          <t>Barthes, homosexualidad, colonialismo, turismo sexual, biografía</t>
+          <t>Monográfico de autor/a, Sexualidad y disidencia sexual, Colonialismo y poscolonialismo, Narración, ficción y autoficción</t>
         </is>
       </c>
       <c r="J477" s="2" t="inlineStr">
@@ -38041,7 +38041,7 @@
       </c>
       <c r="I478" s="2" t="inlineStr">
         <is>
-          <t>Barthes, homosexualidad, colonialismo, turismo sexual, biografía</t>
+          <t>Monográfico de autor/a, Sexualidad y disidencia sexual, Colonialismo y poscolonialismo, Narración, ficción y autoficción</t>
         </is>
       </c>
       <c r="J478" s="2" t="inlineStr"/>
@@ -38128,7 +38128,7 @@
       </c>
       <c r="I479" s="2" t="inlineStr">
         <is>
-          <t>Barthes, homosexualidad, colonialismo, turismo sexual, biografía</t>
+          <t>Monográfico de autor/a, Sexualidad y disidencia sexual, Colonialismo y poscolonialismo, Narración, ficción y autoficción</t>
         </is>
       </c>
       <c r="J479" s="2" t="inlineStr"/>
@@ -38205,7 +38205,7 @@
       </c>
       <c r="I480" s="2" t="inlineStr">
         <is>
-          <t>Barthes, homosexualidad, colonialismo, turismo sexual, biografía</t>
+          <t>Monográfico de autor/a, Sexualidad y disidencia sexual, Colonialismo y poscolonialismo, Narración, ficción y autoficción</t>
         </is>
       </c>
       <c r="J480" s="2" t="inlineStr"/>
@@ -38282,7 +38282,7 @@
       </c>
       <c r="I481" s="2" t="inlineStr">
         <is>
-          <t>Barthes, homosexualidad, colonialismo, turismo sexual, biografía</t>
+          <t>Monográfico de autor/a, Sexualidad y disidencia sexual, Colonialismo y poscolonialismo, Narración, ficción y autoficción</t>
         </is>
       </c>
       <c r="J481" s="2" t="inlineStr">
@@ -38367,7 +38367,7 @@
       </c>
       <c r="I482" s="2" t="inlineStr">
         <is>
-          <t>Barthes, homosexualidad, colonialismo, turismo sexual, biografía</t>
+          <t>Monográfico de autor/a, Sexualidad y disidencia sexual, Colonialismo y poscolonialismo, Narración, ficción y autoficción</t>
         </is>
       </c>
       <c r="J482" s="2" t="inlineStr">
@@ -38452,7 +38452,7 @@
       </c>
       <c r="I483" s="2" t="inlineStr">
         <is>
-          <t>categorías, lenguaje, nominalismo, clasificación, metafísica</t>
+          <t>Filosofía y epistemología, Lenguaje y escritura</t>
         </is>
       </c>
       <c r="J483" s="2" t="inlineStr"/>
@@ -38529,7 +38529,7 @@
       </c>
       <c r="I484" s="2" t="inlineStr">
         <is>
-          <t>categorías, lenguaje, nominalismo, clasificación, metafísica</t>
+          <t>Filosofía y epistemología, Lenguaje y escritura</t>
         </is>
       </c>
       <c r="J484" s="2" t="inlineStr"/>
@@ -38616,7 +38616,7 @@
       </c>
       <c r="I485" s="2" t="inlineStr">
         <is>
-          <t>categorías, lenguaje, nominalismo, clasificación, metafísica</t>
+          <t>Filosofía y epistemología, Lenguaje y escritura</t>
         </is>
       </c>
       <c r="J485" s="2" t="inlineStr"/>
@@ -38697,7 +38697,7 @@
       </c>
       <c r="I486" s="2" t="inlineStr">
         <is>
-          <t>categorías, lenguaje, nominalismo, clasificación, metafísica</t>
+          <t>Filosofía y epistemología, Lenguaje y escritura</t>
         </is>
       </c>
       <c r="J486" s="2" t="inlineStr"/>
@@ -38778,7 +38778,7 @@
       </c>
       <c r="I487" s="2" t="inlineStr">
         <is>
-          <t>categorías, lenguaje, nominalismo, clasificación, metafísica</t>
+          <t>Filosofía y epistemología, Lenguaje y escritura</t>
         </is>
       </c>
       <c r="J487" s="2" t="inlineStr"/>
@@ -38859,7 +38859,7 @@
       </c>
       <c r="I488" s="2" t="inlineStr">
         <is>
-          <t>categorías, lenguaje, nominalismo, clasificación, metafísica</t>
+          <t>Filosofía y epistemología, Lenguaje y escritura</t>
         </is>
       </c>
       <c r="J488" s="2" t="inlineStr"/>
@@ -38946,7 +38946,7 @@
       </c>
       <c r="I489" s="2" t="inlineStr">
         <is>
-          <t>compasión, ética, alteridad, dolor</t>
+          <t>Ética y moral, Filosofía y epistemología, Emociones y afectos</t>
         </is>
       </c>
       <c r="J489" s="2" t="inlineStr"/>
@@ -39033,7 +39033,7 @@
       </c>
       <c r="I490" s="2" t="inlineStr">
         <is>
-          <t>compasión, ética, alteridad, dolor</t>
+          <t>Ética y moral, Filosofía y epistemología, Emociones y afectos</t>
         </is>
       </c>
       <c r="J490" s="2" t="inlineStr"/>
@@ -39120,7 +39120,7 @@
       </c>
       <c r="I491" s="2" t="inlineStr">
         <is>
-          <t>compasión, ética, alteridad, dolor</t>
+          <t>Ética y moral, Filosofía y epistemología, Emociones y afectos</t>
         </is>
       </c>
       <c r="J491" s="2" t="inlineStr"/>
@@ -39201,7 +39201,7 @@
       </c>
       <c r="I492" s="2" t="inlineStr">
         <is>
-          <t>compasión, ética, alteridad, dolor</t>
+          <t>Ética y moral, Filosofía y epistemología, Emociones y afectos</t>
         </is>
       </c>
       <c r="J492" s="2" t="inlineStr"/>
@@ -39278,7 +39278,7 @@
       </c>
       <c r="I493" s="2" t="inlineStr">
         <is>
-          <t>compasión, ética, alteridad, dolor</t>
+          <t>Ética y moral, Filosofía y epistemología, Emociones y afectos</t>
         </is>
       </c>
       <c r="J493" s="2" t="inlineStr"/>
@@ -39365,7 +39365,7 @@
       </c>
       <c r="I494" s="2" t="inlineStr">
         <is>
-          <t>silencio, poder, violencia, familia, secreto</t>
+          <t>Sonido y escucha, Política y actualidad, Violencia y daño, Familia y maternidad, Miedo y vulnerabilidad</t>
         </is>
       </c>
       <c r="J494" s="2" t="inlineStr"/>
@@ -39446,7 +39446,7 @@
       </c>
       <c r="I495" s="2" t="inlineStr">
         <is>
-          <t>silencio, poder, violencia, familia, secreto</t>
+          <t>Sonido y escucha, Política y actualidad, Violencia y daño, Familia y maternidad, Miedo y vulnerabilidad</t>
         </is>
       </c>
       <c r="J495" s="2" t="inlineStr"/>
@@ -39527,7 +39527,7 @@
       </c>
       <c r="I496" s="2" t="inlineStr">
         <is>
-          <t>silencio, poder, violencia, familia, secreto</t>
+          <t>Sonido y escucha, Política y actualidad, Violencia y daño, Familia y maternidad, Miedo y vulnerabilidad</t>
         </is>
       </c>
       <c r="J496" s="2" t="inlineStr"/>
@@ -39614,7 +39614,7 @@
       </c>
       <c r="I497" s="2" t="inlineStr">
         <is>
-          <t>silencio, poder, violencia, familia, secreto</t>
+          <t>Sonido y escucha, Política y actualidad, Violencia y daño, Familia y maternidad, Miedo y vulnerabilidad</t>
         </is>
       </c>
       <c r="J497" s="2" t="inlineStr"/>
@@ -39701,7 +39701,7 @@
       </c>
       <c r="I498" s="2" t="inlineStr">
         <is>
-          <t>silencio, poder, violencia, familia, secreto</t>
+          <t>Sonido y escucha, Política y actualidad, Violencia y daño, Familia y maternidad, Miedo y vulnerabilidad</t>
         </is>
       </c>
       <c r="J498" s="2" t="inlineStr"/>
@@ -39778,7 +39778,7 @@
       </c>
       <c r="I499" s="2" t="inlineStr">
         <is>
-          <t>silencio, poder, violencia, familia, secreto</t>
+          <t>Sonido y escucha, Política y actualidad, Violencia y daño, Familia y maternidad, Miedo y vulnerabilidad</t>
         </is>
       </c>
       <c r="J499" s="2" t="inlineStr"/>
@@ -39869,7 +39869,7 @@
       </c>
       <c r="I500" s="2" t="inlineStr">
         <is>
-          <t>silencio, gesto, arte, filosofía, Wittgenstein</t>
+          <t>Sonido y escucha, Cuerpo y mirada, Arte, Filosofía y epistemología, Monográfico de autor/a</t>
         </is>
       </c>
       <c r="J500" s="2" t="inlineStr"/>
@@ -39956,7 +39956,7 @@
       </c>
       <c r="I501" s="2" t="inlineStr">
         <is>
-          <t>silencio, gesto, arte, filosofía, Wittgenstein</t>
+          <t>Sonido y escucha, Cuerpo y mirada, Arte, Filosofía y epistemología, Monográfico de autor/a</t>
         </is>
       </c>
       <c r="J501" s="2" t="inlineStr"/>
@@ -40037,7 +40037,7 @@
       </c>
       <c r="I502" s="2" t="inlineStr">
         <is>
-          <t>silencio, gesto, arte, filosofía, Wittgenstein</t>
+          <t>Sonido y escucha, Cuerpo y mirada, Arte, Filosofía y epistemología, Monográfico de autor/a</t>
         </is>
       </c>
       <c r="J502" s="2" t="inlineStr"/>
@@ -40114,7 +40114,7 @@
       </c>
       <c r="I503" s="2" t="inlineStr">
         <is>
-          <t>silencio, gesto, arte, filosofía, Wittgenstein</t>
+          <t>Sonido y escucha, Cuerpo y mirada, Arte, Filosofía y epistemología, Monográfico de autor/a</t>
         </is>
       </c>
       <c r="J503" s="2" t="inlineStr"/>
@@ -40201,7 +40201,7 @@
       </c>
       <c r="I504" s="2" t="inlineStr">
         <is>
-          <t>silencio, gesto, arte, filosofía, Wittgenstein</t>
+          <t>Sonido y escucha, Cuerpo y mirada, Arte, Filosofía y epistemología, Monográfico de autor/a</t>
         </is>
       </c>
       <c r="J504" s="2" t="inlineStr"/>
@@ -40282,7 +40282,7 @@
       </c>
       <c r="I505" s="2" t="inlineStr">
         <is>
-          <t>silencio, gesto, arte, filosofía, Wittgenstein</t>
+          <t>Sonido y escucha, Cuerpo y mirada, Arte, Filosofía y epistemología, Monográfico de autor/a</t>
         </is>
       </c>
       <c r="J505" s="2" t="inlineStr"/>
@@ -40363,7 +40363,7 @@
       </c>
       <c r="I506" s="2" t="inlineStr">
         <is>
-          <t>silencio, gesto, arte, filosofía, Wittgenstein</t>
+          <t>Sonido y escucha, Cuerpo y mirada, Arte, Filosofía y epistemología, Monográfico de autor/a</t>
         </is>
       </c>
       <c r="J506" s="2" t="inlineStr"/>
@@ -40440,7 +40440,7 @@
       </c>
       <c r="I507" s="2" t="inlineStr">
         <is>
-          <t>silencio, gesto, arte, filosofía, Wittgenstein</t>
+          <t>Sonido y escucha, Cuerpo y mirada, Arte, Filosofía y epistemología, Monográfico de autor/a</t>
         </is>
       </c>
       <c r="J507" s="2" t="inlineStr"/>
@@ -40521,7 +40521,7 @@
       </c>
       <c r="I508" s="2" t="inlineStr">
         <is>
-          <t>silencio, gesto, arte, filosofía, Wittgenstein</t>
+          <t>Sonido y escucha, Cuerpo y mirada, Arte, Filosofía y epistemología, Monográfico de autor/a</t>
         </is>
       </c>
       <c r="J508" s="2" t="inlineStr"/>
@@ -40602,7 +40602,7 @@
       </c>
       <c r="I509" s="2" t="inlineStr">
         <is>
-          <t>miedo, emociones, razón, política</t>
+          <t>Miedo y vulnerabilidad, Emociones y afectos, Filosofía y epistemología, Política y actualidad</t>
         </is>
       </c>
       <c r="J509" s="2" t="inlineStr"/>
@@ -40689,7 +40689,7 @@
       </c>
       <c r="I510" s="2" t="inlineStr">
         <is>
-          <t>miedo, emociones, razón, política</t>
+          <t>Miedo y vulnerabilidad, Emociones y afectos, Filosofía y epistemología, Política y actualidad</t>
         </is>
       </c>
       <c r="J510" s="2" t="inlineStr"/>
@@ -40770,7 +40770,7 @@
       </c>
       <c r="I511" s="2" t="inlineStr">
         <is>
-          <t>miedo, emociones, razón, política</t>
+          <t>Miedo y vulnerabilidad, Emociones y afectos, Filosofía y epistemología, Política y actualidad</t>
         </is>
       </c>
       <c r="J511" s="2" t="inlineStr"/>
@@ -40857,7 +40857,7 @@
       </c>
       <c r="I512" s="2" t="inlineStr">
         <is>
-          <t>miedo, emociones, razón, política</t>
+          <t>Miedo y vulnerabilidad, Emociones y afectos, Filosofía y epistemología, Política y actualidad</t>
         </is>
       </c>
       <c r="J512" s="2" t="inlineStr"/>
@@ -40938,7 +40938,7 @@
       </c>
       <c r="I513" s="2" t="inlineStr">
         <is>
-          <t>mar, poesía, lenguaje, fenomenología, literatura</t>
+          <t>Naturaleza y elementos, Literatura y lectura, Lenguaje y escritura, Filosofía y epistemología</t>
         </is>
       </c>
       <c r="J513" s="2" t="inlineStr"/>
@@ -41015,7 +41015,7 @@
       </c>
       <c r="I514" s="2" t="inlineStr">
         <is>
-          <t>mar, poesía, lenguaje, fenomenología, literatura</t>
+          <t>Naturaleza y elementos, Literatura y lectura, Lenguaje y escritura, Filosofía y epistemología</t>
         </is>
       </c>
       <c r="J514" s="2" t="inlineStr">
@@ -41100,7 +41100,7 @@
       </c>
       <c r="I515" s="2" t="inlineStr">
         <is>
-          <t>mar, poesía, lenguaje, fenomenología, literatura</t>
+          <t>Naturaleza y elementos, Literatura y lectura, Lenguaje y escritura, Filosofía y epistemología</t>
         </is>
       </c>
       <c r="J515" s="2" t="inlineStr"/>
@@ -41177,7 +41177,7 @@
       </c>
       <c r="I516" s="2" t="inlineStr">
         <is>
-          <t>mar, poesía, lenguaje, fenomenología, literatura</t>
+          <t>Naturaleza y elementos, Literatura y lectura, Lenguaje y escritura, Filosofía y epistemología</t>
         </is>
       </c>
       <c r="J516" s="2" t="inlineStr"/>
@@ -41264,7 +41264,7 @@
       </c>
       <c r="I517" s="2" t="inlineStr">
         <is>
-          <t>mar, poesía, lenguaje, fenomenología, literatura</t>
+          <t>Naturaleza y elementos, Literatura y lectura, Lenguaje y escritura, Filosofía y epistemología</t>
         </is>
       </c>
       <c r="J517" s="2" t="inlineStr"/>
@@ -41345,7 +41345,7 @@
       </c>
       <c r="I518" s="2" t="inlineStr">
         <is>
-          <t>mar, poesía, lenguaje, fenomenología, literatura</t>
+          <t>Naturaleza y elementos, Literatura y lectura, Lenguaje y escritura, Filosofía y epistemología</t>
         </is>
       </c>
       <c r="J518" s="2" t="inlineStr"/>
@@ -41432,7 +41432,7 @@
       </c>
       <c r="I519" s="2" t="inlineStr">
         <is>
-          <t>autoría, muerte del autor, feminismo, poscolonial, memoria, subalternidad</t>
+          <t>Narración, ficción y autoficción, Feminismo y género, Colonialismo y poscolonialismo, Memoria e historia</t>
         </is>
       </c>
       <c r="J519" s="2" t="inlineStr"/>
@@ -41513,7 +41513,7 @@
       </c>
       <c r="I520" s="2" t="inlineStr">
         <is>
-          <t>autoría, muerte del autor, feminismo, poscolonial, memoria, subalternidad</t>
+          <t>Narración, ficción y autoficción, Feminismo y género, Colonialismo y poscolonialismo, Memoria e historia</t>
         </is>
       </c>
       <c r="J520" s="2" t="inlineStr"/>
@@ -41590,7 +41590,7 @@
       </c>
       <c r="I521" s="2" t="inlineStr">
         <is>
-          <t>autoría, muerte del autor, feminismo, poscolonial, memoria, subalternidad</t>
+          <t>Narración, ficción y autoficción, Feminismo y género, Colonialismo y poscolonialismo, Memoria e historia</t>
         </is>
       </c>
       <c r="J521" s="2" t="inlineStr"/>
@@ -41677,7 +41677,7 @@
       </c>
       <c r="I522" s="2" t="inlineStr">
         <is>
-          <t>autoría, muerte del autor, feminismo, poscolonial, memoria, subalternidad</t>
+          <t>Narración, ficción y autoficción, Feminismo y género, Colonialismo y poscolonialismo, Memoria e historia</t>
         </is>
       </c>
       <c r="J522" s="2" t="inlineStr"/>
@@ -41764,7 +41764,7 @@
       </c>
       <c r="I523" s="2" t="inlineStr">
         <is>
-          <t>autoría, muerte del autor, feminismo, poscolonial, memoria, subalternidad</t>
+          <t>Narración, ficción y autoficción, Feminismo y género, Colonialismo y poscolonialismo, Memoria e historia</t>
         </is>
       </c>
       <c r="J523" s="2" t="inlineStr"/>
@@ -41845,7 +41845,7 @@
       </c>
       <c r="I524" s="2" t="inlineStr">
         <is>
-          <t>autoría, muerte del autor, feminismo, poscolonial, memoria, subalternidad</t>
+          <t>Narración, ficción y autoficción, Feminismo y género, Colonialismo y poscolonialismo, Memoria e historia</t>
         </is>
       </c>
       <c r="J524" s="2" t="inlineStr"/>
@@ -41926,7 +41926,7 @@
       </c>
       <c r="I525" s="2" t="inlineStr">
         <is>
-          <t>autoría, muerte del autor, feminismo, poscolonial, memoria, subalternidad</t>
+          <t>Narración, ficción y autoficción, Feminismo y género, Colonialismo y poscolonialismo, Memoria e historia</t>
         </is>
       </c>
       <c r="J525" s="2" t="inlineStr"/>
@@ -42007,7 +42007,7 @@
       </c>
       <c r="I526" s="2" t="inlineStr">
         <is>
-          <t>museo, museología crítica, colonialismo, arte, ética</t>
+          <t>Arte, Colonialismo y poscolonialismo, Ética y moral</t>
         </is>
       </c>
       <c r="J526" s="2" t="inlineStr"/>
@@ -42084,7 +42084,7 @@
       </c>
       <c r="I527" s="2" t="inlineStr">
         <is>
-          <t>museo, museología crítica, colonialismo, arte, ética</t>
+          <t>Arte, Colonialismo y poscolonialismo, Ética y moral</t>
         </is>
       </c>
       <c r="J527" s="2" t="inlineStr"/>
@@ -42161,7 +42161,7 @@
       </c>
       <c r="I528" s="2" t="inlineStr">
         <is>
-          <t>museo, museología crítica, colonialismo, arte, ética</t>
+          <t>Arte, Colonialismo y poscolonialismo, Ética y moral</t>
         </is>
       </c>
       <c r="J528" s="2" t="inlineStr"/>
@@ -42238,7 +42238,7 @@
       </c>
       <c r="I529" s="2" t="inlineStr">
         <is>
-          <t>museo, museología crítica, colonialismo, arte, ética</t>
+          <t>Arte, Colonialismo y poscolonialismo, Ética y moral</t>
         </is>
       </c>
       <c r="J529" s="2" t="inlineStr"/>
@@ -42319,7 +42319,7 @@
       </c>
       <c r="I530" s="2" t="inlineStr">
         <is>
-          <t>museo, museología crítica, colonialismo, arte, ética</t>
+          <t>Arte, Colonialismo y poscolonialismo, Ética y moral</t>
         </is>
       </c>
       <c r="J530" s="2" t="inlineStr"/>
@@ -42400,7 +42400,7 @@
       </c>
       <c r="I531" s="2" t="inlineStr">
         <is>
-          <t>museo, museología crítica, colonialismo, arte, ética</t>
+          <t>Arte, Colonialismo y poscolonialismo, Ética y moral</t>
         </is>
       </c>
       <c r="J531" s="2" t="inlineStr"/>
@@ -42481,7 +42481,7 @@
       </c>
       <c r="I532" s="2" t="inlineStr">
         <is>
-          <t>museo, museología crítica, colonialismo, arte, ética</t>
+          <t>Arte, Colonialismo y poscolonialismo, Ética y moral</t>
         </is>
       </c>
       <c r="J532" s="2" t="inlineStr"/>
@@ -42568,7 +42568,7 @@
       </c>
       <c r="I533" s="2" t="inlineStr">
         <is>
-          <t>ruralidad, amor, espacio, masculinidad, deseo, homosexualidad, queer</t>
+          <t>Ruralidad y territorio, Amor y vínculos afectivos, Espacio, límite y frontera, Feminismo y género, Deseo y erotismo, Sexualidad y disidencia sexual</t>
         </is>
       </c>
       <c r="J533" s="2" t="inlineStr"/>
@@ -42655,7 +42655,7 @@
       </c>
       <c r="I534" s="2" t="inlineStr">
         <is>
-          <t>ruralidad, amor, espacio, masculinidad, deseo, homosexualidad, queer</t>
+          <t>Ruralidad y territorio, Amor y vínculos afectivos, Espacio, límite y frontera, Feminismo y género, Deseo y erotismo, Sexualidad y disidencia sexual</t>
         </is>
       </c>
       <c r="J534" s="2" t="inlineStr"/>
@@ -42732,7 +42732,7 @@
       </c>
       <c r="I535" s="2" t="inlineStr">
         <is>
-          <t>ruralidad, amor, espacio, masculinidad, deseo, homosexualidad, queer</t>
+          <t>Ruralidad y territorio, Amor y vínculos afectivos, Espacio, límite y frontera, Feminismo y género, Deseo y erotismo, Sexualidad y disidencia sexual</t>
         </is>
       </c>
       <c r="J535" s="2" t="inlineStr"/>
@@ -42813,7 +42813,7 @@
       </c>
       <c r="I536" s="2" t="inlineStr">
         <is>
-          <t>ruralidad, amor, espacio, masculinidad, deseo, homosexualidad, queer</t>
+          <t>Ruralidad y territorio, Amor y vínculos afectivos, Espacio, límite y frontera, Feminismo y género, Deseo y erotismo, Sexualidad y disidencia sexual</t>
         </is>
       </c>
       <c r="J536" s="2" t="inlineStr"/>
@@ -42890,7 +42890,7 @@
       </c>
       <c r="I537" s="2" t="inlineStr">
         <is>
-          <t>ruralidad, amor, espacio, masculinidad, deseo, homosexualidad, queer</t>
+          <t>Ruralidad y territorio, Amor y vínculos afectivos, Espacio, límite y frontera, Feminismo y género, Deseo y erotismo, Sexualidad y disidencia sexual</t>
         </is>
       </c>
       <c r="J537" s="2" t="inlineStr"/>
@@ -42977,7 +42977,7 @@
       </c>
       <c r="I538" s="2" t="inlineStr">
         <is>
-          <t>ruralidad, amor, espacio, masculinidad, deseo, homosexualidad, queer</t>
+          <t>Ruralidad y territorio, Amor y vínculos afectivos, Espacio, límite y frontera, Feminismo y género, Deseo y erotismo, Sexualidad y disidencia sexual</t>
         </is>
       </c>
       <c r="J538" s="2" t="inlineStr"/>
@@ -43054,7 +43054,7 @@
       </c>
       <c r="I539" s="2" t="inlineStr">
         <is>
-          <t>ruralidad, amor, espacio, masculinidad, deseo, homosexualidad, queer</t>
+          <t>Ruralidad y territorio, Amor y vínculos afectivos, Espacio, límite y frontera, Feminismo y género, Deseo y erotismo, Sexualidad y disidencia sexual</t>
         </is>
       </c>
       <c r="J539" s="2" t="inlineStr"/>
@@ -43131,7 +43131,7 @@
       </c>
       <c r="I540" s="2" t="inlineStr">
         <is>
-          <t>crueldad, ética, literatura, violencia, función de la ficción</t>
+          <t>Violencia y daño, Ética y moral, Literatura y lectura, Narración, ficción y autoficción</t>
         </is>
       </c>
       <c r="J540" s="2" t="inlineStr"/>
@@ -43218,7 +43218,7 @@
       </c>
       <c r="I541" s="2" t="inlineStr">
         <is>
-          <t>crueldad, ética, literatura, violencia, función de la ficción</t>
+          <t>Violencia y daño, Ética y moral, Literatura y lectura, Narración, ficción y autoficción</t>
         </is>
       </c>
       <c r="J541" s="2" t="inlineStr"/>
@@ -43295,7 +43295,7 @@
       </c>
       <c r="I542" s="2" t="inlineStr">
         <is>
-          <t>crueldad, ética, literatura, violencia, función de la ficción</t>
+          <t>Violencia y daño, Ética y moral, Literatura y lectura, Narración, ficción y autoficción</t>
         </is>
       </c>
       <c r="J542" s="2" t="inlineStr"/>
@@ -43382,7 +43382,7 @@
       </c>
       <c r="I543" s="2" t="inlineStr">
         <is>
-          <t>crueldad, ética, literatura, violencia, función de la ficción</t>
+          <t>Violencia y daño, Ética y moral, Literatura y lectura, Narración, ficción y autoficción</t>
         </is>
       </c>
       <c r="J543" s="2" t="inlineStr"/>
@@ -43463,7 +43463,7 @@
       </c>
       <c r="I544" s="2" t="inlineStr">
         <is>
-          <t>crueldad, ética, literatura, violencia, función de la ficción</t>
+          <t>Violencia y daño, Ética y moral, Literatura y lectura, Narración, ficción y autoficción</t>
         </is>
       </c>
       <c r="J544" s="2" t="inlineStr"/>
@@ -43544,7 +43544,7 @@
       </c>
       <c r="I545" s="2" t="inlineStr">
         <is>
-          <t>amor, ruptura amorosa, duelo, desamor, Barthes</t>
+          <t>Amor y vínculos afectivos, Muerte y duelo, Monográfico de autor/a</t>
         </is>
       </c>
       <c r="J545" s="2" t="inlineStr"/>
@@ -43631,7 +43631,7 @@
       </c>
       <c r="I546" s="2" t="inlineStr">
         <is>
-          <t>amor, ruptura amorosa, duelo, desamor, Barthes</t>
+          <t>Amor y vínculos afectivos, Muerte y duelo, Monográfico de autor/a</t>
         </is>
       </c>
       <c r="J546" s="2" t="inlineStr"/>
@@ -43712,7 +43712,7 @@
       </c>
       <c r="I547" s="2" t="inlineStr">
         <is>
-          <t>amor, ruptura amorosa, duelo, desamor, Barthes</t>
+          <t>Amor y vínculos afectivos, Muerte y duelo, Monográfico de autor/a</t>
         </is>
       </c>
       <c r="J547" s="2" t="inlineStr"/>
@@ -43789,7 +43789,7 @@
       </c>
       <c r="I548" s="2" t="inlineStr">
         <is>
-          <t>amor, ruptura amorosa, duelo, desamor, Barthes</t>
+          <t>Amor y vínculos afectivos, Muerte y duelo, Monográfico de autor/a</t>
         </is>
       </c>
       <c r="J548" s="2" t="inlineStr"/>
@@ -43866,7 +43866,7 @@
       </c>
       <c r="I549" s="2" t="inlineStr">
         <is>
-          <t>amor, ruptura amorosa, duelo, desamor, Barthes</t>
+          <t>Amor y vínculos afectivos, Muerte y duelo, Monográfico de autor/a</t>
         </is>
       </c>
       <c r="J549" s="2" t="inlineStr"/>
@@ -43943,7 +43943,7 @@
       </c>
       <c r="I550" s="2" t="inlineStr">
         <is>
-          <t>amor, ruptura amorosa, duelo, desamor, Barthes</t>
+          <t>Amor y vínculos afectivos, Muerte y duelo, Monográfico de autor/a</t>
         </is>
       </c>
       <c r="J550" s="2" t="inlineStr"/>
@@ -44020,7 +44020,7 @@
       </c>
       <c r="I551" s="2" t="inlineStr">
         <is>
-          <t>amor, ruptura amorosa, duelo, desamor, Barthes</t>
+          <t>Amor y vínculos afectivos, Muerte y duelo, Monográfico de autor/a</t>
         </is>
       </c>
       <c r="J551" s="2" t="inlineStr"/>
@@ -44093,7 +44093,7 @@
       </c>
       <c r="I552" s="2" t="inlineStr">
         <is>
-          <t>amor, ruptura amorosa, duelo, desamor, Barthes</t>
+          <t>Amor y vínculos afectivos, Muerte y duelo, Monográfico de autor/a</t>
         </is>
       </c>
       <c r="J552" s="2" t="inlineStr"/>
@@ -44162,7 +44162,7 @@
       </c>
       <c r="I553" s="2" t="inlineStr">
         <is>
-          <t>amor, ruptura amorosa, duelo, desamor, Barthes</t>
+          <t>Amor y vínculos afectivos, Muerte y duelo, Monográfico de autor/a</t>
         </is>
       </c>
       <c r="J553" s="2" t="inlineStr"/>
@@ -44233,7 +44233,7 @@
       </c>
       <c r="I554" s="2" t="inlineStr">
         <is>
-          <t>comunes, ecología, economía, bien común</t>
+          <t>Capitalismo, trabajo y economía, Ecología y crisis climática</t>
         </is>
       </c>
       <c r="J554" s="2" t="inlineStr"/>
@@ -44308,7 +44308,7 @@
       </c>
       <c r="I555" s="2" t="inlineStr">
         <is>
-          <t>nostalgia, memoria, tiempo</t>
+          <t>Memoria e historia, Tiempo</t>
         </is>
       </c>
       <c r="J555" s="2" t="inlineStr"/>
@@ -44387,7 +44387,7 @@
       </c>
       <c r="I556" s="2" t="inlineStr">
         <is>
-          <t>salud sexual, educación sexual, juventud</t>
+          <t>Sexualidad y disidencia sexual, Tiempo</t>
         </is>
       </c>
       <c r="J556" s="2" t="inlineStr"/>
@@ -44462,7 +44462,7 @@
       </c>
       <c r="I557" s="2" t="inlineStr">
         <is>
-          <t>salud sexual, educación sexual, juventud</t>
+          <t>Sexualidad y disidencia sexual, Tiempo</t>
         </is>
       </c>
       <c r="J557" s="2" t="inlineStr"/>
@@ -44545,7 +44545,7 @@
       </c>
       <c r="I558" s="2" t="inlineStr">
         <is>
-          <t>salud sexual, educación sexual, juventud</t>
+          <t>Sexualidad y disidencia sexual, Tiempo</t>
         </is>
       </c>
       <c r="J558" s="2" t="inlineStr">
@@ -44628,7 +44628,7 @@
       </c>
       <c r="I559" s="2" t="inlineStr">
         <is>
-          <t>Rodoreda, exposición, literatura catalana</t>
+          <t>Monográfico de autor/a, Arte, Literatura y lectura</t>
         </is>
       </c>
       <c r="J559" s="2" t="inlineStr"/>
@@ -44707,7 +44707,7 @@
       </c>
       <c r="I560" s="2" t="inlineStr">
         <is>
-          <t>tierra, cuatro elementos, mitología, ecología, especial Anagrama</t>
+          <t>Naturaleza y elementos, Mito y relato, Ecología y crisis climática, Formato especial y evento</t>
         </is>
       </c>
       <c r="J560" s="2" t="inlineStr"/>
@@ -44782,7 +44782,7 @@
       </c>
       <c r="I561" s="2" t="inlineStr">
         <is>
-          <t>tierra, cuatro elementos, mitología, ecología, especial Anagrama</t>
+          <t>Naturaleza y elementos, Mito y relato, Ecología y crisis climática, Formato especial y evento</t>
         </is>
       </c>
       <c r="J561" s="2" t="inlineStr"/>
@@ -44861,7 +44861,7 @@
       </c>
       <c r="I562" s="2" t="inlineStr">
         <is>
-          <t>tierra, cuatro elementos, mitología, ecología, especial Anagrama</t>
+          <t>Naturaleza y elementos, Mito y relato, Ecología y crisis climática, Formato especial y evento</t>
         </is>
       </c>
       <c r="J562" s="2" t="inlineStr"/>
@@ -44940,7 +44940,7 @@
       </c>
       <c r="I563" s="2" t="inlineStr">
         <is>
-          <t>tierra, cuatro elementos, mitología, ecología, especial Anagrama</t>
+          <t>Naturaleza y elementos, Mito y relato, Ecología y crisis climática, Formato especial y evento</t>
         </is>
       </c>
       <c r="J563" s="2" t="inlineStr"/>
@@ -45025,7 +45025,7 @@
       </c>
       <c r="I564" s="2" t="inlineStr">
         <is>
-          <t>tierra, cuatro elementos, mitología, ecología, especial Anagrama</t>
+          <t>Naturaleza y elementos, Mito y relato, Ecología y crisis climática, Formato especial y evento</t>
         </is>
       </c>
       <c r="J564" s="2" t="inlineStr"/>
@@ -45100,7 +45100,7 @@
       </c>
       <c r="I565" s="2" t="inlineStr">
         <is>
-          <t>tierra, cuatro elementos, mitología, ecología, especial Anagrama</t>
+          <t>Naturaleza y elementos, Mito y relato, Ecología y crisis climática, Formato especial y evento</t>
         </is>
       </c>
       <c r="J565" s="2" t="inlineStr"/>
@@ -45175,7 +45175,7 @@
       </c>
       <c r="I566" s="2" t="inlineStr">
         <is>
-          <t>aire, cuatro elementos, levedad, mitología, especial Anagrama</t>
+          <t>Naturaleza y elementos, Existencia y contingencia, Mito y relato, Formato especial y evento</t>
         </is>
       </c>
       <c r="J566" s="2" t="inlineStr"/>
@@ -45264,7 +45264,7 @@
       </c>
       <c r="I567" s="2" t="inlineStr">
         <is>
-          <t>aire, cuatro elementos, levedad, mitología, especial Anagrama</t>
+          <t>Naturaleza y elementos, Existencia y contingencia, Mito y relato, Formato especial y evento</t>
         </is>
       </c>
       <c r="J567" s="2" t="inlineStr"/>
@@ -45339,7 +45339,7 @@
       </c>
       <c r="I568" s="2" t="inlineStr">
         <is>
-          <t>aire, cuatro elementos, levedad, mitología, especial Anagrama</t>
+          <t>Naturaleza y elementos, Existencia y contingencia, Mito y relato, Formato especial y evento</t>
         </is>
       </c>
       <c r="J568" s="2" t="inlineStr"/>
@@ -45418,7 +45418,7 @@
       </c>
       <c r="I569" s="2" t="inlineStr">
         <is>
-          <t>aire, cuatro elementos, levedad, mitología, especial Anagrama</t>
+          <t>Naturaleza y elementos, Existencia y contingencia, Mito y relato, Formato especial y evento</t>
         </is>
       </c>
       <c r="J569" s="2" t="inlineStr"/>
@@ -45503,7 +45503,7 @@
       </c>
       <c r="I570" s="2" t="inlineStr">
         <is>
-          <t>aire, cuatro elementos, levedad, mitología, especial Anagrama</t>
+          <t>Naturaleza y elementos, Existencia y contingencia, Mito y relato, Formato especial y evento</t>
         </is>
       </c>
       <c r="J570" s="2" t="inlineStr"/>
@@ -45588,7 +45588,7 @@
       </c>
       <c r="I571" s="2" t="inlineStr">
         <is>
-          <t>aire, cuatro elementos, levedad, mitología, especial Anagrama</t>
+          <t>Naturaleza y elementos, Existencia y contingencia, Mito y relato, Formato especial y evento</t>
         </is>
       </c>
       <c r="J571" s="2" t="inlineStr"/>
@@ -45673,7 +45673,7 @@
       </c>
       <c r="I572" s="2" t="inlineStr">
         <is>
-          <t>aire, cuatro elementos, levedad, mitología, especial Anagrama</t>
+          <t>Naturaleza y elementos, Existencia y contingencia, Mito y relato, Formato especial y evento</t>
         </is>
       </c>
       <c r="J572" s="2" t="inlineStr"/>
@@ -45754,7 +45754,7 @@
       </c>
       <c r="I573" s="2" t="inlineStr">
         <is>
-          <t>aire, cuatro elementos, levedad, mitología, especial Anagrama</t>
+          <t>Naturaleza y elementos, Existencia y contingencia, Mito y relato, Formato especial y evento</t>
         </is>
       </c>
       <c r="J573" s="2" t="inlineStr"/>
@@ -45829,7 +45829,7 @@
       </c>
       <c r="I574" s="2" t="inlineStr">
         <is>
-          <t>agua, cuatro elementos, mitología, presocráticos, especial Anagrama</t>
+          <t>Naturaleza y elementos, Mito y relato, Filosofía y epistemología, Formato especial y evento</t>
         </is>
       </c>
       <c r="J574" s="2" t="inlineStr"/>
@@ -45904,7 +45904,7 @@
       </c>
       <c r="I575" s="2" t="inlineStr">
         <is>
-          <t>agua, cuatro elementos, mitología, presocráticos, especial Anagrama</t>
+          <t>Naturaleza y elementos, Mito y relato, Filosofía y epistemología, Formato especial y evento</t>
         </is>
       </c>
       <c r="J575" s="2" t="inlineStr"/>
@@ -45979,7 +45979,7 @@
       </c>
       <c r="I576" s="2" t="inlineStr">
         <is>
-          <t>agua, cuatro elementos, mitología, presocráticos, especial Anagrama</t>
+          <t>Naturaleza y elementos, Mito y relato, Filosofía y epistemología, Formato especial y evento</t>
         </is>
       </c>
       <c r="J576" s="2" t="inlineStr"/>
@@ -46058,7 +46058,7 @@
       </c>
       <c r="I577" s="2" t="inlineStr">
         <is>
-          <t>agua, cuatro elementos, mitología, presocráticos, especial Anagrama</t>
+          <t>Naturaleza y elementos, Mito y relato, Filosofía y epistemología, Formato especial y evento</t>
         </is>
       </c>
       <c r="J577" s="2" t="inlineStr"/>
@@ -46143,7 +46143,7 @@
       </c>
       <c r="I578" s="2" t="inlineStr">
         <is>
-          <t>agua, cuatro elementos, mitología, presocráticos, especial Anagrama</t>
+          <t>Naturaleza y elementos, Mito y relato, Filosofía y epistemología, Formato especial y evento</t>
         </is>
       </c>
       <c r="J578" s="2" t="inlineStr"/>
@@ -46228,7 +46228,7 @@
       </c>
       <c r="I579" s="2" t="inlineStr">
         <is>
-          <t>agua, cuatro elementos, mitología, presocráticos, especial Anagrama</t>
+          <t>Naturaleza y elementos, Mito y relato, Filosofía y epistemología, Formato especial y evento</t>
         </is>
       </c>
       <c r="J579" s="2" t="inlineStr"/>
@@ -46303,7 +46303,7 @@
       </c>
       <c r="I580" s="2" t="inlineStr">
         <is>
-          <t>agua, cuatro elementos, mitología, presocráticos, especial Anagrama</t>
+          <t>Naturaleza y elementos, Mito y relato, Filosofía y epistemología, Formato especial y evento</t>
         </is>
       </c>
       <c r="J580" s="2" t="inlineStr"/>
@@ -46382,7 +46382,7 @@
       </c>
       <c r="I581" s="2" t="inlineStr">
         <is>
-          <t>agua, cuatro elementos, mitología, presocráticos, especial Anagrama</t>
+          <t>Naturaleza y elementos, Mito y relato, Filosofía y epistemología, Formato especial y evento</t>
         </is>
       </c>
       <c r="J581" s="2" t="inlineStr"/>
@@ -46467,7 +46467,7 @@
       </c>
       <c r="I582" s="2" t="inlineStr">
         <is>
-          <t>agua, cuatro elementos, mitología, presocráticos, especial Anagrama</t>
+          <t>Naturaleza y elementos, Mito y relato, Filosofía y epistemología, Formato especial y evento</t>
         </is>
       </c>
       <c r="J582" s="2" t="inlineStr"/>
@@ -46552,7 +46552,7 @@
       </c>
       <c r="I583" s="2" t="inlineStr">
         <is>
-          <t>agua, cuatro elementos, mitología, presocráticos, especial Anagrama</t>
+          <t>Naturaleza y elementos, Mito y relato, Filosofía y epistemología, Formato especial y evento</t>
         </is>
       </c>
       <c r="J583" s="2" t="inlineStr"/>
@@ -46627,7 +46627,7 @@
       </c>
       <c r="I584" s="2" t="inlineStr">
         <is>
-          <t>escucha, interlocutor, Carmen Martín Gaite, crossover, FIL Guadalajara</t>
+          <t>Sonido y escucha, Lenguaje y escritura, Monográfico de autor/a, Formato especial y evento</t>
         </is>
       </c>
       <c r="J584" s="2" t="inlineStr"/>
@@ -46794,7 +46794,7 @@
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>presentación, amor, amistad, Barthes</t>
+          <t>Formato especial y evento, Amor y vínculos afectivos, Monográfico de autor/a</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
@@ -46847,7 +46847,7 @@
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>ausencia, amor, memoria, familia</t>
+          <t>Muerte y duelo, Amor y vínculos afectivos, Memoria e historia, Familia y maternidad</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
@@ -46900,7 +46900,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>exuberancia, dinero, clase social, influencers, intimidad</t>
+          <t>Arte, Capitalismo, trabajo y economía, Identidad y clase social, Medios, redes e internet, Amor y vínculos afectivos</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -46953,7 +46953,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>desrealidad, espacio, arquitectura, jerarquías sociales, cine</t>
+          <t>Existencia y contingencia, Espacio, límite y frontera, Ciudad y urbanismo, Identidad y clase social, Cine y series</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -47010,7 +47010,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>cartas, correspondencia, escritura, amor</t>
+          <t>Lenguaje y escritura, Amor y vínculos afectivos</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -47063,7 +47063,7 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>salida, crisis amorosa, matrimonio, arte</t>
+          <t>Viaje y desplazamiento, Amor y vínculos afectivos, Arte</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -47116,7 +47116,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>jardín, naturaleza, fotografía, escritura, Barthes</t>
+          <t>Naturaleza y elementos, Fotografía e imagen, Lenguaje y escritura, Monográfico de autor/a</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -47169,7 +47169,7 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>cartas, arte, escritura asémica, correspondencia</t>
+          <t>Lenguaje y escritura, Arte</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
@@ -47222,7 +47222,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>noche, oscuridad, abusos sexuales, urbanismo feminista, literatura japonesa</t>
+          <t>Tiempo, Miedo y vulnerabilidad, Violencia y daño, Ciudad y urbanismo, Literatura y lectura</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -47275,7 +47275,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>traducción, lenguaje, identidad</t>
+          <t>Lenguaje y escritura, Identidad y clase social</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -47328,7 +47328,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>declaración, cortejo, amor, cine</t>
+          <t>Amor y vínculos afectivos, Cine y series</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -47381,7 +47381,7 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>noche, sueño, escepticismo, capitalismo, mitología</t>
+          <t>Tiempo, Existencia y contingencia, Filosofía y epistemología, Capitalismo, trabajo y economía, Mito y relato</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -47434,7 +47434,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>recuerdo, olvido, lenguaje, series</t>
+          <t>Memoria e historia, Lenguaje y escritura, Cine y series</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -47487,7 +47487,7 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>dolor, enfermedad, cáncer, vulnerabilidad</t>
+          <t>Emociones y afectos, Cuerpo y mirada, Miedo y vulnerabilidad</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
@@ -47540,7 +47540,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>dolor ajeno, ética médica, vulnerabilidad</t>
+          <t>Emociones y afectos, Ética y moral, Miedo y vulnerabilidad</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -47593,7 +47593,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>amistad, vínculos, toxicidad, Barthes</t>
+          <t>Amor y vínculos afectivos, Monográfico de autor/a</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -47646,7 +47646,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>lectura, ficción, erotismo, arte y moral</t>
+          <t>Literatura y lectura, Narración, ficción y autoficción, Deseo y erotismo, Ética y moral</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -47699,7 +47699,7 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>mito, ideología, publicidad, Barthes</t>
+          <t>Mito y relato, Política y actualidad, Medios, redes e internet, Monográfico de autor/a</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
@@ -47752,7 +47752,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>fiesta, alegría, tiempo, trabajo</t>
+          <t>Emociones y afectos, Tiempo, Capitalismo, trabajo y economía</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -47805,7 +47805,7 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>Annie Ernaux, autoficción, orígenes, clase social</t>
+          <t>Monográfico de autor/a, Narración, ficción y autoficción, Memoria e historia, Identidad y clase social</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
@@ -47858,7 +47858,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>exilio, lengua, imaginario amoroso, Historia</t>
+          <t>Viaje y desplazamiento, Lenguaje y escritura, Amor y vínculos afectivos, Memoria e historia</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -47911,7 +47911,7 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>Annie Ernaux, clase social, tránsfuga de clase, universidad</t>
+          <t>Monográfico de autor/a, Identidad y clase social</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
@@ -47964,7 +47964,7 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>Annie Ernaux, familia, aborto, escritura, duelo</t>
+          <t>Monográfico de autor/a, Familia y maternidad, Feminismo y género, Lenguaje y escritura, Muerte y duelo</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
@@ -48017,7 +48017,7 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>encuentro, duelo amoroso, urbanismo, espacio público</t>
+          <t>Amor y vínculos afectivos, Ciudad y urbanismo</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
@@ -48070,7 +48070,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>Annie Ernaux, pasión amorosa, deseo, celos, sexo</t>
+          <t>Monográfico de autor/a, Amor y vínculos afectivos, Deseo y erotismo, Sexualidad y disidencia sexual</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -48123,7 +48123,7 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>escucha, sonido, ruido, ética, radio</t>
+          <t>Sonido y escucha, Ética y moral</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
@@ -48176,7 +48176,7 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>ruinas, memoria, ciudad, poesía, antropología</t>
+          <t>Ciudad y urbanismo, Memoria e historia, Literatura y lectura, Filosofía y epistemología</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
@@ -48229,7 +48229,7 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>Katherine Mansfield, modernismo, cuento, biografía</t>
+          <t>Monográfico de autor/a, Arte, Literatura y lectura, Narración, ficción y autoficción</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
@@ -48282,7 +48282,7 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>primavera, mito, crisis climática, mundo rural</t>
+          <t>Tiempo, Mito y relato, Ecología y crisis climática, Ruralidad y territorio</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
@@ -48335,7 +48335,7 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>Janet Frame, salud mental, autobiografía, Nueva Zelanda</t>
+          <t>Monográfico de autor/a, Cuerpo y mirada, Narración, ficción y autoficción, Viaje y desplazamiento</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
@@ -48388,7 +48388,7 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>ligar, deseo, vulnerabilidad, aislacionismo amoroso, ética</t>
+          <t>Amor y vínculos afectivos, Deseo y erotismo, Miedo y vulnerabilidad, Soledad y aislamiento, Ética y moral</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
@@ -48441,7 +48441,7 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>lectura, lector, bibliotecas, clásicos</t>
+          <t>Literatura y lectura</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
@@ -48494,7 +48494,7 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>agua, abismo, mito, filosofía griega, capitalismo</t>
+          <t>Naturaleza y elementos, Existencia y contingencia, Mito y relato, Filosofía y epistemología, Capitalismo, trabajo y economía</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
@@ -48547,7 +48547,7 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>juego, infancia, violencia, Feria del Libro de Madrid</t>
+          <t>Emociones y afectos, Familia y maternidad, Violencia y daño, Formato especial y evento</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
@@ -48600,7 +48600,7 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>daño, crueldad, tortura, obsesión, culpa</t>
+          <t>Violencia y daño, Emociones y afectos, Ética y moral</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
@@ -48653,7 +48653,7 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>verano, memoria, turismo, identidad, Barthes</t>
+          <t>Tiempo, Memoria e historia, Viaje y desplazamiento, Identidad y clase social, Monográfico de autor/a</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
@@ -48706,7 +48706,7 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>amor, ficción, deseo autotélico, emociones</t>
+          <t>Amor y vínculos afectivos, Narración, ficción y autoficción, Deseo y erotismo, Emociones y afectos</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
@@ -48763,7 +48763,7 @@
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>sexo, educación sexual, pornografía, intimidad, cine</t>
+          <t>Sexualidad y disidencia sexual, Amor y vínculos afectivos, Cine y series</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
@@ -48820,7 +48820,7 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>rapto, caída, mito, inclinación, amor</t>
+          <t>Violencia y daño, Existencia y contingencia, Mito y relato, Filosofía y epistemología, Amor y vínculos afectivos</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
@@ -48877,7 +48877,7 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>imagen, violencia, muerte, Gaza, fotografía</t>
+          <t>Fotografía e imagen, Violencia y daño, Muerte y duelo, Política y actualidad</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
@@ -48934,7 +48934,7 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>contingencia, azar, posibilidad</t>
+          <t>Existencia y contingencia</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
@@ -48995,7 +48995,7 @@
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>luz, mirada, percepción</t>
+          <t>Naturaleza y elementos, Cuerpo y mirada, Filosofía y epistemología</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
@@ -49056,7 +49056,7 @@
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>deseo, consumo, publicidad, sexo, epistemología</t>
+          <t>Deseo y erotismo, Capitalismo, trabajo y economía, Medios, redes e internet, Sexualidad y disidencia sexual, Filosofía y epistemología</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
@@ -49113,7 +49113,7 @@
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>narración, memoria, identidad, tiempo, autoengaño</t>
+          <t>Narración, ficción y autoficción, Memoria e historia, Identidad y clase social, Tiempo, Ética y moral</t>
         </is>
       </c>
       <c r="I45" s="2" t="inlineStr">
@@ -49170,7 +49170,7 @@
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>nombre propio, identidad, memoria, dictadura, comunidad trans</t>
+          <t>Lenguaje y escritura, Identidad y clase social, Memoria e historia, Sexualidad y disidencia sexual</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
@@ -49227,7 +49227,7 @@
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>finales, angustia, muerte, fin de la historia, éxito</t>
+          <t>Tiempo, Miedo y vulnerabilidad, Muerte y duelo, Política y actualidad, Emociones y afectos</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
@@ -49284,7 +49284,7 @@
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>fatiga, pereza, trabajo, agotamiento emocional, Barthes</t>
+          <t>Emociones y afectos, Capitalismo, trabajo y economía, Monográfico de autor/a</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
@@ -49341,7 +49341,7 @@
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>imagen, intimidad, redes sociales, influencers, ética de la mirada</t>
+          <t>Fotografía e imagen, Amor y vínculos afectivos, Medios, redes e internet, Ética y moral</t>
         </is>
       </c>
       <c r="I49" s="2" t="inlineStr">
@@ -49398,7 +49398,7 @@
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>herencia, duelo, clase social, posteridad</t>
+          <t>Memoria e historia, Muerte y duelo, Identidad y clase social</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr">
@@ -49455,7 +49455,7 @@
       </c>
       <c r="H51" s="2" t="inlineStr">
         <is>
-          <t>maternidad, aborto, abandono, arrepentimiento, mito</t>
+          <t>Familia y maternidad, Feminismo y género, Amor y vínculos afectivos, Emociones y afectos, Mito y relato</t>
         </is>
       </c>
       <c r="I51" s="2" t="inlineStr">
@@ -49512,7 +49512,7 @@
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>mirar atrás, memoria, tiempo, arrepentimiento, mito</t>
+          <t>Memoria e historia, Tiempo, Emociones y afectos, Mito y relato</t>
         </is>
       </c>
       <c r="I52" s="2" t="inlineStr">
@@ -49569,7 +49569,7 @@
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>memoria histórica, olvido, franquismo, memoria colectiva</t>
+          <t>Memoria e historia</t>
         </is>
       </c>
       <c r="I53" s="2" t="inlineStr">
@@ -49626,7 +49626,7 @@
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>tabú, transgresión, canibalismo, virginidad, ruralidad queer</t>
+          <t>Ética y moral, Violencia y daño, Sexualidad y disidencia sexual, Ruralidad y territorio</t>
         </is>
       </c>
       <c r="I54" s="2" t="inlineStr">
@@ -49683,7 +49683,7 @@
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t>orientación, fenomenología queer, norte, orientalismo</t>
+          <t>Sexualidad y disidencia sexual, Espacio, límite y frontera, Colonialismo y poscolonialismo</t>
         </is>
       </c>
       <c r="I55" s="2" t="inlineStr">
@@ -49740,7 +49740,7 @@
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>inercia, amor, razones, existencia</t>
+          <t>Existencia y contingencia, Amor y vínculos afectivos, Filosofía y epistemología</t>
         </is>
       </c>
       <c r="I56" s="2" t="inlineStr">
@@ -49797,7 +49797,7 @@
       </c>
       <c r="H57" s="2" t="inlineStr">
         <is>
-          <t>dependencia, competición, ser segundo, jerarquía afectiva</t>
+          <t>Amor y vínculos afectivos, Emociones y afectos, Feminismo y género</t>
         </is>
       </c>
       <c r="I57" s="2" t="inlineStr">
@@ -49854,7 +49854,7 @@
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
-          <t>amor, lenguaje, Barthes, afasia</t>
+          <t>Amor y vínculos afectivos, Lenguaje y escritura, Monográfico de autor/a</t>
         </is>
       </c>
       <c r="I58" s="2" t="inlineStr">
@@ -49911,7 +49911,7 @@
       </c>
       <c r="H59" s="2" t="inlineStr">
         <is>
-          <t>Gaza, violencia, mal, decolonial, ética</t>
+          <t>Política y actualidad, Violencia y daño, Ética y moral, Colonialismo y poscolonialismo</t>
         </is>
       </c>
       <c r="I59" s="2" t="inlineStr">
@@ -49968,7 +49968,7 @@
       </c>
       <c r="H60" s="2" t="inlineStr">
         <is>
-          <t>matrimonio, mito, violencia sexual, herencia, miedo, episodio con invitada</t>
+          <t>Amor y vínculos afectivos, Mito y relato, Violencia y daño, Memoria e historia, Miedo y vulnerabilidad, Formato especial y evento</t>
         </is>
       </c>
       <c r="I60" s="2" t="inlineStr">
@@ -50025,7 +50025,7 @@
       </c>
       <c r="H61" s="2" t="inlineStr">
         <is>
-          <t>soledad, lenguaje, despoblación, política</t>
+          <t>Soledad y aislamiento, Lenguaje y escritura, Ruralidad y territorio, Política y actualidad</t>
         </is>
       </c>
       <c r="I61" s="2" t="inlineStr">
@@ -50082,7 +50082,7 @@
       </c>
       <c r="H62" s="2" t="inlineStr">
         <is>
-          <t>pérdida, olvido, memoria, Barthes</t>
+          <t>Muerte y duelo, Memoria e historia, Monográfico de autor/a</t>
         </is>
       </c>
       <c r="I62" s="2" t="inlineStr">
@@ -50139,7 +50139,7 @@
       </c>
       <c r="H63" s="2" t="inlineStr">
         <is>
-          <t>caminar, exilio, filosofía, viaje, FIL Guadalajara</t>
+          <t>Viaje y desplazamiento, Filosofía y epistemología, Formato especial y evento</t>
         </is>
       </c>
       <c r="I63" s="2" t="inlineStr">
@@ -50196,7 +50196,7 @@
       </c>
       <c r="H64" s="2" t="inlineStr">
         <is>
-          <t>amor contemporáneo, deseo, pareja, FIL Guadalajara, episodio con invitada</t>
+          <t>Amor y vínculos afectivos, Deseo y erotismo, Formato especial y evento</t>
         </is>
       </c>
       <c r="I64" s="2" t="inlineStr">
@@ -50253,7 +50253,7 @@
       </c>
       <c r="H65" s="2" t="inlineStr">
         <is>
-          <t>comienzos, tiempo, mito, prehistoria, narración</t>
+          <t>Tiempo, Mito y relato, Narración, ficción y autoficción</t>
         </is>
       </c>
       <c r="I65" s="2" t="inlineStr">
@@ -50310,7 +50310,7 @@
       </c>
       <c r="H66" s="2" t="inlineStr">
         <is>
-          <t>afuera, lugar social, escritura, ruralidad, adentro/afuera</t>
+          <t>Espacio, límite y frontera, Identidad y clase social, Lenguaje y escritura, Ruralidad y territorio</t>
         </is>
       </c>
       <c r="I66" s="2" t="inlineStr">
@@ -50367,7 +50367,7 @@
       </c>
       <c r="H67" s="2" t="inlineStr">
         <is>
-          <t>espera, amor, Barthes, Penélope, tiempo</t>
+          <t>Tiempo, Amor y vínculos afectivos, Monográfico de autor/a, Mito y relato</t>
         </is>
       </c>
       <c r="I67" s="2" t="inlineStr">
@@ -50424,7 +50424,7 @@
       </c>
       <c r="H68" s="2" t="inlineStr">
         <is>
-          <t>vacío, España vaciada, espacio, horror vacui, Barthes</t>
+          <t>Existencia y contingencia, Ruralidad y territorio, Espacio, límite y frontera, Arte, Monográfico de autor/a</t>
         </is>
       </c>
       <c r="I68" s="2" t="inlineStr">
@@ -50481,7 +50481,7 @@
       </c>
       <c r="H69" s="2" t="inlineStr">
         <is>
-          <t>mirada aérea, paisaje, costa, poesía, fotografía</t>
+          <t>Cuerpo y mirada, Naturaleza y elementos, Espacio, límite y frontera, Literatura y lectura, Fotografía e imagen</t>
         </is>
       </c>
       <c r="I69" s="2" t="inlineStr">
@@ -50538,7 +50538,7 @@
       </c>
       <c r="H70" s="2" t="inlineStr">
         <is>
-          <t>realidad, ficción, desinformación, series, internet</t>
+          <t>Existencia y contingencia, Narración, ficción y autoficción, Medios, redes e internet, Cine y series</t>
         </is>
       </c>
       <c r="I70" s="2" t="inlineStr">
@@ -50595,7 +50595,7 @@
       </c>
       <c r="H71" s="2" t="inlineStr">
         <is>
-          <t>amor no correspondido, rechazo, Barthes, psicología</t>
+          <t>Amor y vínculos afectivos, Monográfico de autor/a, Filosofía y epistemología</t>
         </is>
       </c>
       <c r="I71" s="2" t="inlineStr">
@@ -50652,7 +50652,7 @@
       </c>
       <c r="H72" s="2" t="inlineStr">
         <is>
-          <t>límite, transgresión, liminalidad, frontera, lenguaje</t>
+          <t>Espacio, límite y frontera, Violencia y daño, Lenguaje y escritura</t>
         </is>
       </c>
       <c r="I72" s="2" t="inlineStr">
@@ -50709,7 +50709,7 @@
       </c>
       <c r="H73" s="2" t="inlineStr">
         <is>
-          <t>trabajo, artesanía, arte, marxismo, división sexual del trabajo, epistemología</t>
+          <t>Capitalismo, trabajo y economía, Arte, Feminismo y género, Filosofía y epistemología</t>
         </is>
       </c>
       <c r="I73" s="2" t="inlineStr">
@@ -50766,7 +50766,7 @@
       </c>
       <c r="H74" s="2" t="inlineStr">
         <is>
-          <t>plan, planificación, bricoleur, Estado, urbanismo</t>
+          <t>Existencia y contingencia, Arte, Política y actualidad, Ciudad y urbanismo</t>
         </is>
       </c>
       <c r="I74" s="2" t="inlineStr">
@@ -50823,7 +50823,7 @@
       </c>
       <c r="H75" s="2" t="inlineStr">
         <is>
-          <t>delirio amoroso, erotomanía, locura femenina, Barthes, literatura</t>
+          <t>Amor y vínculos afectivos, Feminismo y género, Monográfico de autor/a, Literatura y lectura</t>
         </is>
       </c>
       <c r="I75" s="2" t="inlineStr">
@@ -50880,7 +50880,7 @@
       </c>
       <c r="H76" s="2" t="inlineStr">
         <is>
-          <t>verano, ruralidad, huida, tiempo, ocio</t>
+          <t>Tiempo, Ruralidad y territorio, Viaje y desplazamiento, Emociones y afectos</t>
         </is>
       </c>
       <c r="I76" s="2" t="inlineStr">
@@ -50937,7 +50937,7 @@
       </c>
       <c r="H77" s="2" t="inlineStr">
         <is>
-          <t>responsabilidad moral, violencia, víctima, Gaza, ética, acción y omisión</t>
+          <t>Ética y moral, Violencia y daño, Política y actualidad</t>
         </is>
       </c>
       <c r="I77" s="2" t="inlineStr">
@@ -50994,7 +50994,7 @@
       </c>
       <c r="H78" s="2" t="inlineStr">
         <is>
-          <t>fragmento, brevedad, glosa, escritura, Barthes</t>
+          <t>Lenguaje y escritura, Formato especial y evento, Monográfico de autor/a</t>
         </is>
       </c>
       <c r="I78" s="2" t="inlineStr">
@@ -51051,7 +51051,7 @@
       </c>
       <c r="H79" s="2" t="inlineStr">
         <is>
-          <t>mirada, voyeurismo, fotografía, arte, deseo, performance</t>
+          <t>Cuerpo y mirada, Fotografía e imagen, Arte, Deseo y erotismo</t>
         </is>
       </c>
       <c r="I79" s="2" t="inlineStr">
@@ -51108,7 +51108,7 @@
       </c>
       <c r="H80" s="2" t="inlineStr">
         <is>
-          <t>familia, abolición de la familia, extrema derecha, políticas públicas, feminismo</t>
+          <t>Familia y maternidad, Política y actualidad, Feminismo y género</t>
         </is>
       </c>
       <c r="I80" s="2" t="inlineStr">
@@ -51165,7 +51165,7 @@
       </c>
       <c r="H81" s="2" t="inlineStr">
         <is>
-          <t>sacrificio, religión, violencia, ética, política</t>
+          <t>Ética y moral, Filosofía y epistemología, Violencia y daño, Política y actualidad</t>
         </is>
       </c>
       <c r="I81" s="2" t="inlineStr">
@@ -51222,7 +51222,7 @@
       </c>
       <c r="H82" s="2" t="inlineStr">
         <is>
-          <t>conocimiento del otro, amor, misterio, secreto</t>
+          <t>Filosofía y epistemología, Amor y vínculos afectivos, Existencia y contingencia, Miedo y vulnerabilidad</t>
         </is>
       </c>
       <c r="I82" s="2" t="inlineStr">
@@ -51279,7 +51279,7 @@
       </c>
       <c r="H83" s="2" t="inlineStr">
         <is>
-          <t>Barthes, homosexualidad, colonialismo, turismo sexual, biografía</t>
+          <t>Monográfico de autor/a, Sexualidad y disidencia sexual, Colonialismo y poscolonialismo, Narración, ficción y autoficción</t>
         </is>
       </c>
       <c r="I83" s="2" t="inlineStr">
@@ -51336,7 +51336,7 @@
       </c>
       <c r="H84" s="2" t="inlineStr">
         <is>
-          <t>categorías, lenguaje, nominalismo, clasificación, metafísica</t>
+          <t>Filosofía y epistemología, Lenguaje y escritura</t>
         </is>
       </c>
       <c r="I84" s="2" t="inlineStr">
@@ -51393,7 +51393,7 @@
       </c>
       <c r="H85" s="2" t="inlineStr">
         <is>
-          <t>compasión, ética, alteridad, dolor</t>
+          <t>Ética y moral, Filosofía y epistemología, Emociones y afectos</t>
         </is>
       </c>
       <c r="I85" s="2" t="inlineStr">
@@ -51450,7 +51450,7 @@
       </c>
       <c r="H86" s="2" t="inlineStr">
         <is>
-          <t>silencio, poder, violencia, familia, secreto</t>
+          <t>Sonido y escucha, Política y actualidad, Violencia y daño, Familia y maternidad, Miedo y vulnerabilidad</t>
         </is>
       </c>
       <c r="I86" s="2" t="inlineStr">
@@ -51507,7 +51507,7 @@
       </c>
       <c r="H87" s="2" t="inlineStr">
         <is>
-          <t>silencio, gesto, arte, filosofía, Wittgenstein</t>
+          <t>Sonido y escucha, Cuerpo y mirada, Arte, Filosofía y epistemología, Monográfico de autor/a</t>
         </is>
       </c>
       <c r="I87" s="2" t="inlineStr">
@@ -51564,7 +51564,7 @@
       </c>
       <c r="H88" s="2" t="inlineStr">
         <is>
-          <t>miedo, emociones, razón, política</t>
+          <t>Miedo y vulnerabilidad, Emociones y afectos, Filosofía y epistemología, Política y actualidad</t>
         </is>
       </c>
       <c r="I88" s="2" t="inlineStr">
@@ -51621,7 +51621,7 @@
       </c>
       <c r="H89" s="2" t="inlineStr">
         <is>
-          <t>mar, poesía, lenguaje, fenomenología, literatura</t>
+          <t>Naturaleza y elementos, Literatura y lectura, Lenguaje y escritura, Filosofía y epistemología</t>
         </is>
       </c>
       <c r="I89" s="2" t="inlineStr">
@@ -51678,7 +51678,7 @@
       </c>
       <c r="H90" s="2" t="inlineStr">
         <is>
-          <t>autoría, muerte del autor, feminismo, poscolonial, memoria, subalternidad</t>
+          <t>Narración, ficción y autoficción, Feminismo y género, Colonialismo y poscolonialismo, Memoria e historia</t>
         </is>
       </c>
       <c r="I90" s="2" t="inlineStr">
@@ -51735,7 +51735,7 @@
       </c>
       <c r="H91" s="2" t="inlineStr">
         <is>
-          <t>museo, museología crítica, colonialismo, arte, ética</t>
+          <t>Arte, Colonialismo y poscolonialismo, Ética y moral</t>
         </is>
       </c>
       <c r="I91" s="2" t="inlineStr">
@@ -51792,7 +51792,7 @@
       </c>
       <c r="H92" s="2" t="inlineStr">
         <is>
-          <t>ruralidad, amor, espacio, masculinidad, deseo, homosexualidad, queer</t>
+          <t>Ruralidad y territorio, Amor y vínculos afectivos, Espacio, límite y frontera, Feminismo y género, Deseo y erotismo, Sexualidad y disidencia sexual</t>
         </is>
       </c>
       <c r="I92" s="2" t="inlineStr">
@@ -51849,7 +51849,7 @@
       </c>
       <c r="H93" s="2" t="inlineStr">
         <is>
-          <t>crueldad, ética, literatura, violencia, función de la ficción</t>
+          <t>Violencia y daño, Ética y moral, Literatura y lectura, Narración, ficción y autoficción</t>
         </is>
       </c>
       <c r="I93" s="2" t="inlineStr">
@@ -51906,7 +51906,7 @@
       </c>
       <c r="H94" s="2" t="inlineStr">
         <is>
-          <t>amor, ruptura amorosa, duelo, desamor, Barthes</t>
+          <t>Amor y vínculos afectivos, Muerte y duelo, Monográfico de autor/a</t>
         </is>
       </c>
       <c r="I94" s="2" t="inlineStr">
@@ -51961,7 +51961,7 @@
       </c>
       <c r="H95" s="2" t="inlineStr">
         <is>
-          <t>comunes, ecología, economía, bien común</t>
+          <t>Capitalismo, trabajo y economía, Ecología y crisis climática</t>
         </is>
       </c>
       <c r="I95" s="2" t="inlineStr">
@@ -52016,7 +52016,7 @@
       </c>
       <c r="H96" s="2" t="inlineStr">
         <is>
-          <t>nostalgia, memoria, tiempo</t>
+          <t>Memoria e historia, Tiempo</t>
         </is>
       </c>
       <c r="I96" s="2" t="inlineStr">
@@ -52071,7 +52071,7 @@
       </c>
       <c r="H97" s="2" t="inlineStr">
         <is>
-          <t>salud sexual, educación sexual, juventud</t>
+          <t>Sexualidad y disidencia sexual, Tiempo</t>
         </is>
       </c>
       <c r="I97" s="2" t="inlineStr">
@@ -52126,7 +52126,7 @@
       </c>
       <c r="H98" s="2" t="inlineStr">
         <is>
-          <t>Rodoreda, exposición, literatura catalana</t>
+          <t>Monográfico de autor/a, Arte, Literatura y lectura</t>
         </is>
       </c>
       <c r="I98" s="2" t="inlineStr">
@@ -52181,7 +52181,7 @@
       </c>
       <c r="H99" s="2" t="inlineStr">
         <is>
-          <t>fuego, cuatro elementos, especial Anagrama</t>
+          <t>Naturaleza y elementos, Formato especial y evento</t>
         </is>
       </c>
       <c r="I99" s="2" t="inlineStr">
@@ -52240,7 +52240,7 @@
       </c>
       <c r="H100" s="2" t="inlineStr">
         <is>
-          <t>tierra, cuatro elementos, mitología, ecología, especial Anagrama</t>
+          <t>Naturaleza y elementos, Mito y relato, Ecología y crisis climática, Formato especial y evento</t>
         </is>
       </c>
       <c r="I100" s="2" t="inlineStr">
@@ -52295,7 +52295,7 @@
       </c>
       <c r="H101" s="2" t="inlineStr">
         <is>
-          <t>aire, cuatro elementos, levedad, mitología, especial Anagrama</t>
+          <t>Naturaleza y elementos, Existencia y contingencia, Mito y relato, Formato especial y evento</t>
         </is>
       </c>
       <c r="I101" s="2" t="inlineStr">
@@ -52350,7 +52350,7 @@
       </c>
       <c r="H102" s="2" t="inlineStr">
         <is>
-          <t>agua, cuatro elementos, mitología, presocráticos, especial Anagrama</t>
+          <t>Naturaleza y elementos, Mito y relato, Filosofía y epistemología, Formato especial y evento</t>
         </is>
       </c>
       <c r="I102" s="2" t="inlineStr">
@@ -52405,7 +52405,7 @@
       </c>
       <c r="H103" s="2" t="inlineStr">
         <is>
-          <t>escucha, interlocutor, Carmen Martín Gaite, crossover, FIL Guadalajara</t>
+          <t>Sonido y escucha, Lenguaje y escritura, Monográfico de autor/a, Formato especial y evento</t>
         </is>
       </c>
       <c r="I103" s="2" t="inlineStr">

--- a/podcast-data/Punzadas_Sonoras_referencias.xlsx
+++ b/podcast-data/Punzadas_Sonoras_referencias.xlsx
@@ -13164,21 +13164,9 @@
           <t>sin datos</t>
         </is>
       </c>
-      <c r="O158" s="2" t="inlineStr">
-        <is>
-          <t>Fancy Ediciones</t>
-        </is>
-      </c>
-      <c r="P158" s="2" t="inlineStr">
-        <is>
-          <t>2007</t>
-        </is>
-      </c>
-      <c r="Q158" s="2" t="inlineStr">
-        <is>
-          <t>MCU — inferido</t>
-        </is>
-      </c>
+      <c r="O158" s="2" t="inlineStr"/>
+      <c r="P158" s="2" t="inlineStr"/>
+      <c r="Q158" s="2" t="inlineStr"/>
       <c r="R158" s="2" t="inlineStr">
         <is>
           <t>no — título normalizado o inferido</t>
@@ -25421,7 +25409,7 @@
       </c>
       <c r="P308" s="2" t="inlineStr">
         <is>
-          <t>2011</t>
+          <t>2020</t>
         </is>
       </c>
       <c r="Q308" s="2" t="inlineStr">
@@ -25860,21 +25848,9 @@
           <t>sin datos</t>
         </is>
       </c>
-      <c r="O313" s="2" t="inlineStr">
-        <is>
-          <t>Aguado Rubira, Pedro Francisco</t>
-        </is>
-      </c>
-      <c r="P313" s="2" t="inlineStr">
-        <is>
-          <t>2008</t>
-        </is>
-      </c>
-      <c r="Q313" s="2" t="inlineStr">
-        <is>
-          <t>MCU — inferido</t>
-        </is>
-      </c>
+      <c r="O313" s="2" t="inlineStr"/>
+      <c r="P313" s="2" t="inlineStr"/>
+      <c r="Q313" s="2" t="inlineStr"/>
       <c r="R313" s="2" t="inlineStr">
         <is>
           <t>sí</t>
@@ -30087,7 +30063,7 @@
       </c>
       <c r="P364" s="2" t="inlineStr">
         <is>
-          <t>1886</t>
+          <t>2023</t>
         </is>
       </c>
       <c r="Q364" s="2" t="inlineStr">
@@ -30363,7 +30339,7 @@
       </c>
       <c r="P367" s="2" t="inlineStr">
         <is>
-          <t>2014</t>
+          <t>2021</t>
         </is>
       </c>
       <c r="Q367" s="2" t="inlineStr">
@@ -31374,21 +31350,9 @@
           <t>sin datos</t>
         </is>
       </c>
-      <c r="O379" s="2" t="inlineStr">
-        <is>
-          <t>Editorial Verbum, S.L.</t>
-        </is>
-      </c>
-      <c r="P379" s="2" t="inlineStr">
-        <is>
-          <t>2001</t>
-        </is>
-      </c>
-      <c r="Q379" s="2" t="inlineStr">
-        <is>
-          <t>MCU — inferido</t>
-        </is>
-      </c>
+      <c r="O379" s="2" t="inlineStr"/>
+      <c r="P379" s="2" t="inlineStr"/>
+      <c r="Q379" s="2" t="inlineStr"/>
       <c r="R379" s="2" t="inlineStr">
         <is>
           <t>sí</t>
@@ -33720,21 +33684,9 @@
           <t>sin datos</t>
         </is>
       </c>
-      <c r="O406" s="2" t="inlineStr">
-        <is>
-          <t>Sar Alejandria Ediciones</t>
-        </is>
-      </c>
-      <c r="P406" s="2" t="inlineStr">
-        <is>
-          <t>2020</t>
-        </is>
-      </c>
-      <c r="Q406" s="2" t="inlineStr">
-        <is>
-          <t>MCU — inferido</t>
-        </is>
-      </c>
+      <c r="O406" s="2" t="inlineStr"/>
+      <c r="P406" s="2" t="inlineStr"/>
+      <c r="Q406" s="2" t="inlineStr"/>
       <c r="R406" s="2" t="inlineStr">
         <is>
           <t>sí</t>
@@ -35816,21 +35768,9 @@
           <t>sin datos</t>
         </is>
       </c>
-      <c r="O431" s="2" t="inlineStr">
-        <is>
-          <t>Harlequin Ibérica</t>
-        </is>
-      </c>
-      <c r="P431" s="2" t="inlineStr">
-        <is>
-          <t>1991</t>
-        </is>
-      </c>
-      <c r="Q431" s="2" t="inlineStr">
-        <is>
-          <t>MCU — inferido</t>
-        </is>
-      </c>
+      <c r="O431" s="2" t="inlineStr"/>
+      <c r="P431" s="2" t="inlineStr"/>
+      <c r="Q431" s="2" t="inlineStr"/>
       <c r="R431" s="2" t="inlineStr">
         <is>
           <t>sí</t>
@@ -36677,7 +36617,7 @@
       </c>
       <c r="P441" s="2" t="inlineStr">
         <is>
-          <t>2097</t>
+          <t>1995</t>
         </is>
       </c>
       <c r="Q441" s="2" t="inlineStr">
@@ -36939,7 +36879,7 @@
       </c>
       <c r="P444" s="2" t="inlineStr">
         <is>
-          <t>1989</t>
+          <t>2013</t>
         </is>
       </c>
       <c r="Q444" s="2" t="inlineStr">
@@ -37111,7 +37051,7 @@
       </c>
       <c r="P446" s="2" t="inlineStr">
         <is>
-          <t>1885</t>
+          <t>2014</t>
         </is>
       </c>
       <c r="Q446" s="2" t="inlineStr">
@@ -38387,7 +38327,7 @@
       </c>
       <c r="P461" s="2" t="inlineStr">
         <is>
-          <t>1853</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="Q461" s="2" t="inlineStr">
@@ -39243,7 +39183,7 @@
       </c>
       <c r="P471" s="2" t="inlineStr">
         <is>
-          <t>1988</t>
+          <t>2021</t>
         </is>
       </c>
       <c r="Q471" s="2" t="inlineStr">
@@ -39852,21 +39792,9 @@
           <t>sin datos</t>
         </is>
       </c>
-      <c r="O478" s="2" t="inlineStr">
-        <is>
-          <t>Axóuxere Editora</t>
-        </is>
-      </c>
-      <c r="P478" s="2" t="inlineStr">
-        <is>
-          <t>2017</t>
-        </is>
-      </c>
-      <c r="Q478" s="2" t="inlineStr">
-        <is>
-          <t>MCU — inferido</t>
-        </is>
-      </c>
+      <c r="O478" s="2" t="inlineStr"/>
+      <c r="P478" s="2" t="inlineStr"/>
+      <c r="Q478" s="2" t="inlineStr"/>
       <c r="R478" s="2" t="inlineStr">
         <is>
           <t>sí</t>
@@ -40628,21 +40556,9 @@
           <t>sin datos</t>
         </is>
       </c>
-      <c r="O487" s="2" t="inlineStr">
-        <is>
-          <t>Nova Terra, S.A.</t>
-        </is>
-      </c>
-      <c r="P487" s="2" t="inlineStr">
-        <is>
-          <t>1969</t>
-        </is>
-      </c>
-      <c r="Q487" s="2" t="inlineStr">
-        <is>
-          <t>MCU — inferido</t>
-        </is>
-      </c>
+      <c r="O487" s="2" t="inlineStr"/>
+      <c r="P487" s="2" t="inlineStr"/>
+      <c r="Q487" s="2" t="inlineStr"/>
       <c r="R487" s="2" t="inlineStr">
         <is>
           <t>sí</t>
@@ -41068,21 +40984,9 @@
           <t>sin datos</t>
         </is>
       </c>
-      <c r="O492" s="2" t="inlineStr">
-        <is>
-          <t>Babidi-Bú</t>
-        </is>
-      </c>
-      <c r="P492" s="2" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="Q492" s="2" t="inlineStr">
-        <is>
-          <t>MCU — inferido</t>
-        </is>
-      </c>
+      <c r="O492" s="2" t="inlineStr"/>
+      <c r="P492" s="2" t="inlineStr"/>
+      <c r="Q492" s="2" t="inlineStr"/>
       <c r="R492" s="2" t="inlineStr">
         <is>
           <t>sí</t>
@@ -41368,7 +41272,7 @@
       </c>
       <c r="Q495" s="2" t="inlineStr">
         <is>
-          <t>MCU — inferido</t>
+          <t>MCU — verificado</t>
         </is>
       </c>
       <c r="R495" s="2" t="inlineStr">
@@ -42140,7 +42044,7 @@
       </c>
       <c r="Q504" s="2" t="inlineStr">
         <is>
-          <t>MCU — inferido</t>
+          <t>MCU — verificado</t>
         </is>
       </c>
       <c r="R504" s="2" t="inlineStr">
@@ -43420,21 +43324,9 @@
           <t>sin datos</t>
         </is>
       </c>
-      <c r="O519" s="2" t="inlineStr">
-        <is>
-          <t>Instituto de Estadística y Cartografía de Andalucía</t>
-        </is>
-      </c>
-      <c r="P519" s="2" t="inlineStr">
-        <is>
-          <t>2012</t>
-        </is>
-      </c>
-      <c r="Q519" s="2" t="inlineStr">
-        <is>
-          <t>MCU — inferido</t>
-        </is>
-      </c>
+      <c r="O519" s="2" t="inlineStr"/>
+      <c r="P519" s="2" t="inlineStr"/>
+      <c r="Q519" s="2" t="inlineStr"/>
       <c r="R519" s="2" t="inlineStr">
         <is>
           <t>sí</t>
@@ -44069,7 +43961,7 @@
       </c>
       <c r="P526" s="2" t="inlineStr">
         <is>
-          <t>1925</t>
+          <t>2002</t>
         </is>
       </c>
       <c r="Q526" s="2" t="inlineStr">
@@ -46244,21 +46136,9 @@
           <t>sin datos</t>
         </is>
       </c>
-      <c r="O551" s="2" t="inlineStr">
-        <is>
-          <t>Abenójar Sanjuán, Óscar</t>
-        </is>
-      </c>
-      <c r="P551" s="2" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="Q551" s="2" t="inlineStr">
-        <is>
-          <t>MCU — inferido</t>
-        </is>
-      </c>
+      <c r="O551" s="2" t="inlineStr"/>
+      <c r="P551" s="2" t="inlineStr"/>
+      <c r="Q551" s="2" t="inlineStr"/>
       <c r="R551" s="2" t="inlineStr">
         <is>
           <t>sí</t>
@@ -49384,7 +49264,7 @@
       </c>
       <c r="Q587" s="2" t="inlineStr">
         <is>
-          <t>MCU — inferido</t>
+          <t>MCU — verificado</t>
         </is>
       </c>
       <c r="R587" s="2" t="inlineStr">
@@ -50360,7 +50240,7 @@
       </c>
       <c r="Q598" s="2" t="inlineStr">
         <is>
-          <t>MCU — inferido</t>
+          <t>MCU — verificado</t>
         </is>
       </c>
       <c r="R598" s="2" t="inlineStr">
@@ -50451,7 +50331,7 @@
       </c>
       <c r="P599" s="2" t="inlineStr">
         <is>
-          <t>1888</t>
+          <t>2011</t>
         </is>
       </c>
       <c r="Q599" s="2" t="inlineStr">
@@ -52634,21 +52514,9 @@
           <t>sin datos</t>
         </is>
       </c>
-      <c r="O624" s="2" t="inlineStr">
-        <is>
-          <t>Badenes Bou, María Elena</t>
-        </is>
-      </c>
-      <c r="P624" s="2" t="inlineStr">
-        <is>
-          <t>2022</t>
-        </is>
-      </c>
-      <c r="Q624" s="2" t="inlineStr">
-        <is>
-          <t>MCU — inferido</t>
-        </is>
-      </c>
+      <c r="O624" s="2" t="inlineStr"/>
+      <c r="P624" s="2" t="inlineStr"/>
+      <c r="Q624" s="2" t="inlineStr"/>
       <c r="R624" s="2" t="inlineStr">
         <is>
           <t>sí</t>
@@ -53619,7 +53487,7 @@
       </c>
       <c r="P636" s="2" t="inlineStr">
         <is>
-          <t>2007</t>
+          <t>2004</t>
         </is>
       </c>
       <c r="Q636" s="2" t="inlineStr">
@@ -53702,21 +53570,9 @@
           <t>sin datos</t>
         </is>
       </c>
-      <c r="O637" s="2" t="inlineStr">
-        <is>
-          <t>Ediciones Encuentro, S.A.</t>
-        </is>
-      </c>
-      <c r="P637" s="2" t="inlineStr">
-        <is>
-          <t>2022</t>
-        </is>
-      </c>
-      <c r="Q637" s="2" t="inlineStr">
-        <is>
-          <t>MCU — inferido</t>
-        </is>
-      </c>
+      <c r="O637" s="2" t="inlineStr"/>
+      <c r="P637" s="2" t="inlineStr"/>
+      <c r="Q637" s="2" t="inlineStr"/>
       <c r="R637" s="2" t="inlineStr">
         <is>
           <t>sí</t>
@@ -56416,21 +56272,9 @@
           <t>sin datos</t>
         </is>
       </c>
-      <c r="O669" s="2" t="inlineStr">
-        <is>
-          <t>De Vecchi Ediciones, S.A.</t>
-        </is>
-      </c>
-      <c r="P669" s="2" t="inlineStr">
-        <is>
-          <t>1996</t>
-        </is>
-      </c>
-      <c r="Q669" s="2" t="inlineStr">
-        <is>
-          <t>MCU — inferido</t>
-        </is>
-      </c>
+      <c r="O669" s="2" t="inlineStr"/>
+      <c r="P669" s="2" t="inlineStr"/>
+      <c r="Q669" s="2" t="inlineStr"/>
       <c r="R669" s="2" t="inlineStr">
         <is>
           <t>sí</t>
@@ -56598,21 +56442,9 @@
           <t>sin datos</t>
         </is>
       </c>
-      <c r="O671" s="2" t="inlineStr">
-        <is>
-          <t>Álvarez Álvarez, Covadonga</t>
-        </is>
-      </c>
-      <c r="P671" s="2" t="inlineStr">
-        <is>
-          <t>2024</t>
-        </is>
-      </c>
-      <c r="Q671" s="2" t="inlineStr">
-        <is>
-          <t>MCU — inferido</t>
-        </is>
-      </c>
+      <c r="O671" s="2" t="inlineStr"/>
+      <c r="P671" s="2" t="inlineStr"/>
+      <c r="Q671" s="2" t="inlineStr"/>
       <c r="R671" s="2" t="inlineStr">
         <is>
           <t>sí</t>
